--- a/packages/calculators/src/modules/test/4.7-other-livestock-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.7-other-livestock-manure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47116608-09EC-0345-95F2-F5B53AF80DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEE1AAC-71EE-1A42-95E6-0B8A507DDCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51360" yWindow="6120" windowWidth="28800" windowHeight="25760" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="93">
   <si>
     <t>Livestock type</t>
   </si>
@@ -135,15 +135,6 @@
   </si>
   <si>
     <t>MAT</t>
-  </si>
-  <si>
-    <t>≤10</t>
-  </si>
-  <si>
-    <t>≥28</t>
-  </si>
-  <si>
-    <t>Climate zone</t>
   </si>
   <si>
     <t>State</t>
@@ -404,6 +395,18 @@
   </si>
   <si>
     <t>FracGASMSoil</t>
+  </si>
+  <si>
+    <t>Temperature zone</t>
+  </si>
+  <si>
+    <t>input (method 2)</t>
+  </si>
+  <si>
+    <t>10 or below</t>
+  </si>
+  <si>
+    <t>28 or above</t>
   </si>
 </sst>
 </file>
@@ -840,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A5655F-5BFE-554E-A3D3-9DFA9517010F}">
-  <dimension ref="A1:AM55"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="3" customWidth="1"/>
@@ -848,7 +851,8 @@
     <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.6640625" customWidth="1"/>
     <col min="5" max="5" width="29.6640625" customWidth="1"/>
-    <col min="6" max="7" width="12.1640625" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" customWidth="1"/>
     <col min="8" max="8" width="5.5" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -886,18 +890,18 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="Z3" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
       <c r="AG3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AH3">
         <v>0.21</v>
       </c>
       <c r="AJ3" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AK3">
         <v>0.24</v>
@@ -907,6 +911,9 @@
       <c r="C4">
         <v>1776</v>
       </c>
+      <c r="F4">
+        <v>1779</v>
+      </c>
       <c r="I4">
         <v>1783</v>
       </c>
@@ -953,17 +960,17 @@
         <v>1779</v>
       </c>
       <c r="Z4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AG4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="AH4">
         <f>44/28</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="AJ4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AK4">
         <v>0.11</v>
@@ -971,61 +978,64 @@
     </row>
     <row r="5" spans="1:39">
       <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" t="s">
         <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="M5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="S5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="T5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="V5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="W5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Y5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="AG5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="AH5">
         <v>0.6784</v>
       </c>
       <c r="AJ5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AK5">
         <v>0.19</v>
@@ -1035,21 +1045,21 @@
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="AF6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="AG6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AH6">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="AJ6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:39">
       <c r="AG7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AH7">
         <v>2E-3</v>
@@ -1064,15 +1074,15 @@
     <row r="9" spans="1:39">
       <c r="A9" s="4"/>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AH9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="AJ9" s="2"/>
       <c r="AK9" s="2"/>
       <c r="AM9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:39" ht="17">
@@ -1086,98 +1096,98 @@
         <v>2</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="P10" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q10" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="R10" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="S10" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="K10" s="6" t="s">
+      <c r="T10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="V10" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="W10" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="X10" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y10" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z10" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="R10" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="S10" s="11" t="s">
+      <c r="AA10" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB10" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC10" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="T10" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="U10" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="V10" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="W10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="X10" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y10" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z10" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA10" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB10" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC10" s="9" t="s">
-        <v>54</v>
       </c>
       <c r="AD10" s="11"/>
       <c r="AE10" s="11"/>
       <c r="AG10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AH10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AI10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AJ10" s="2"/>
       <c r="AK10" s="2"/>
       <c r="AL10" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AM10" s="2">
         <v>5.8999999999999999E-3</v>
@@ -1194,13 +1204,13 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I11">
         <f>VLOOKUP(A11, $AG$11:$AH$18,2,FALSE)</f>
@@ -1211,7 +1221,7 @@
         <v>0.19</v>
       </c>
       <c r="K11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L11">
         <f>1-M11</f>
@@ -1289,7 +1299,7 @@
       <c r="AJ11" s="2"/>
       <c r="AK11" s="2"/>
       <c r="AL11" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="AM11" s="2">
         <v>7.0000000000000001E-3</v>
@@ -1306,13 +1316,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I12">
         <f>VLOOKUP(A12, $AG$11:$AH$18,2,FALSE)</f>
@@ -1323,7 +1333,7 @@
         <v>0.19</v>
       </c>
       <c r="K12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L12">
         <f>1-M12</f>
@@ -1401,7 +1411,7 @@
       <c r="AJ12" s="2"/>
       <c r="AK12" s="2"/>
       <c r="AL12" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AM12" s="2">
         <v>1.8E-3</v>
@@ -1418,13 +1428,13 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I13">
         <f t="shared" ref="I13:I30" si="0">VLOOKUP(A13, $AG$11:$AH$18,2,FALSE)</f>
@@ -1435,7 +1445,7 @@
         <v>0.19</v>
       </c>
       <c r="K13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L13">
         <f t="shared" ref="L13:L30" si="2">1-M13</f>
@@ -1513,7 +1523,7 @@
       <c r="AJ13" s="2"/>
       <c r="AK13" s="2"/>
       <c r="AL13" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AM13" s="2">
         <v>2.8999999999999998E-3</v>
@@ -1530,13 +1540,13 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I14">
         <f t="shared" si="0"/>
@@ -1547,7 +1557,7 @@
         <v>0.19</v>
       </c>
       <c r="K14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L14">
         <f t="shared" si="2"/>
@@ -1625,7 +1635,7 @@
       <c r="AJ14" s="2"/>
       <c r="AK14" s="2"/>
       <c r="AL14" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AM14" s="2">
         <v>8.0000000000000002E-3</v>
@@ -1642,13 +1652,13 @@
         <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I15">
         <f t="shared" si="0"/>
@@ -1659,7 +1669,7 @@
         <v>0.19</v>
       </c>
       <c r="K15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L15">
         <f t="shared" si="2"/>
@@ -1737,7 +1747,7 @@
       <c r="AJ15" s="2"/>
       <c r="AK15" s="2"/>
       <c r="AL15" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AM15" s="2">
         <v>1.9900000000000001E-2</v>
@@ -1754,10 +1764,10 @@
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>28</v>
@@ -1771,7 +1781,7 @@
         <v>0.19</v>
       </c>
       <c r="K16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L16">
         <f t="shared" si="2"/>
@@ -1849,7 +1859,7 @@
       <c r="AJ16" s="2"/>
       <c r="AK16" s="2"/>
       <c r="AL16" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AM16" s="2">
         <v>5.3E-3</v>
@@ -1866,13 +1876,13 @@
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I17">
         <f t="shared" si="0"/>
@@ -1883,7 +1893,7 @@
         <v>0.19</v>
       </c>
       <c r="K17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L17">
         <f t="shared" si="2"/>
@@ -1961,7 +1971,7 @@
       <c r="AJ17" s="2"/>
       <c r="AK17" s="2"/>
       <c r="AL17" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AM17" s="2">
         <v>6.4000000000000003E-3</v>
@@ -1978,13 +1988,13 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I18">
         <f t="shared" si="0"/>
@@ -1995,7 +2005,7 @@
         <v>0.19</v>
       </c>
       <c r="K18" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L18">
         <f t="shared" si="2"/>
@@ -2062,7 +2072,7 @@
         <v>9.0217403904000024E-4</v>
       </c>
       <c r="AG18" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AH18" s="2">
         <v>0.34</v>
@@ -2073,7 +2083,7 @@
       <c r="AJ18" s="2"/>
       <c r="AK18" s="10"/>
       <c r="AL18" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AM18" s="2">
         <v>2.5999999999999999E-3</v>
@@ -2090,13 +2100,13 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I19">
         <f t="shared" si="0"/>
@@ -2107,7 +2117,7 @@
         <v>0.19</v>
       </c>
       <c r="K19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L19">
         <f t="shared" si="2"/>
@@ -2176,7 +2186,7 @@
       <c r="AJ19" s="2"/>
       <c r="AK19" s="10"/>
       <c r="AL19" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AM19" s="2">
         <v>3.0000000000000001E-3</v>
@@ -2193,13 +2203,13 @@
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I20">
         <f t="shared" si="0"/>
@@ -2210,7 +2220,7 @@
         <v>0.19</v>
       </c>
       <c r="K20" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L20">
         <f t="shared" si="2"/>
@@ -2279,7 +2289,7 @@
       <c r="AJ20" s="2"/>
       <c r="AK20" s="2"/>
       <c r="AL20" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AM20" s="2">
         <v>5.0000000000000001E-3</v>
@@ -2296,13 +2306,13 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I21">
         <f t="shared" si="0"/>
@@ -2313,7 +2323,7 @@
         <v>0.19</v>
       </c>
       <c r="K21" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L21">
         <f t="shared" si="2"/>
@@ -2388,7 +2398,7 @@
       <c r="AJ21" s="2"/>
       <c r="AK21" s="2"/>
       <c r="AL21" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AM21" s="2">
         <v>2.5999999999999999E-3</v>
@@ -2405,13 +2415,13 @@
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I22">
         <f t="shared" si="0"/>
@@ -2422,7 +2432,7 @@
         <v>0.19</v>
       </c>
       <c r="K22" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L22">
         <f t="shared" si="2"/>
@@ -2492,7 +2502,7 @@
         <v>27</v>
       </c>
       <c r="AL22" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AM22" s="2">
         <v>1.8E-3</v>
@@ -2509,13 +2519,13 @@
         <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I23">
         <f t="shared" si="0"/>
@@ -2526,7 +2536,7 @@
         <v>0.19</v>
       </c>
       <c r="K23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L23">
         <f t="shared" si="2"/>
@@ -2611,10 +2621,10 @@
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>28</v>
@@ -2628,7 +2638,7 @@
         <v>0.19</v>
       </c>
       <c r="K24" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L24">
         <f t="shared" si="2"/>
@@ -2695,7 +2705,7 @@
         <v>3.0798248539968022E-2</v>
       </c>
       <c r="AG24" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="AH24" s="2">
         <v>0.75</v>
@@ -2714,13 +2724,13 @@
         <v>19</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I25">
         <f t="shared" si="0"/>
@@ -2731,7 +2741,7 @@
         <v>0.19</v>
       </c>
       <c r="K25" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L25">
         <f t="shared" si="2"/>
@@ -2798,7 +2808,7 @@
         <v>3.4136148990944033E-2</v>
       </c>
       <c r="AG25" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AH25" s="2">
         <v>0.8</v>
@@ -2817,13 +2827,13 @@
         <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I26">
         <f t="shared" si="0"/>
@@ -2834,7 +2844,7 @@
         <v>0.19</v>
       </c>
       <c r="K26" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L26">
         <f t="shared" si="2"/>
@@ -2901,7 +2911,7 @@
         <v>0.11422028619456009</v>
       </c>
       <c r="AG26" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AH26" s="2">
         <v>0.78</v>
@@ -2920,13 +2930,13 @@
         <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I27">
         <f t="shared" si="0"/>
@@ -2937,7 +2947,7 @@
         <v>0.19</v>
       </c>
       <c r="K27" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L27">
         <f t="shared" si="2"/>
@@ -3004,7 +3014,7 @@
         <v>1.4600583098304016E-2</v>
       </c>
       <c r="AG27" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="AH27" s="2">
         <v>0.74</v>
@@ -3023,13 +3033,13 @@
         <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I28">
         <f t="shared" si="0"/>
@@ -3040,7 +3050,7 @@
         <v>0.19</v>
       </c>
       <c r="K28" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L28">
         <f t="shared" si="2"/>
@@ -3107,7 +3117,7 @@
         <v>0.11716537914681611</v>
       </c>
       <c r="AG28" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH28" s="2">
         <v>0.7</v>
@@ -3126,13 +3136,13 @@
         <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I29">
         <f t="shared" si="0"/>
@@ -3143,7 +3153,7 @@
         <v>0.19</v>
       </c>
       <c r="K29" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L29">
         <f t="shared" si="2"/>
@@ -3210,7 +3220,7 @@
         <v>3.8860970305248023E-2</v>
       </c>
       <c r="AG29" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AH29" s="2">
         <v>0.74</v>
@@ -3220,7 +3230,7 @@
     </row>
     <row r="30" spans="1:39">
       <c r="A30" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>23</v>
@@ -3229,13 +3239,13 @@
         <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I30">
         <f t="shared" si="0"/>
@@ -3246,7 +3256,7 @@
         <v>0.19</v>
       </c>
       <c r="K30" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L30">
         <f t="shared" si="2"/>
@@ -3313,7 +3323,7 @@
         <v>1.5918572990976015E-2</v>
       </c>
       <c r="AG30" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="AH30" s="2">
         <v>0.76</v>
@@ -3331,37 +3341,37 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="5:34">
+    <row r="33" spans="1:34">
       <c r="E33" s="2"/>
       <c r="AG33">
         <v>4.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="34" spans="5:34">
+    <row r="34" spans="1:34">
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="5:34">
+    <row r="35" spans="1:34">
       <c r="E35" s="2"/>
       <c r="AG35" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="5:34">
+    <row r="36" spans="1:34">
       <c r="E36" s="2"/>
       <c r="AG36" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="5:34">
+    <row r="37" spans="1:34">
       <c r="E37" s="2"/>
       <c r="AG37" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="AH37">
         <v>0.66</v>
       </c>
     </row>
-    <row r="38" spans="5:34">
+    <row r="38" spans="1:34">
       <c r="E38" s="2"/>
       <c r="AG38">
         <v>11</v>
@@ -3370,7 +3380,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="39" spans="5:34">
+    <row r="39" spans="1:34">
       <c r="AG39">
         <v>12</v>
       </c>
@@ -3378,7 +3388,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="40" spans="5:34">
+    <row r="40" spans="1:34">
       <c r="AG40">
         <v>13</v>
       </c>
@@ -3386,7 +3396,103 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="41" spans="5:34">
+    <row r="41" spans="1:34" ht="17">
+      <c r="A41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41">
+        <v>5</v>
+      </c>
+      <c r="D41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41" t="s">
+        <v>66</v>
+      </c>
+      <c r="I41">
+        <f>VLOOKUP(A41, $AG$11:$AH$18,2,FALSE)</f>
+        <v>2.73</v>
+      </c>
+      <c r="J41">
+        <f>$AK$5</f>
+        <v>0.19</v>
+      </c>
+      <c r="K41" t="s">
+        <v>57</v>
+      </c>
+      <c r="L41">
+        <f>1-M41</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="M41">
+        <f>IF(K41="yes", 1, 0.95)</f>
+        <v>0.95</v>
+      </c>
+      <c r="N41">
+        <f>$AH$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O41">
+        <f>VLOOKUP(A41, $AG$11:$AI$18,3,FALSE)</f>
+        <v>39.5</v>
+      </c>
+      <c r="P41">
+        <f>VLOOKUP(E41,$AL$10:$AM$22,2,FALSE)</f>
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="Q41">
+        <f>IF(D41="yes", 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="S41">
+        <f>$AK$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="T41">
+        <f>$AK$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="U41">
+        <f>$AH$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W41">
+        <f>VLOOKUP(F41, $AG$37:$AH$55, 2, FALSE)</f>
+        <v>0.66</v>
+      </c>
+      <c r="X41">
+        <f>I41*J41*L41*W41*U41</f>
+        <v>1.1612240640000012E-2</v>
+      </c>
+      <c r="Y41">
+        <f>$AG$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z41">
+        <f>I41*J41*M41*Y41*U41</f>
+        <v>1.5711713472E-3</v>
+      </c>
+      <c r="AA41">
+        <f>C41*X41*365</f>
+        <v>21.192339168000025</v>
+      </c>
+      <c r="AB41">
+        <f>C41*Z41*365</f>
+        <v>2.8673877086399999</v>
+      </c>
+      <c r="AC41">
+        <f>(AA41+AB41)*10^-3</f>
+        <v>2.4059726876640024E-2</v>
+      </c>
       <c r="AG41">
         <v>14</v>
       </c>
@@ -3394,7 +3500,103 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="42" spans="5:34">
+    <row r="42" spans="1:34" ht="17">
+      <c r="A42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42">
+        <v>6</v>
+      </c>
+      <c r="D42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F42">
+        <v>11</v>
+      </c>
+      <c r="H42" t="s">
+        <v>66</v>
+      </c>
+      <c r="I42">
+        <f>VLOOKUP(A42, $AG$11:$AH$18,2,FALSE)</f>
+        <v>2.73</v>
+      </c>
+      <c r="J42">
+        <f>$AK$5</f>
+        <v>0.19</v>
+      </c>
+      <c r="K42" t="s">
+        <v>57</v>
+      </c>
+      <c r="L42">
+        <f>1-M42</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="M42">
+        <f>IF(K42="yes", 1, 0.95)</f>
+        <v>0.95</v>
+      </c>
+      <c r="N42">
+        <f>$AH$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O42">
+        <f>VLOOKUP(A42, $AG$11:$AI$18,3,FALSE)</f>
+        <v>39.5</v>
+      </c>
+      <c r="P42">
+        <f>VLOOKUP(E42,$AL$10:$AM$22,2,FALSE)</f>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Q42">
+        <f>IF(D42="yes", 1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <f>$AK$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="T42">
+        <f>$AK$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="U42">
+        <f>$AH$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W42">
+        <f t="shared" ref="W42:W60" si="18">VLOOKUP(F42, $AG$37:$AH$55, 2, FALSE)</f>
+        <v>0.68</v>
+      </c>
+      <c r="X42">
+        <f>I42*J42*L42*W42*U42</f>
+        <v>1.1964126720000011E-2</v>
+      </c>
+      <c r="Y42">
+        <f>$AG$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z42">
+        <f>I42*J42*M42*Y42*U42</f>
+        <v>1.5711713472E-3</v>
+      </c>
+      <c r="AA42">
+        <f>C42*X42*365</f>
+        <v>26.201437516800027</v>
+      </c>
+      <c r="AB42">
+        <f>C42*Z42*365</f>
+        <v>3.4408652503679997</v>
+      </c>
+      <c r="AC42">
+        <f>(AA42+AB42)*10^-3</f>
+        <v>2.9642302767168026E-2</v>
+      </c>
       <c r="AG42">
         <v>15</v>
       </c>
@@ -3402,7 +3604,103 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="43" spans="5:34">
+    <row r="43" spans="1:34" ht="17">
+      <c r="A43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43">
+        <v>7</v>
+      </c>
+      <c r="D43" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F43">
+        <v>12</v>
+      </c>
+      <c r="H43" t="s">
+        <v>66</v>
+      </c>
+      <c r="I43">
+        <f t="shared" ref="I43:I60" si="19">VLOOKUP(A43, $AG$11:$AH$18,2,FALSE)</f>
+        <v>2.73</v>
+      </c>
+      <c r="J43">
+        <f t="shared" ref="J43:J60" si="20">$AK$5</f>
+        <v>0.19</v>
+      </c>
+      <c r="K43" t="s">
+        <v>57</v>
+      </c>
+      <c r="L43">
+        <f t="shared" ref="L43:L60" si="21">1-M43</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="M43">
+        <f t="shared" ref="M43:M60" si="22">IF(K43="yes", 1, 0.95)</f>
+        <v>0.95</v>
+      </c>
+      <c r="N43">
+        <f t="shared" ref="N43:N60" si="23">$AH$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O43">
+        <f t="shared" ref="O43:O60" si="24">VLOOKUP(A43, $AG$11:$AI$18,3,FALSE)</f>
+        <v>39.5</v>
+      </c>
+      <c r="P43">
+        <f t="shared" ref="P43:P60" si="25">VLOOKUP(E43,$AL$10:$AM$22,2,FALSE)</f>
+        <v>1.8E-3</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" ref="Q43:Q60" si="26">IF(D43="yes", 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="S43">
+        <f t="shared" ref="S43:S60" si="27">$AK$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="T43">
+        <f t="shared" ref="T43:T60" si="28">$AK$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="U43">
+        <f t="shared" ref="U43:U60" si="29">$AH$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W43">
+        <f t="shared" si="18"/>
+        <v>0.7</v>
+      </c>
+      <c r="X43">
+        <f t="shared" ref="X43:X60" si="30">I43*J43*L43*W43*U43</f>
+        <v>1.231601280000001E-2</v>
+      </c>
+      <c r="Y43">
+        <f t="shared" ref="Y43:Y60" si="31">$AG$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z43">
+        <f t="shared" ref="Z43:Z60" si="32">I43*J43*M43*Y43*U43</f>
+        <v>1.5711713472E-3</v>
+      </c>
+      <c r="AA43">
+        <f t="shared" ref="AA43:AA60" si="33">C43*X43*365</f>
+        <v>31.467412704000026</v>
+      </c>
+      <c r="AB43">
+        <f t="shared" ref="AB43:AB60" si="34">C43*Z43*365</f>
+        <v>4.0143427920960004</v>
+      </c>
+      <c r="AC43">
+        <f t="shared" ref="AC43:AC60" si="35">(AA43+AB43)*10^-3</f>
+        <v>3.5481755496096029E-2</v>
+      </c>
       <c r="AG43">
         <v>16</v>
       </c>
@@ -3410,7 +3708,103 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="44" spans="5:34">
+    <row r="44" spans="1:34" ht="17">
+      <c r="A44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s">
+        <v>66</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="19"/>
+        <v>2.73</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K44" t="s">
+        <v>57</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="21"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="22"/>
+        <v>0.95</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="24"/>
+        <v>39.5</v>
+      </c>
+      <c r="P44">
+        <f t="shared" si="25"/>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T44">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U44">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W44">
+        <f t="shared" si="18"/>
+        <v>0.71</v>
+      </c>
+      <c r="X44">
+        <f t="shared" si="30"/>
+        <v>1.2491955840000011E-2</v>
+      </c>
+      <c r="Y44">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z44">
+        <f t="shared" si="32"/>
+        <v>1.5711713472E-3</v>
+      </c>
+      <c r="AA44">
+        <f t="shared" si="33"/>
+        <v>36.476511052800035</v>
+      </c>
+      <c r="AB44">
+        <f t="shared" si="34"/>
+        <v>4.5878203338240002</v>
+      </c>
+      <c r="AC44">
+        <f t="shared" si="35"/>
+        <v>4.1064331386624034E-2</v>
+      </c>
       <c r="AG44">
         <v>17</v>
       </c>
@@ -3418,7 +3812,103 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="45" spans="5:34">
+    <row r="45" spans="1:34" ht="17">
+      <c r="A45" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45">
+        <v>9</v>
+      </c>
+      <c r="D45" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F45">
+        <v>14</v>
+      </c>
+      <c r="H45" t="s">
+        <v>66</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="19"/>
+        <v>0.34</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K45" t="s">
+        <v>57</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="21"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="22"/>
+        <v>0.95</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="P45">
+        <f t="shared" si="25"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T45">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U45">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W45">
+        <f t="shared" si="18"/>
+        <v>0.73</v>
+      </c>
+      <c r="X45">
+        <f t="shared" si="30"/>
+        <v>1.5995993600000015E-3</v>
+      </c>
+      <c r="Y45">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z45">
+        <f t="shared" si="32"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AA45">
+        <f t="shared" si="33"/>
+        <v>5.254683897600005</v>
+      </c>
+      <c r="AB45">
+        <f t="shared" si="34"/>
+        <v>0.64279900281600011</v>
+      </c>
+      <c r="AC45">
+        <f t="shared" si="35"/>
+        <v>5.8974829004160047E-3</v>
+      </c>
       <c r="AG45">
         <v>18</v>
       </c>
@@ -3426,7 +3916,103 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="46" spans="5:34">
+    <row r="46" spans="1:34" ht="17">
+      <c r="A46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46">
+        <v>10</v>
+      </c>
+      <c r="D46" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F46">
+        <v>15</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="19"/>
+        <v>0.34</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K46" t="s">
+        <v>57</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="21"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="22"/>
+        <v>0.95</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="P46">
+        <f t="shared" si="25"/>
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="Q46">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T46">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U46">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W46">
+        <f t="shared" si="18"/>
+        <v>0.74</v>
+      </c>
+      <c r="X46">
+        <f t="shared" si="30"/>
+        <v>1.6215116800000018E-3</v>
+      </c>
+      <c r="Y46">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z46">
+        <f t="shared" si="32"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AA46">
+        <f t="shared" si="33"/>
+        <v>5.9185176320000075</v>
+      </c>
+      <c r="AB46">
+        <f t="shared" si="34"/>
+        <v>0.71422111424000012</v>
+      </c>
+      <c r="AC46">
+        <f t="shared" si="35"/>
+        <v>6.6327387462400073E-3</v>
+      </c>
       <c r="AG46">
         <v>19</v>
       </c>
@@ -3434,7 +4020,103 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="47" spans="5:34">
+    <row r="47" spans="1:34" ht="17">
+      <c r="A47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47">
+        <v>11</v>
+      </c>
+      <c r="D47" t="s">
+        <v>56</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F47">
+        <v>16</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="19"/>
+        <v>0.34</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K47" t="s">
+        <v>57</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="21"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="22"/>
+        <v>0.95</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="P47">
+        <f t="shared" si="25"/>
+        <v>5.3E-3</v>
+      </c>
+      <c r="Q47">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="S47">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T47">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U47">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W47">
+        <f t="shared" si="18"/>
+        <v>0.75</v>
+      </c>
+      <c r="X47">
+        <f t="shared" si="30"/>
+        <v>1.6434240000000016E-3</v>
+      </c>
+      <c r="Y47">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z47">
+        <f t="shared" si="32"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AA47">
+        <f t="shared" si="33"/>
+        <v>6.5983473600000062</v>
+      </c>
+      <c r="AB47">
+        <f t="shared" si="34"/>
+        <v>0.78564322566400013</v>
+      </c>
+      <c r="AC47">
+        <f t="shared" si="35"/>
+        <v>7.383990585664006E-3</v>
+      </c>
       <c r="AG47">
         <v>20</v>
       </c>
@@ -3442,7 +4124,103 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="48" spans="5:34">
+    <row r="48" spans="1:34" ht="17">
+      <c r="A48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>57</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F48">
+        <v>17</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="19"/>
+        <v>0.34</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K48" t="s">
+        <v>57</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="21"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="22"/>
+        <v>0.95</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O48">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="P48">
+        <f t="shared" si="25"/>
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="Q48">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T48">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U48">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W48">
+        <f t="shared" si="18"/>
+        <v>0.76</v>
+      </c>
+      <c r="X48">
+        <f t="shared" si="30"/>
+        <v>1.6653363200000019E-3</v>
+      </c>
+      <c r="Y48">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z48">
+        <f t="shared" si="32"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AA48">
+        <f t="shared" si="33"/>
+        <v>7.2941730816000083</v>
+      </c>
+      <c r="AB48">
+        <f t="shared" si="34"/>
+        <v>0.85706533708800003</v>
+      </c>
+      <c r="AC48">
+        <f t="shared" si="35"/>
+        <v>8.1512384186880078E-3</v>
+      </c>
       <c r="AG48">
         <v>21</v>
       </c>
@@ -3450,7 +4228,103 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="49" spans="33:34">
+    <row r="49" spans="1:34" ht="17">
+      <c r="A49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F49">
+        <v>18</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="19"/>
+        <v>0.34</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K49" t="s">
+        <v>57</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="21"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="22"/>
+        <v>0.95</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="P49">
+        <f t="shared" si="25"/>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="Q49">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="S49">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T49">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U49">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W49">
+        <f t="shared" si="18"/>
+        <v>0.77</v>
+      </c>
+      <c r="X49">
+        <f t="shared" si="30"/>
+        <v>1.6872486400000017E-3</v>
+      </c>
+      <c r="Y49">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z49">
+        <f t="shared" si="32"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AA49">
+        <f t="shared" si="33"/>
+        <v>8.0059947968000085</v>
+      </c>
+      <c r="AB49">
+        <f t="shared" si="34"/>
+        <v>0.92848744851200005</v>
+      </c>
+      <c r="AC49">
+        <f t="shared" si="35"/>
+        <v>8.9344822453120091E-3</v>
+      </c>
       <c r="AG49">
         <v>22</v>
       </c>
@@ -3458,7 +4332,103 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="50" spans="33:34">
+    <row r="50" spans="1:34" ht="17">
+      <c r="A50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50">
+        <v>14</v>
+      </c>
+      <c r="D50" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F50">
+        <v>19</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="19"/>
+        <v>0.34</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K50" t="s">
+        <v>57</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="21"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="22"/>
+        <v>0.95</v>
+      </c>
+      <c r="N50">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="P50">
+        <f t="shared" si="25"/>
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Q50">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T50">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U50">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W50">
+        <f t="shared" si="18"/>
+        <v>0.77</v>
+      </c>
+      <c r="X50">
+        <f t="shared" si="30"/>
+        <v>1.6872486400000017E-3</v>
+      </c>
+      <c r="Y50">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z50">
+        <f t="shared" si="32"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AA50">
+        <f t="shared" si="33"/>
+        <v>8.6218405504000089</v>
+      </c>
+      <c r="AB50">
+        <f t="shared" si="34"/>
+        <v>0.99990955993600006</v>
+      </c>
+      <c r="AC50">
+        <f t="shared" si="35"/>
+        <v>9.6217501103360095E-3</v>
+      </c>
       <c r="AG50">
         <v>23</v>
       </c>
@@ -3466,7 +4436,103 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="51" spans="33:34">
+    <row r="51" spans="1:34" ht="17">
+      <c r="A51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>56</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F51">
+        <v>20</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="19"/>
+        <v>0.34</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K51" t="s">
+        <v>56</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="P51">
+        <f t="shared" si="25"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="Q51">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="S51">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T51">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U51">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W51">
+        <f t="shared" si="18"/>
+        <v>0.78</v>
+      </c>
+      <c r="X51">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z51">
+        <f t="shared" si="32"/>
+        <v>2.0597580800000003E-4</v>
+      </c>
+      <c r="AA51">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <f t="shared" si="34"/>
+        <v>1.1277175488000002</v>
+      </c>
+      <c r="AC51">
+        <f t="shared" si="35"/>
+        <v>1.1277175488000003E-3</v>
+      </c>
       <c r="AG51">
         <v>24</v>
       </c>
@@ -3474,7 +4540,103 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="52" spans="33:34">
+    <row r="52" spans="1:34" ht="17">
+      <c r="A52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52">
+        <v>16</v>
+      </c>
+      <c r="D52" t="s">
+        <v>57</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F52">
+        <v>21</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="19"/>
+        <v>0.91</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K52" t="s">
+        <v>56</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="N52">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="24"/>
+        <v>13.2</v>
+      </c>
+      <c r="P52">
+        <f t="shared" si="25"/>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T52">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U52">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W52">
+        <f t="shared" si="18"/>
+        <v>0.78</v>
+      </c>
+      <c r="X52">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z52">
+        <f t="shared" si="32"/>
+        <v>5.5128819200000003E-4</v>
+      </c>
+      <c r="AA52">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <f t="shared" si="34"/>
+        <v>3.21952304128</v>
+      </c>
+      <c r="AC52">
+        <f t="shared" si="35"/>
+        <v>3.21952304128E-3</v>
+      </c>
       <c r="AG52">
         <v>25</v>
       </c>
@@ -3482,7 +4644,103 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="53" spans="33:34">
+    <row r="53" spans="1:34" ht="17">
+      <c r="A53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53">
+        <v>17</v>
+      </c>
+      <c r="D53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F53">
+        <v>22</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="19"/>
+        <v>0.91</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K53" t="s">
+        <v>56</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="N53">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="24"/>
+        <v>13.2</v>
+      </c>
+      <c r="P53">
+        <f t="shared" si="25"/>
+        <v>1.8E-3</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="S53">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U53">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W53">
+        <f t="shared" si="18"/>
+        <v>0.78</v>
+      </c>
+      <c r="X53">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z53">
+        <f t="shared" si="32"/>
+        <v>5.5128819200000003E-4</v>
+      </c>
+      <c r="AA53">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <f t="shared" si="34"/>
+        <v>3.4207432313599999</v>
+      </c>
+      <c r="AC53">
+        <f t="shared" si="35"/>
+        <v>3.4207432313600001E-3</v>
+      </c>
       <c r="AG53">
         <v>26</v>
       </c>
@@ -3490,7 +4748,103 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="54" spans="33:34">
+    <row r="54" spans="1:34" ht="17">
+      <c r="A54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54">
+        <v>18</v>
+      </c>
+      <c r="D54" t="s">
+        <v>57</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F54">
+        <v>23</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="19"/>
+        <v>0.91</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K54" t="s">
+        <v>56</v>
+      </c>
+      <c r="L54">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="N54">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O54">
+        <f t="shared" si="24"/>
+        <v>13.2</v>
+      </c>
+      <c r="P54">
+        <f t="shared" si="25"/>
+        <v>1.8E-3</v>
+      </c>
+      <c r="Q54">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T54">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U54">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W54">
+        <f t="shared" si="18"/>
+        <v>0.79</v>
+      </c>
+      <c r="X54">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z54">
+        <f t="shared" si="32"/>
+        <v>5.5128819200000003E-4</v>
+      </c>
+      <c r="AA54">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AB54">
+        <f t="shared" si="34"/>
+        <v>3.6219634214399998</v>
+      </c>
+      <c r="AC54">
+        <f t="shared" si="35"/>
+        <v>3.6219634214399998E-3</v>
+      </c>
       <c r="AG54">
         <v>27</v>
       </c>
@@ -3498,13 +4852,611 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="55" spans="33:34">
+    <row r="55" spans="1:34" ht="17">
+      <c r="A55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55">
+        <v>19</v>
+      </c>
+      <c r="D55" t="s">
+        <v>56</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F55">
+        <v>24</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="19"/>
+        <v>0.91</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K55" t="s">
+        <v>56</v>
+      </c>
+      <c r="L55">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O55">
+        <f t="shared" si="24"/>
+        <v>13.2</v>
+      </c>
+      <c r="P55">
+        <f t="shared" si="25"/>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="S55">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T55">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U55">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W55">
+        <f t="shared" si="18"/>
+        <v>0.79</v>
+      </c>
+      <c r="X55">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z55">
+        <f t="shared" si="32"/>
+        <v>5.5128819200000003E-4</v>
+      </c>
+      <c r="AA55">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <f t="shared" si="34"/>
+        <v>3.8231836115200006</v>
+      </c>
+      <c r="AC55">
+        <f t="shared" si="35"/>
+        <v>3.8231836115200008E-3</v>
+      </c>
       <c r="AG55" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="AH55">
         <v>0.8</v>
       </c>
+    </row>
+    <row r="56" spans="1:34">
+      <c r="A56" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56">
+        <v>20</v>
+      </c>
+      <c r="D56" t="s">
+        <v>57</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F56">
+        <v>25</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="19"/>
+        <v>2.73</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K56" t="s">
+        <v>56</v>
+      </c>
+      <c r="L56">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="N56">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O56">
+        <f t="shared" si="24"/>
+        <v>39.5</v>
+      </c>
+      <c r="P56">
+        <f t="shared" si="25"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Q56">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T56">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U56">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W56">
+        <f t="shared" si="18"/>
+        <v>0.79</v>
+      </c>
+      <c r="X56">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z56">
+        <f t="shared" si="32"/>
+        <v>1.6538645760000002E-3</v>
+      </c>
+      <c r="AA56">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <f t="shared" si="34"/>
+        <v>12.0732114048</v>
+      </c>
+      <c r="AC56">
+        <f t="shared" si="35"/>
+        <v>1.2073211404800001E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:34">
+      <c r="A57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57">
+        <v>21</v>
+      </c>
+      <c r="D57" t="s">
+        <v>56</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F57">
+        <v>26</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="19"/>
+        <v>0.34</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K57" t="s">
+        <v>56</v>
+      </c>
+      <c r="L57">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="N57">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O57">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="P57">
+        <f t="shared" si="25"/>
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="Q57">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="S57">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T57">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U57">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W57">
+        <f t="shared" si="18"/>
+        <v>0.79</v>
+      </c>
+      <c r="X57">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z57">
+        <f t="shared" si="32"/>
+        <v>2.0597580800000003E-4</v>
+      </c>
+      <c r="AA57">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <f t="shared" si="34"/>
+        <v>1.57880456832</v>
+      </c>
+      <c r="AC57">
+        <f t="shared" si="35"/>
+        <v>1.5788045683200001E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:34">
+      <c r="A58" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58">
+        <v>22</v>
+      </c>
+      <c r="D58" t="s">
+        <v>57</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F58">
+        <v>27</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="19"/>
+        <v>2.73</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K58" t="s">
+        <v>56</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="N58">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O58">
+        <f t="shared" si="24"/>
+        <v>39.5</v>
+      </c>
+      <c r="P58">
+        <f t="shared" si="25"/>
+        <v>5.3E-3</v>
+      </c>
+      <c r="Q58">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T58">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U58">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W58">
+        <f t="shared" si="18"/>
+        <v>0.8</v>
+      </c>
+      <c r="X58">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z58">
+        <f t="shared" si="32"/>
+        <v>1.6538645760000002E-3</v>
+      </c>
+      <c r="AA58">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <f t="shared" si="34"/>
+        <v>13.28053254528</v>
+      </c>
+      <c r="AC58">
+        <f t="shared" si="35"/>
+        <v>1.3280532545279999E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:34">
+      <c r="A59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59">
+        <v>23</v>
+      </c>
+      <c r="D59" t="s">
+        <v>56</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F59" t="s">
+        <v>92</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="19"/>
+        <v>0.91</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K59" t="s">
+        <v>56</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="N59">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O59">
+        <f t="shared" si="24"/>
+        <v>13.2</v>
+      </c>
+      <c r="P59">
+        <f t="shared" si="25"/>
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="Q59">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="S59">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T59">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U59">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W59">
+        <f t="shared" si="18"/>
+        <v>0.8</v>
+      </c>
+      <c r="X59">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z59">
+        <f t="shared" si="32"/>
+        <v>5.5128819200000003E-4</v>
+      </c>
+      <c r="AA59">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <f t="shared" si="34"/>
+        <v>4.6280643718399999</v>
+      </c>
+      <c r="AC59">
+        <f t="shared" si="35"/>
+        <v>4.6280643718400001E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:34">
+      <c r="A60" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60">
+        <v>24</v>
+      </c>
+      <c r="D60" t="s">
+        <v>57</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F60">
+        <v>20</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="19"/>
+        <v>0.34</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="20"/>
+        <v>0.19</v>
+      </c>
+      <c r="K60" t="s">
+        <v>56</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <f t="shared" si="23"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="O60">
+        <f t="shared" si="24"/>
+        <v>7</v>
+      </c>
+      <c r="P60">
+        <f t="shared" si="25"/>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="Q60">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <f t="shared" si="27"/>
+        <v>0.24</v>
+      </c>
+      <c r="T60">
+        <f t="shared" si="28"/>
+        <v>0.11</v>
+      </c>
+      <c r="U60">
+        <f t="shared" si="29"/>
+        <v>0.6784</v>
+      </c>
+      <c r="W60">
+        <f t="shared" si="18"/>
+        <v>0.78</v>
+      </c>
+      <c r="X60">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <f t="shared" si="31"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="Z60">
+        <f t="shared" si="32"/>
+        <v>2.0597580800000003E-4</v>
+      </c>
+      <c r="AA60">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AB60">
+        <f t="shared" si="34"/>
+        <v>1.8043480780800005</v>
+      </c>
+      <c r="AC60">
+        <f t="shared" si="35"/>
+        <v>1.8043480780800005E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:34">
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" spans="1:34">
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" spans="1:34">
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:34">
+      <c r="E64" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/packages/calculators/src/modules/test/4.7-other-livestock-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.7-other-livestock-manure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18BA794-E060-B44A-AED9-B7FC81B81AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89528F04-08AE-A242-B0AD-391DD2A41BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="-2420" windowWidth="28800" windowHeight="25760" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="51220" yWindow="-3180" windowWidth="28800" windowHeight="25760" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="4.7.1.1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="109">
   <si>
     <t>Livestock type</t>
   </si>
@@ -446,6 +446,15 @@
   </si>
   <si>
     <t>Boreal dry</t>
+  </si>
+  <si>
+    <t>En2o,ad</t>
+  </si>
+  <si>
+    <t>Mvol</t>
+  </si>
+  <si>
+    <t>expression</t>
   </si>
 </sst>
 </file>
@@ -882,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A5655F-5BFE-554E-A3D3-9DFA9517010F}">
-  <dimension ref="A1:AO64"/>
+  <dimension ref="A1:AP64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="3" customWidth="1"/>
@@ -910,19 +919,19 @@
     <col min="28" max="28" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="12.1640625" customWidth="1"/>
-    <col min="32" max="33" width="16.5" customWidth="1"/>
-    <col min="35" max="36" width="16" customWidth="1"/>
-    <col min="38" max="38" width="36" customWidth="1"/>
-    <col min="40" max="40" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="16.5" customWidth="1"/>
+    <col min="36" max="37" width="16" customWidth="1"/>
+    <col min="39" max="39" width="36" customWidth="1"/>
+    <col min="41" max="41" width="35.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41">
-      <c r="AJ1" s="1"/>
-    </row>
-    <row r="2" spans="1:41">
-      <c r="AJ2" s="1"/>
-    </row>
-    <row r="3" spans="1:41">
+    <row r="1" spans="1:42">
+      <c r="AK1" s="1"/>
+    </row>
+    <row r="2" spans="1:42">
+      <c r="AK2" s="1"/>
+    </row>
+    <row r="3" spans="1:42">
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -934,20 +943,20 @@
       </c>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
-      <c r="AI3" t="s">
+      <c r="AJ3" t="s">
         <v>48</v>
       </c>
-      <c r="AJ3">
+      <c r="AK3">
         <v>0.21</v>
       </c>
-      <c r="AL3" s="7" t="s">
+      <c r="AM3" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AM3">
+      <c r="AN3">
         <v>0.24</v>
       </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:42">
       <c r="C4">
         <v>1776</v>
       </c>
@@ -1005,21 +1014,24 @@
       <c r="AA4" t="s">
         <v>53</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AG4">
+        <v>1753</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>38</v>
       </c>
-      <c r="AJ4">
+      <c r="AK4">
         <f>44/28</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>50</v>
       </c>
-      <c r="AM4">
+      <c r="AN4">
         <v>0.11</v>
       </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:42">
       <c r="C5" t="s">
         <v>88</v>
       </c>
@@ -1071,61 +1083,64 @@
       <c r="Z5" t="s">
         <v>72</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AG5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ5" t="s">
         <v>39</v>
       </c>
-      <c r="AJ5">
+      <c r="AK5">
         <v>0.6784</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AM5" t="s">
         <v>61</v>
       </c>
-      <c r="AM5">
+      <c r="AN5">
         <v>0.19</v>
       </c>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:42">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
-      <c r="AH6" t="s">
+      <c r="AI6" t="s">
         <v>40</v>
       </c>
-      <c r="AI6" t="s">
+      <c r="AJ6" t="s">
         <v>41</v>
       </c>
-      <c r="AJ6">
+      <c r="AK6">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:41">
-      <c r="AI7" t="s">
+    <row r="7" spans="1:42">
+      <c r="AJ7" t="s">
         <v>42</v>
       </c>
-      <c r="AJ7">
+      <c r="AK7">
         <v>2E-3</v>
       </c>
-      <c r="AL7" s="2"/>
       <c r="AM7" s="2"/>
-    </row>
-    <row r="8" spans="1:41">
-      <c r="AL8" s="2"/>
+      <c r="AN7" s="2"/>
+    </row>
+    <row r="8" spans="1:42">
       <c r="AM8" s="2"/>
-    </row>
-    <row r="9" spans="1:41">
+      <c r="AN8" s="2"/>
+    </row>
+    <row r="9" spans="1:42">
       <c r="A9" s="4"/>
       <c r="C9" t="s">
         <v>51</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AK9" t="s">
         <v>36</v>
       </c>
-      <c r="AL9" s="2"/>
       <c r="AM9" s="2"/>
-      <c r="AO9" t="s">
+      <c r="AN9" s="2"/>
+      <c r="AP9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="17">
+    <row r="10" spans="1:42" ht="17">
       <c r="A10" s="5" t="s">
         <v>0</v>
       </c>
@@ -1222,26 +1237,31 @@
       <c r="AF10" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="AG10" s="11"/>
-      <c r="AI10" t="s">
-        <v>35</v>
+      <c r="AG10" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH10" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="AJ10" t="s">
         <v>35</v>
       </c>
       <c r="AK10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL10" t="s">
         <v>44</v>
       </c>
-      <c r="AL10" s="2"/>
       <c r="AM10" s="2"/>
-      <c r="AN10" s="2" t="s">
+      <c r="AN10" s="2"/>
+      <c r="AO10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AO10" s="2">
+      <c r="AP10" s="2">
         <v>5.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:41" ht="17">
+    <row r="11" spans="1:42" ht="17">
       <c r="A11" s="3" t="s">
         <v>3</v>
       </c>
@@ -1261,18 +1281,18 @@
         <v>96</v>
       </c>
       <c r="H11" t="str">
-        <f>VLOOKUP(G11,$AN$31:$AO$40,2,FALSE)</f>
+        <f>VLOOKUP(G11,$AO$31:$AP$40,2,FALSE)</f>
         <v>wet</v>
       </c>
       <c r="I11" t="s">
         <v>67</v>
       </c>
       <c r="J11">
-        <f>VLOOKUP(A11, $AI$11:$AJ$18,2,FALSE)</f>
+        <f>VLOOKUP(A11, $AJ$11:$AK$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K11">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L11" t="s">
@@ -1287,39 +1307,43 @@
         <v>1</v>
       </c>
       <c r="O11">
-        <f>$AJ$4</f>
+        <f>$AK$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P11">
-        <f>VLOOKUP(A11, $AI$11:$AK$18,3,FALSE)</f>
+        <f>VLOOKUP(A11, $AJ$11:$AL$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q11">
-        <f>VLOOKUP(E11,$AN$10:$AO$22,2,FALSE)</f>
+        <f>VLOOKUP(E11,$AO$10:$AP$22,2,FALSE)</f>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R11">
         <f>IF(D11="yes", 1, 0)</f>
         <v>1</v>
       </c>
+      <c r="S11">
+        <f>$AK$3</f>
+        <v>0.21</v>
+      </c>
       <c r="T11">
-        <f>$AM$3</f>
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
       <c r="U11">
-        <f>$AM$4</f>
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
       <c r="V11">
-        <f>$AJ$5</f>
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
       <c r="W11">
-        <f>IF(H11="wet",$AJ$6,$AJ$7)</f>
+        <f>IF(H11="wet",$AK$6,$AK$7)</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X11">
-        <f>VLOOKUP(I11,$AI$23:$AJ$30,2,FALSE)</f>
+        <f>VLOOKUP(I11,$AJ$23:$AK$30,2,FALSE)</f>
         <v>0.78</v>
       </c>
       <c r="Y11">
@@ -1327,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA11">
@@ -1354,25 +1378,33 @@
         <f>AE11*W11*O11*10^-3</f>
         <v>0.6796821428571429</v>
       </c>
-      <c r="AI11" s="2" t="s">
+      <c r="AG11">
+        <f>AE11*S11</f>
+        <v>15138.375</v>
+      </c>
+      <c r="AH11">
+        <f>AG11*Q11*O11*10^-3</f>
+        <v>0.16652212499999999</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="AJ11" s="2">
+      <c r="AK11" s="2">
         <v>2.73</v>
       </c>
-      <c r="AK11" s="2">
+      <c r="AL11" s="2">
         <v>39.5</v>
       </c>
-      <c r="AL11" s="2"/>
       <c r="AM11" s="2"/>
-      <c r="AN11" s="2" t="s">
+      <c r="AN11" s="2"/>
+      <c r="AO11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AO11" s="2">
+      <c r="AP11" s="2">
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="17">
+    <row r="12" spans="1:42" ht="17">
       <c r="A12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1392,18 +1424,18 @@
         <v>97</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" ref="H12:H30" si="0">VLOOKUP(G12,$AN$31:$AO$40,2,FALSE)</f>
+        <f t="shared" ref="H12:H30" si="0">VLOOKUP(G12,$AO$31:$AP$40,2,FALSE)</f>
         <v>wet</v>
       </c>
       <c r="I12" t="s">
         <v>67</v>
       </c>
       <c r="J12">
-        <f>VLOOKUP(A12, $AI$11:$AJ$18,2,FALSE)</f>
+        <f>VLOOKUP(A12, $AJ$11:$AK$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K12">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L12" t="s">
@@ -1418,39 +1450,43 @@
         <v>1</v>
       </c>
       <c r="O12">
-        <f>$AJ$4</f>
+        <f>$AK$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P12">
-        <f>VLOOKUP(A12, $AI$11:$AK$18,3,FALSE)</f>
+        <f>VLOOKUP(A12, $AJ$11:$AL$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q12">
-        <f>VLOOKUP(E12,$AN$10:$AO$22,2,FALSE)</f>
+        <f>VLOOKUP(E12,$AO$10:$AP$22,2,FALSE)</f>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R12">
         <f>IF(D12="yes", 1, 0)</f>
         <v>0</v>
       </c>
+      <c r="S12">
+        <f t="shared" ref="S12:S30" si="1">$AK$3</f>
+        <v>0.21</v>
+      </c>
       <c r="T12">
-        <f>$AM$3</f>
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
       <c r="U12">
-        <f>$AM$4</f>
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
       <c r="V12">
-        <f>$AJ$5</f>
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
       <c r="W12">
-        <f t="shared" ref="W12:W30" si="1">IF(H12="wet",$AJ$6,$AJ$7)</f>
+        <f t="shared" ref="W12:W30" si="2">IF(H12="wet",$AK$6,$AK$7)</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X12">
-        <f>VLOOKUP(I12,$AI$23:$AJ$30,2,FALSE)</f>
+        <f>VLOOKUP(I12,$AJ$23:$AK$30,2,FALSE)</f>
         <v>0.78</v>
       </c>
       <c r="Y12">
@@ -1458,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA12">
@@ -1478,32 +1514,40 @@
         <v>3.6219634214400007E-3</v>
       </c>
       <c r="AE12" s="11">
-        <f t="shared" ref="AE12:AE30" si="2">C12*P12*365</f>
+        <f t="shared" ref="AE12:AE30" si="3">C12*P12*365</f>
         <v>86505</v>
       </c>
       <c r="AF12">
-        <f t="shared" ref="AF12:AF30" si="3">AE12*W12*O12*10^-3</f>
+        <f t="shared" ref="AF12:AF30" si="4">AE12*W12*O12*10^-3</f>
         <v>0.81561857142857142</v>
       </c>
-      <c r="AI12" s="2" t="s">
+      <c r="AG12">
+        <f t="shared" ref="AG12:AG30" si="5">AE12*S12</f>
+        <v>18166.05</v>
+      </c>
+      <c r="AH12">
+        <f t="shared" ref="AH12:AH30" si="6">AG12*Q12*O12*10^-3</f>
+        <v>0.19982654999999999</v>
+      </c>
+      <c r="AJ12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ12" s="2">
+      <c r="AK12" s="2">
         <v>0.34</v>
       </c>
-      <c r="AK12" s="2">
+      <c r="AL12" s="2">
         <v>7</v>
       </c>
-      <c r="AL12" s="2"/>
       <c r="AM12" s="2"/>
-      <c r="AN12" s="2" t="s">
+      <c r="AN12" s="2"/>
+      <c r="AO12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AO12" s="2">
+      <c r="AP12" s="2">
         <v>1.8E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="17">
+    <row r="13" spans="1:42" ht="17">
       <c r="A13" s="3" t="s">
         <v>3</v>
       </c>
@@ -1530,111 +1574,123 @@
         <v>67</v>
       </c>
       <c r="J13">
-        <f t="shared" ref="J13:J30" si="4">VLOOKUP(A13, $AI$11:$AJ$18,2,FALSE)</f>
+        <f t="shared" ref="J13:J30" si="7">VLOOKUP(A13, $AJ$11:$AK$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K13">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L13" t="s">
         <v>57</v>
       </c>
       <c r="M13">
-        <f t="shared" ref="M13:M30" si="5">1-N13</f>
+        <f t="shared" ref="M13:M30" si="8">1-N13</f>
         <v>0</v>
       </c>
       <c r="N13">
-        <f t="shared" ref="N13:N30" si="6">IF(L13="yes", 1, 0.95)</f>
+        <f t="shared" ref="N13:N30" si="9">IF(L13="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O13">
-        <f>$AJ$4</f>
+        <f>$AK$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P13">
-        <f t="shared" ref="P13:P30" si="7">VLOOKUP(A13, $AI$11:$AK$18,3,FALSE)</f>
+        <f t="shared" ref="P13:P30" si="10">VLOOKUP(A13, $AJ$11:$AL$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q13">
-        <f t="shared" ref="Q13:Q30" si="8">VLOOKUP(E13,$AN$10:$AO$22,2,FALSE)</f>
+        <f t="shared" ref="Q13:Q30" si="11">VLOOKUP(E13,$AO$10:$AP$22,2,FALSE)</f>
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="R13">
-        <f t="shared" ref="R13:R30" si="9">IF(D13="yes", 1, 0)</f>
+        <f t="shared" ref="R13:R30" si="12">IF(D13="yes", 1, 0)</f>
         <v>1</v>
       </c>
+      <c r="S13">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
       <c r="T13">
-        <f>$AM$3</f>
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
       <c r="U13">
-        <f>$AM$4</f>
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
       <c r="V13">
-        <f>$AJ$5</f>
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
       <c r="W13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X13">
-        <f t="shared" ref="X13:X30" si="10">VLOOKUP(I13,$AI$23:$AJ$30,2,FALSE)</f>
+        <f t="shared" ref="X13:X30" si="13">VLOOKUP(I13,$AJ$23:$AK$30,2,FALSE)</f>
         <v>0.78</v>
       </c>
       <c r="Y13">
-        <f t="shared" ref="Y13:Y30" si="11">J13*K13*M13*X13*V13</f>
+        <f t="shared" ref="Y13:Y30" si="14">J13*K13*M13*X13*V13</f>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA13">
-        <f t="shared" ref="AA13:AA30" si="12">J13*K13*N13*Z13*V13</f>
+        <f t="shared" ref="AA13:AA30" si="15">J13*K13*N13*Z13*V13</f>
         <v>1.6538645760000002E-3</v>
       </c>
       <c r="AB13">
-        <f t="shared" ref="AB13:AB30" si="13">C13*Y13*365</f>
+        <f t="shared" ref="AB13:AB30" si="16">C13*Y13*365</f>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f t="shared" ref="AC13:AC30" si="14">C13*AA13*365</f>
+        <f t="shared" ref="AC13:AC30" si="17">C13*AA13*365</f>
         <v>4.22562399168</v>
       </c>
       <c r="AD13">
-        <f t="shared" ref="AD13:AD30" si="15">(AB13+AC13)*10^-3</f>
+        <f t="shared" ref="AD13:AD30" si="18">(AB13+AC13)*10^-3</f>
         <v>4.2256239916799998E-3</v>
       </c>
       <c r="AE13" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100922.5</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.95155499999999993</v>
       </c>
-      <c r="AI13" s="2" t="s">
+      <c r="AG13">
+        <f t="shared" si="5"/>
+        <v>21193.724999999999</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="6"/>
+        <v>0.19649610749999999</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AJ13" s="2">
+      <c r="AK13" s="2">
         <v>0.91</v>
       </c>
-      <c r="AK13" s="2">
+      <c r="AL13" s="2">
         <v>13.2</v>
       </c>
-      <c r="AL13" s="2"/>
       <c r="AM13" s="2"/>
-      <c r="AN13" s="2" t="s">
+      <c r="AN13" s="2"/>
+      <c r="AO13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AO13" s="2">
+      <c r="AP13" s="2">
         <v>2.8999999999999998E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:41" ht="17">
+    <row r="14" spans="1:42" ht="17">
       <c r="A14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1661,111 +1717,123 @@
         <v>67</v>
       </c>
       <c r="J14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>2.73</v>
       </c>
       <c r="K14">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L14" t="s">
         <v>57</v>
       </c>
       <c r="M14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="10"/>
+        <v>39.5</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="11"/>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
+      <c r="T14">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U14">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V14">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="2"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X14">
+        <f t="shared" si="13"/>
+        <v>0.78</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="15"/>
+        <v>1.6538645760000002E-3</v>
+      </c>
+      <c r="AB14">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="17"/>
+        <v>4.8292845619200007</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="18"/>
+        <v>4.8292845619200006E-3</v>
+      </c>
+      <c r="AE14" s="11">
+        <f t="shared" si="3"/>
+        <v>115340</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" si="4"/>
+        <v>1.0874914285714286</v>
+      </c>
+      <c r="AG14">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N14">
+        <v>24221.399999999998</v>
+      </c>
+      <c r="AH14">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P14">
-        <f t="shared" si="7"/>
+        <v>0.26643539999999999</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK14" s="2">
+        <v>2.73</v>
+      </c>
+      <c r="AL14" s="2">
         <v>39.5</v>
       </c>
-      <c r="Q14">
-        <f t="shared" si="8"/>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U14">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V14">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W14">
-        <f t="shared" si="1"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X14">
-        <f t="shared" si="10"/>
-        <v>0.78</v>
-      </c>
-      <c r="Y14">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA14">
-        <f t="shared" si="12"/>
-        <v>1.6538645760000002E-3</v>
-      </c>
-      <c r="AB14">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <f t="shared" si="14"/>
-        <v>4.8292845619200007</v>
-      </c>
-      <c r="AD14">
-        <f t="shared" si="15"/>
-        <v>4.8292845619200006E-3</v>
-      </c>
-      <c r="AE14" s="11">
-        <f t="shared" si="2"/>
-        <v>115340</v>
-      </c>
-      <c r="AF14">
-        <f t="shared" si="3"/>
-        <v>1.0874914285714286</v>
-      </c>
-      <c r="AI14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AJ14" s="2">
-        <v>2.73</v>
-      </c>
-      <c r="AK14" s="2">
-        <v>39.5</v>
-      </c>
-      <c r="AL14" s="2"/>
       <c r="AM14" s="2"/>
-      <c r="AN14" s="2" t="s">
+      <c r="AN14" s="2"/>
+      <c r="AO14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AO14" s="2">
+      <c r="AP14" s="2">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:41" ht="17">
+    <row r="15" spans="1:42" ht="17">
       <c r="A15" s="3" t="s">
         <v>25</v>
       </c>
@@ -1792,111 +1860,123 @@
         <v>67</v>
       </c>
       <c r="J15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.34</v>
       </c>
       <c r="K15">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L15" t="s">
         <v>57</v>
       </c>
       <c r="M15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N15">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="8"/>
-        <v>1.8E-3</v>
-      </c>
-      <c r="R15">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
+      <c r="O15">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="11"/>
+        <v>1.8E-3</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
       <c r="T15">
-        <f>$AM$3</f>
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
       <c r="U15">
-        <f>$AM$4</f>
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
       <c r="V15">
-        <f>$AJ$5</f>
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
       <c r="W15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.78</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0.67663052928000011</v>
       </c>
       <c r="AD15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>6.7663052928000015E-4</v>
       </c>
       <c r="AE15" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>22995</v>
       </c>
       <c r="AF15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.21681</v>
       </c>
-      <c r="AI15" s="2" t="s">
+      <c r="AG15">
+        <f t="shared" si="5"/>
+        <v>4828.95</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="6"/>
+        <v>1.3659029999999999E-2</v>
+      </c>
+      <c r="AJ15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AJ15" s="2">
+      <c r="AK15" s="2">
         <v>0.34</v>
       </c>
-      <c r="AK15" s="2">
+      <c r="AL15" s="2">
         <v>7</v>
       </c>
-      <c r="AL15" s="2"/>
       <c r="AM15" s="2"/>
-      <c r="AN15" s="2" t="s">
+      <c r="AN15" s="2"/>
+      <c r="AO15" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AO15" s="2">
+      <c r="AP15" s="2">
         <v>1.9900000000000001E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:41" ht="17">
+    <row r="16" spans="1:42" ht="17">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -1923,111 +2003,123 @@
         <v>28</v>
       </c>
       <c r="J16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.34</v>
       </c>
       <c r="K16">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L16" t="s">
         <v>57</v>
       </c>
       <c r="M16">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="11"/>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
+      <c r="T16">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U16">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V16">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="2"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X16">
+        <f t="shared" si="13"/>
+        <v>0.71</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA16">
+        <f t="shared" si="15"/>
+        <v>2.0597580800000003E-4</v>
+      </c>
+      <c r="AB16">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="17"/>
+        <v>0.75181169920000002</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="18"/>
+        <v>7.518116992E-4</v>
+      </c>
+      <c r="AE16" s="11">
+        <f t="shared" si="3"/>
+        <v>25550</v>
+      </c>
+      <c r="AF16">
+        <f t="shared" si="4"/>
+        <v>0.2409</v>
+      </c>
+      <c r="AG16">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N16">
+        <v>5365.5</v>
+      </c>
+      <c r="AH16">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="O16">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P16">
-        <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="8"/>
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="R16">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U16">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V16">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W16">
-        <f t="shared" si="1"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X16">
-        <f t="shared" si="10"/>
-        <v>0.71</v>
-      </c>
-      <c r="Y16">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA16">
-        <f t="shared" si="12"/>
-        <v>2.0597580800000003E-4</v>
-      </c>
-      <c r="AB16">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <f t="shared" si="14"/>
-        <v>0.75181169920000002</v>
-      </c>
-      <c r="AD16">
-        <f t="shared" si="15"/>
-        <v>7.518116992E-4</v>
-      </c>
-      <c r="AE16" s="11">
-        <f t="shared" si="2"/>
-        <v>25550</v>
-      </c>
-      <c r="AF16">
-        <f t="shared" si="3"/>
-        <v>0.2409</v>
-      </c>
-      <c r="AI16" s="2" t="s">
+        <v>2.4451349999999997E-2</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AJ16" s="2">
+      <c r="AK16" s="2">
         <v>2.73</v>
       </c>
-      <c r="AK16" s="2">
+      <c r="AL16" s="2">
         <v>39.5</v>
       </c>
-      <c r="AL16" s="2"/>
       <c r="AM16" s="2"/>
-      <c r="AN16" s="2" t="s">
+      <c r="AN16" s="2"/>
+      <c r="AO16" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AO16" s="2">
+      <c r="AP16" s="2">
         <v>5.3E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:41" ht="17">
+    <row r="17" spans="1:42" ht="17">
       <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
@@ -2054,111 +2146,123 @@
         <v>65</v>
       </c>
       <c r="J17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.34</v>
       </c>
       <c r="K17">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L17" t="s">
         <v>57</v>
       </c>
       <c r="M17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N17">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="O17">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P17">
-        <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="Q17">
-        <f t="shared" si="8"/>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="R17">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
+      <c r="O17">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="11"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
       <c r="T17">
-        <f>$AM$3</f>
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
       <c r="U17">
-        <f>$AM$4</f>
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
       <c r="V17">
-        <f>$AJ$5</f>
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
       <c r="W17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
       <c r="X17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.75</v>
       </c>
       <c r="Y17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0.82699286912000003</v>
       </c>
       <c r="AD17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>8.2699286912000006E-4</v>
       </c>
       <c r="AE17" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>28105</v>
       </c>
       <c r="AF17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.8330000000000006E-2</v>
       </c>
-      <c r="AI17" s="2" t="s">
+      <c r="AG17">
+        <f t="shared" si="5"/>
+        <v>5902.05</v>
+      </c>
+      <c r="AH17">
+        <f t="shared" si="6"/>
+        <v>7.4197199999999991E-2</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AJ17" s="2">
+      <c r="AK17" s="2">
         <v>0.91</v>
       </c>
-      <c r="AK17" s="2">
+      <c r="AL17" s="2">
         <v>13.2</v>
       </c>
-      <c r="AL17" s="2"/>
       <c r="AM17" s="2"/>
-      <c r="AN17" s="2" t="s">
+      <c r="AN17" s="2"/>
+      <c r="AO17" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AO17" s="2">
+      <c r="AP17" s="2">
         <v>6.4000000000000003E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:41" ht="17">
+    <row r="18" spans="1:42" ht="17">
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
@@ -2172,7 +2276,7 @@
         <v>58</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s">
         <v>103</v>
@@ -2185,111 +2289,123 @@
         <v>66</v>
       </c>
       <c r="J18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.34</v>
       </c>
       <c r="K18">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L18" t="s">
         <v>57</v>
       </c>
       <c r="M18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P18">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="11"/>
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
+      <c r="T18">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U18">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V18">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="2"/>
+        <v>2E-3</v>
+      </c>
+      <c r="X18">
+        <f t="shared" si="13"/>
+        <v>0.8</v>
+      </c>
+      <c r="Y18">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA18">
+        <f t="shared" si="15"/>
+        <v>2.0597580800000003E-4</v>
+      </c>
+      <c r="AB18">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <f t="shared" si="17"/>
+        <v>0.90217403904000026</v>
+      </c>
+      <c r="AD18">
+        <f t="shared" si="18"/>
+        <v>9.0217403904000024E-4</v>
+      </c>
+      <c r="AE18" s="11">
+        <f t="shared" si="3"/>
+        <v>30660</v>
+      </c>
+      <c r="AF18">
+        <f t="shared" si="4"/>
+        <v>9.6360000000000001E-2</v>
+      </c>
+      <c r="AG18">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N18">
+        <v>6438.5999999999995</v>
+      </c>
+      <c r="AH18">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="O18">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P18">
-        <f t="shared" si="7"/>
+        <v>5.9695019999999994E-2</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK18" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="AL18" s="2">
         <v>7</v>
       </c>
-      <c r="Q18">
-        <f t="shared" si="8"/>
-        <v>1.9900000000000001E-2</v>
-      </c>
-      <c r="R18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U18">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V18">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W18">
-        <f t="shared" si="1"/>
-        <v>2E-3</v>
-      </c>
-      <c r="X18">
-        <f t="shared" si="10"/>
-        <v>0.8</v>
-      </c>
-      <c r="Y18">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA18">
-        <f t="shared" si="12"/>
-        <v>2.0597580800000003E-4</v>
-      </c>
-      <c r="AB18">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AC18">
-        <f t="shared" si="14"/>
-        <v>0.90217403904000026</v>
-      </c>
-      <c r="AD18">
-        <f t="shared" si="15"/>
-        <v>9.0217403904000024E-4</v>
-      </c>
-      <c r="AE18" s="11">
-        <f t="shared" si="2"/>
-        <v>30660</v>
-      </c>
-      <c r="AF18">
-        <f t="shared" si="3"/>
-        <v>9.6360000000000001E-2</v>
-      </c>
-      <c r="AI18" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ18" s="2">
-        <v>0.34</v>
-      </c>
-      <c r="AK18" s="2">
-        <v>7</v>
-      </c>
-      <c r="AL18" s="2"/>
-      <c r="AM18" s="10"/>
-      <c r="AN18" s="2" t="s">
+      <c r="AM18" s="2"/>
+      <c r="AN18" s="10"/>
+      <c r="AO18" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AO18" s="2">
+      <c r="AP18" s="2">
         <v>2.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:41" ht="17">
+    <row r="19" spans="1:42" ht="17">
       <c r="A19" s="3" t="s">
         <v>25</v>
       </c>
@@ -2303,7 +2419,7 @@
         <v>57</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s">
         <v>104</v>
@@ -2316,102 +2432,114 @@
         <v>67</v>
       </c>
       <c r="J19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.34</v>
       </c>
       <c r="K19">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L19" t="s">
         <v>57</v>
       </c>
       <c r="M19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N19">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P19">
-        <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" si="8"/>
-        <v>5.3E-3</v>
-      </c>
-      <c r="R19">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
+      <c r="O19">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="11"/>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
       <c r="T19">
-        <f>$AM$3</f>
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
       <c r="U19">
-        <f>$AM$4</f>
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
       <c r="V19">
-        <f>$AJ$5</f>
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
       <c r="W19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
       <c r="X19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.78</v>
       </c>
       <c r="Y19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z19">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AC19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0.97735520896000017</v>
       </c>
       <c r="AD19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>9.7735520896000019E-4</v>
       </c>
       <c r="AE19" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>33215</v>
       </c>
       <c r="AF19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.10439000000000001</v>
       </c>
-      <c r="AL19" s="2"/>
-      <c r="AM19" s="10"/>
-      <c r="AN19" s="2" t="s">
+      <c r="AG19">
+        <f t="shared" si="5"/>
+        <v>6975.15</v>
+      </c>
+      <c r="AH19">
+        <f t="shared" si="6"/>
+        <v>7.6726649999999993E-2</v>
+      </c>
+      <c r="AM19" s="2"/>
+      <c r="AN19" s="10"/>
+      <c r="AO19" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="AO19" s="2">
+      <c r="AP19" s="2">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:41" ht="17">
+    <row r="20" spans="1:42" ht="17">
       <c r="A20" s="3" t="s">
         <v>25</v>
       </c>
@@ -2425,7 +2553,7 @@
         <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s">
         <v>105</v>
@@ -2438,102 +2566,114 @@
         <v>68</v>
       </c>
       <c r="J20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.34</v>
       </c>
       <c r="K20">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L20" t="s">
         <v>57</v>
       </c>
       <c r="M20">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="11"/>
+        <v>1.8E-3</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
+      <c r="T20">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U20">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V20">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="2"/>
+        <v>2E-3</v>
+      </c>
+      <c r="X20">
+        <f t="shared" si="13"/>
+        <v>0.74</v>
+      </c>
+      <c r="Y20">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA20">
+        <f t="shared" si="15"/>
+        <v>2.0597580800000003E-4</v>
+      </c>
+      <c r="AB20">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <f t="shared" si="17"/>
+        <v>1.0525363788800002</v>
+      </c>
+      <c r="AD20">
+        <f t="shared" si="18"/>
+        <v>1.0525363788800003E-3</v>
+      </c>
+      <c r="AE20" s="11">
+        <f t="shared" si="3"/>
+        <v>35770</v>
+      </c>
+      <c r="AF20">
+        <f t="shared" si="4"/>
+        <v>0.11242000000000001</v>
+      </c>
+      <c r="AG20">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N20">
+        <v>7511.7</v>
+      </c>
+      <c r="AH20">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="O20">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="8"/>
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U20">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V20">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W20">
-        <f t="shared" si="1"/>
-        <v>2E-3</v>
-      </c>
-      <c r="X20">
-        <f t="shared" si="10"/>
-        <v>0.74</v>
-      </c>
-      <c r="Y20">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA20">
-        <f t="shared" si="12"/>
-        <v>2.0597580800000003E-4</v>
-      </c>
-      <c r="AB20">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <f t="shared" si="14"/>
-        <v>1.0525363788800002</v>
-      </c>
-      <c r="AD20">
-        <f t="shared" si="15"/>
-        <v>1.0525363788800003E-3</v>
-      </c>
-      <c r="AE20" s="11">
-        <f t="shared" si="2"/>
-        <v>35770</v>
-      </c>
-      <c r="AF20">
-        <f t="shared" si="3"/>
-        <v>0.11242000000000001</v>
-      </c>
-      <c r="AL20" s="2"/>
+        <v>2.1247379999999996E-2</v>
+      </c>
       <c r="AM20" s="2"/>
-      <c r="AN20" s="2" t="s">
+      <c r="AN20" s="2"/>
+      <c r="AO20" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AO20" s="2">
+      <c r="AP20" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:41" ht="17">
+    <row r="21" spans="1:42" ht="17">
       <c r="A21" s="3" t="s">
         <v>25</v>
       </c>
@@ -2547,7 +2687,7 @@
         <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s">
         <v>96</v>
@@ -2560,108 +2700,120 @@
         <v>69</v>
       </c>
       <c r="J21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.34</v>
       </c>
       <c r="K21">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L21" t="s">
         <v>57</v>
       </c>
       <c r="M21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N21">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="O21">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="8"/>
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="R21">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
+      <c r="O21">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="11"/>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
       <c r="T21">
-        <f>$AM$3</f>
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
       <c r="U21">
-        <f>$AM$4</f>
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
       <c r="V21">
-        <f>$AJ$5</f>
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
       <c r="W21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="Y21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z21">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AC21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>1.1277175488000002</v>
       </c>
       <c r="AD21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1.1277175488000003E-3</v>
       </c>
       <c r="AE21" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>38325</v>
       </c>
       <c r="AF21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.36135</v>
       </c>
-      <c r="AI21" s="2" t="s">
+      <c r="AG21">
+        <f t="shared" si="5"/>
+        <v>8048.25</v>
+      </c>
+      <c r="AH21">
+        <f t="shared" si="6"/>
+        <v>3.6677024999999995E-2</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AJ21" t="s">
+      <c r="AK21" t="s">
         <v>29</v>
       </c>
-      <c r="AL21" s="2"/>
       <c r="AM21" s="2"/>
-      <c r="AN21" s="2" t="s">
+      <c r="AN21" s="2"/>
+      <c r="AO21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AO21" s="2">
+      <c r="AP21" s="2">
         <v>2.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:41" ht="17">
+    <row r="22" spans="1:42" ht="17">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -2675,7 +2827,7 @@
         <v>58</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s">
         <v>97</v>
@@ -2688,103 +2840,115 @@
         <v>70</v>
       </c>
       <c r="J22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.91</v>
       </c>
       <c r="K22">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L22" t="s">
         <v>57</v>
       </c>
       <c r="M22">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="10"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="11"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
+      <c r="T22">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U22">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V22">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="2"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X22">
+        <f t="shared" si="13"/>
+        <v>0.74</v>
+      </c>
+      <c r="Y22">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA22">
+        <f t="shared" si="15"/>
+        <v>5.5128819200000003E-4</v>
+      </c>
+      <c r="AB22">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <f t="shared" si="17"/>
+        <v>3.21952304128</v>
+      </c>
+      <c r="AD22">
+        <f t="shared" si="18"/>
+        <v>3.21952304128E-3</v>
+      </c>
+      <c r="AE22" s="11">
+        <f t="shared" si="3"/>
+        <v>77088</v>
+      </c>
+      <c r="AF22">
+        <f t="shared" si="4"/>
+        <v>0.7268297142857143</v>
+      </c>
+      <c r="AG22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N22">
+        <v>16188.48</v>
+      </c>
+      <c r="AH22">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="O22">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P22">
-        <f t="shared" si="7"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="8"/>
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U22">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V22">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W22">
-        <f t="shared" si="1"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X22">
-        <f t="shared" si="10"/>
-        <v>0.74</v>
-      </c>
-      <c r="Y22">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA22">
-        <f t="shared" si="12"/>
-        <v>5.5128819200000003E-4</v>
-      </c>
-      <c r="AB22">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <f t="shared" si="14"/>
-        <v>3.21952304128</v>
-      </c>
-      <c r="AD22">
-        <f t="shared" si="15"/>
-        <v>3.21952304128E-3</v>
-      </c>
-      <c r="AE22" s="11">
-        <f t="shared" si="2"/>
-        <v>77088</v>
-      </c>
-      <c r="AF22">
-        <f t="shared" si="3"/>
-        <v>0.7268297142857143</v>
-      </c>
-      <c r="AI22" s="2" t="s">
+        <v>0.20351232</v>
+      </c>
+      <c r="AJ22" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AN22" s="2" t="s">
+      <c r="AO22" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AO22" s="2">
+      <c r="AP22" s="2">
         <v>1.8E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:41" ht="17">
+    <row r="23" spans="1:42" ht="17">
       <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
@@ -2798,7 +2962,7 @@
         <v>57</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s">
         <v>98</v>
@@ -2811,101 +2975,113 @@
         <v>71</v>
       </c>
       <c r="J23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.91</v>
       </c>
       <c r="K23">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L23" t="s">
         <v>57</v>
       </c>
       <c r="M23">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N23">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="O23">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P23">
-        <f t="shared" si="7"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="8"/>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="R23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
+      <c r="O23">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="10"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="11"/>
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
       <c r="T23">
-        <f>$AM$3</f>
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
       <c r="U23">
-        <f>$AM$4</f>
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
       <c r="V23">
-        <f>$AJ$5</f>
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
       <c r="W23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.76</v>
       </c>
       <c r="Y23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z23">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AC23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>3.4207432313599999</v>
       </c>
       <c r="AD23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>3.4207432313600001E-3</v>
       </c>
       <c r="AE23" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>81905.999999999985</v>
       </c>
       <c r="AF23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.77225657142857129</v>
       </c>
-      <c r="AI23" s="2" t="s">
+      <c r="AG23">
+        <f t="shared" si="5"/>
+        <v>17200.259999999995</v>
+      </c>
+      <c r="AH23">
+        <f t="shared" si="6"/>
+        <v>0.15947098199999993</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AJ23" s="2">
+      <c r="AK23" s="2">
         <v>0.71</v>
       </c>
-      <c r="AL23" s="2"/>
-    </row>
-    <row r="24" spans="1:41" ht="17">
+      <c r="AM23" s="2"/>
+    </row>
+    <row r="24" spans="1:42" ht="17">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
@@ -2919,7 +3095,7 @@
         <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s">
         <v>99</v>
@@ -2932,102 +3108,114 @@
         <v>28</v>
       </c>
       <c r="J24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.91</v>
       </c>
       <c r="K24">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L24" t="s">
         <v>58</v>
       </c>
       <c r="M24">
+        <f t="shared" si="8"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="9"/>
+        <v>0.95</v>
+      </c>
+      <c r="O24">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="10"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="11"/>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
+      <c r="T24">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U24">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V24">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W24">
+        <f t="shared" si="2"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X24">
+        <f t="shared" si="13"/>
+        <v>0.71</v>
+      </c>
+      <c r="Y24">
+        <f t="shared" si="14"/>
+        <v>4.1639852800000035E-3</v>
+      </c>
+      <c r="Z24">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA24">
+        <f t="shared" si="15"/>
+        <v>5.2372378239999996E-4</v>
+      </c>
+      <c r="AB24">
+        <f t="shared" si="16"/>
+        <v>27.357383289600023</v>
+      </c>
+      <c r="AC24">
+        <f t="shared" si="17"/>
+        <v>3.4408652503679997</v>
+      </c>
+      <c r="AD24">
+        <f t="shared" si="18"/>
+        <v>3.0798248539968022E-2</v>
+      </c>
+      <c r="AE24" s="11">
+        <f t="shared" si="3"/>
+        <v>86724</v>
+      </c>
+      <c r="AF24">
+        <f t="shared" si="4"/>
+        <v>0.81768342857142862</v>
+      </c>
+      <c r="AG24">
         <f t="shared" si="5"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N24">
+        <v>18212.04</v>
+      </c>
+      <c r="AH24">
         <f t="shared" si="6"/>
-        <v>0.95</v>
-      </c>
-      <c r="O24">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P24">
-        <f t="shared" si="7"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q24">
-        <f t="shared" si="8"/>
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="R24">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U24">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V24">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W24">
-        <f t="shared" si="1"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X24">
-        <f t="shared" si="10"/>
-        <v>0.71</v>
-      </c>
-      <c r="Y24">
-        <f t="shared" si="11"/>
-        <v>4.1639852800000035E-3</v>
-      </c>
-      <c r="Z24">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA24">
-        <f t="shared" si="12"/>
-        <v>5.2372378239999996E-4</v>
-      </c>
-      <c r="AB24">
-        <f t="shared" si="13"/>
-        <v>27.357383289600023</v>
-      </c>
-      <c r="AC24">
-        <f t="shared" si="14"/>
-        <v>3.4408652503679997</v>
-      </c>
-      <c r="AD24">
-        <f t="shared" si="15"/>
-        <v>3.0798248539968022E-2</v>
-      </c>
-      <c r="AE24" s="11">
-        <f t="shared" si="2"/>
-        <v>86724</v>
-      </c>
-      <c r="AF24">
-        <f t="shared" si="3"/>
-        <v>0.81768342857142862</v>
-      </c>
-      <c r="AI24" s="2" t="s">
+        <v>0.20033244000000003</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AJ24" s="2">
+      <c r="AK24" s="2">
         <v>0.75</v>
       </c>
-      <c r="AL24" s="2"/>
       <c r="AM24" s="2"/>
-    </row>
-    <row r="25" spans="1:41" ht="17">
+      <c r="AN24" s="2"/>
+    </row>
+    <row r="25" spans="1:42" ht="17">
       <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
@@ -3041,7 +3229,7 @@
         <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G25" t="s">
         <v>100</v>
@@ -3054,102 +3242,114 @@
         <v>65</v>
       </c>
       <c r="J25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.91</v>
       </c>
       <c r="K25">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L25" t="s">
         <v>58</v>
       </c>
       <c r="M25">
+        <f t="shared" si="8"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="9"/>
+        <v>0.95</v>
+      </c>
+      <c r="O25">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="10"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="11"/>
+        <v>1.8E-3</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
+      <c r="T25">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U25">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V25">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W25">
+        <f t="shared" si="2"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X25">
+        <f t="shared" si="13"/>
+        <v>0.75</v>
+      </c>
+      <c r="Y25">
+        <f t="shared" si="14"/>
+        <v>4.3985760000000039E-3</v>
+      </c>
+      <c r="Z25">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA25">
+        <f t="shared" si="15"/>
+        <v>5.2372378239999996E-4</v>
+      </c>
+      <c r="AB25">
+        <f t="shared" si="16"/>
+        <v>30.504124560000029</v>
+      </c>
+      <c r="AC25">
+        <f t="shared" si="17"/>
+        <v>3.6320244309439995</v>
+      </c>
+      <c r="AD25">
+        <f t="shared" si="18"/>
+        <v>3.4136148990944033E-2</v>
+      </c>
+      <c r="AE25" s="11">
+        <f t="shared" si="3"/>
+        <v>91542</v>
+      </c>
+      <c r="AF25">
+        <f t="shared" si="4"/>
+        <v>0.86311028571428583</v>
+      </c>
+      <c r="AG25">
         <f t="shared" si="5"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N25">
+        <v>19223.82</v>
+      </c>
+      <c r="AH25">
         <f t="shared" si="6"/>
-        <v>0.95</v>
-      </c>
-      <c r="O25">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P25">
-        <f t="shared" si="7"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q25">
-        <f t="shared" si="8"/>
-        <v>1.8E-3</v>
-      </c>
-      <c r="R25">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T25">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U25">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V25">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W25">
-        <f t="shared" si="1"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X25">
-        <f t="shared" si="10"/>
-        <v>0.75</v>
-      </c>
-      <c r="Y25">
-        <f t="shared" si="11"/>
-        <v>4.3985760000000039E-3</v>
-      </c>
-      <c r="Z25">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA25">
-        <f t="shared" si="12"/>
-        <v>5.2372378239999996E-4</v>
-      </c>
-      <c r="AB25">
-        <f t="shared" si="13"/>
-        <v>30.504124560000029</v>
-      </c>
-      <c r="AC25">
-        <f t="shared" si="14"/>
-        <v>3.6320244309439995</v>
-      </c>
-      <c r="AD25">
-        <f t="shared" si="15"/>
-        <v>3.4136148990944033E-2</v>
-      </c>
-      <c r="AE25" s="11">
-        <f t="shared" si="2"/>
-        <v>91542</v>
-      </c>
-      <c r="AF25">
-        <f t="shared" si="3"/>
-        <v>0.86311028571428583</v>
-      </c>
-      <c r="AI25" s="2" t="s">
+        <v>5.4375948E-2</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ25" s="2">
+      <c r="AK25" s="2">
         <v>0.8</v>
       </c>
-      <c r="AL25" s="2"/>
       <c r="AM25" s="2"/>
-    </row>
-    <row r="26" spans="1:41">
+      <c r="AN25" s="2"/>
+    </row>
+    <row r="26" spans="1:42">
       <c r="A26" s="2" t="s">
         <v>19</v>
       </c>
@@ -3163,7 +3363,7 @@
         <v>58</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s">
         <v>101</v>
@@ -3176,102 +3376,114 @@
         <v>66</v>
       </c>
       <c r="J26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>2.73</v>
       </c>
       <c r="K26">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L26" t="s">
         <v>58</v>
       </c>
       <c r="M26">
+        <f t="shared" si="8"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="9"/>
+        <v>0.95</v>
+      </c>
+      <c r="O26">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="10"/>
+        <v>39.5</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="11"/>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
+      <c r="T26">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U26">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V26">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="2"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X26">
+        <f t="shared" si="13"/>
+        <v>0.8</v>
+      </c>
+      <c r="Y26">
+        <f t="shared" si="14"/>
+        <v>1.4075443200000013E-2</v>
+      </c>
+      <c r="Z26">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA26">
+        <f t="shared" si="15"/>
+        <v>1.5711713472E-3</v>
+      </c>
+      <c r="AB26">
+        <f t="shared" si="16"/>
+        <v>102.75073536000009</v>
+      </c>
+      <c r="AC26">
+        <f t="shared" si="17"/>
+        <v>11.46955083456</v>
+      </c>
+      <c r="AD26">
+        <f t="shared" si="18"/>
+        <v>0.11422028619456009</v>
+      </c>
+      <c r="AE26" s="11">
+        <f t="shared" si="3"/>
+        <v>288350</v>
+      </c>
+      <c r="AF26">
+        <f t="shared" si="4"/>
+        <v>2.7187285714285716</v>
+      </c>
+      <c r="AG26">
         <f t="shared" si="5"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N26">
+        <v>60553.5</v>
+      </c>
+      <c r="AH26">
         <f t="shared" si="6"/>
-        <v>0.95</v>
-      </c>
-      <c r="O26">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P26">
-        <f t="shared" si="7"/>
-        <v>39.5</v>
-      </c>
-      <c r="Q26">
-        <f t="shared" si="8"/>
-        <v>5.8999999999999999E-3</v>
-      </c>
-      <c r="R26">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U26">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V26">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W26">
-        <f t="shared" si="1"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X26">
-        <f t="shared" si="10"/>
-        <v>0.8</v>
-      </c>
-      <c r="Y26">
-        <f t="shared" si="11"/>
-        <v>1.4075443200000013E-2</v>
-      </c>
-      <c r="Z26">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA26">
-        <f t="shared" si="12"/>
-        <v>1.5711713472E-3</v>
-      </c>
-      <c r="AB26">
-        <f t="shared" si="13"/>
-        <v>102.75073536000009</v>
-      </c>
-      <c r="AC26">
-        <f t="shared" si="14"/>
-        <v>11.46955083456</v>
-      </c>
-      <c r="AD26">
-        <f t="shared" si="15"/>
-        <v>0.11422028619456009</v>
-      </c>
-      <c r="AE26" s="11">
-        <f t="shared" si="2"/>
-        <v>288350</v>
-      </c>
-      <c r="AF26">
-        <f t="shared" si="3"/>
-        <v>2.7187285714285716</v>
-      </c>
-      <c r="AI26" s="2" t="s">
+        <v>0.27595094999999997</v>
+      </c>
+      <c r="AJ26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AJ26" s="2">
+      <c r="AK26" s="2">
         <v>0.78</v>
       </c>
-      <c r="AL26" s="2"/>
       <c r="AM26" s="2"/>
-    </row>
-    <row r="27" spans="1:41">
+      <c r="AN26" s="2"/>
+    </row>
+    <row r="27" spans="1:42">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -3285,7 +3497,7 @@
         <v>57</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s">
         <v>102</v>
@@ -3298,102 +3510,114 @@
         <v>67</v>
       </c>
       <c r="J27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.34</v>
       </c>
       <c r="K27">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L27" t="s">
         <v>58</v>
       </c>
       <c r="M27">
+        <f t="shared" si="8"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="9"/>
+        <v>0.95</v>
+      </c>
+      <c r="O27">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="11"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R27">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
+      <c r="T27">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U27">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V27">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W27">
+        <f t="shared" si="2"/>
+        <v>2E-3</v>
+      </c>
+      <c r="X27">
+        <f t="shared" si="13"/>
+        <v>0.78</v>
+      </c>
+      <c r="Y27">
+        <f t="shared" si="14"/>
+        <v>1.709160960000002E-3</v>
+      </c>
+      <c r="Z27">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA27">
+        <f t="shared" si="15"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AB27">
+        <f t="shared" si="16"/>
+        <v>13.100718758400015</v>
+      </c>
+      <c r="AC27">
+        <f t="shared" si="17"/>
+        <v>1.4998643399039999</v>
+      </c>
+      <c r="AD27">
+        <f t="shared" si="18"/>
+        <v>1.4600583098304016E-2</v>
+      </c>
+      <c r="AE27" s="11">
+        <f t="shared" si="3"/>
+        <v>53655</v>
+      </c>
+      <c r="AF27">
+        <f t="shared" si="4"/>
+        <v>0.16863</v>
+      </c>
+      <c r="AG27">
         <f t="shared" si="5"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N27">
+        <v>11267.55</v>
+      </c>
+      <c r="AH27">
         <f t="shared" si="6"/>
-        <v>0.95</v>
-      </c>
-      <c r="O27">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P27">
-        <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="Q27">
-        <f t="shared" si="8"/>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="R27">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T27">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U27">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V27">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W27">
-        <f t="shared" si="1"/>
-        <v>2E-3</v>
-      </c>
-      <c r="X27">
-        <f t="shared" si="10"/>
-        <v>0.78</v>
-      </c>
-      <c r="Y27">
-        <f t="shared" si="11"/>
-        <v>1.709160960000002E-3</v>
-      </c>
-      <c r="Z27">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA27">
-        <f t="shared" si="12"/>
-        <v>1.9567701760000002E-4</v>
-      </c>
-      <c r="AB27">
-        <f t="shared" si="13"/>
-        <v>13.100718758400015</v>
-      </c>
-      <c r="AC27">
-        <f t="shared" si="14"/>
-        <v>1.4998643399039999</v>
-      </c>
-      <c r="AD27">
-        <f t="shared" si="15"/>
-        <v>1.4600583098304016E-2</v>
-      </c>
-      <c r="AE27" s="11">
-        <f t="shared" si="2"/>
-        <v>53655</v>
-      </c>
-      <c r="AF27">
-        <f t="shared" si="3"/>
-        <v>0.16863</v>
-      </c>
-      <c r="AI27" s="2" t="s">
+        <v>0.1416492</v>
+      </c>
+      <c r="AJ27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AJ27" s="2">
+      <c r="AK27" s="2">
         <v>0.74</v>
       </c>
-      <c r="AL27" s="2"/>
       <c r="AM27" s="2"/>
-    </row>
-    <row r="28" spans="1:41">
+      <c r="AN27" s="2"/>
+    </row>
+    <row r="28" spans="1:42">
       <c r="A28" s="2" t="s">
         <v>21</v>
       </c>
@@ -3407,7 +3631,7 @@
         <v>58</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
         <v>103</v>
@@ -3420,102 +3644,114 @@
         <v>68</v>
       </c>
       <c r="J28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>2.73</v>
       </c>
       <c r="K28">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L28" t="s">
         <v>58</v>
       </c>
       <c r="M28">
+        <f t="shared" si="8"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="9"/>
+        <v>0.95</v>
+      </c>
+      <c r="O28">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P28">
+        <f t="shared" si="10"/>
+        <v>39.5</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="11"/>
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="R28">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
+      <c r="T28">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U28">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V28">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W28">
+        <f t="shared" si="2"/>
+        <v>2E-3</v>
+      </c>
+      <c r="X28">
+        <f t="shared" si="13"/>
+        <v>0.74</v>
+      </c>
+      <c r="Y28">
+        <f t="shared" si="14"/>
+        <v>1.3019784960000013E-2</v>
+      </c>
+      <c r="Z28">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA28">
+        <f t="shared" si="15"/>
+        <v>1.5711713472E-3</v>
+      </c>
+      <c r="AB28">
+        <f t="shared" si="16"/>
+        <v>104.5488732288001</v>
+      </c>
+      <c r="AC28">
+        <f t="shared" si="17"/>
+        <v>12.616505918016001</v>
+      </c>
+      <c r="AD28">
+        <f t="shared" si="18"/>
+        <v>0.11716537914681611</v>
+      </c>
+      <c r="AE28" s="11">
+        <f t="shared" si="3"/>
+        <v>317185</v>
+      </c>
+      <c r="AF28">
+        <f t="shared" si="4"/>
+        <v>0.99686714285714295</v>
+      </c>
+      <c r="AG28">
         <f t="shared" si="5"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N28">
+        <v>66608.849999999991</v>
+      </c>
+      <c r="AH28">
         <f t="shared" si="6"/>
-        <v>0.95</v>
-      </c>
-      <c r="O28">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P28">
-        <f t="shared" si="7"/>
-        <v>39.5</v>
-      </c>
-      <c r="Q28">
-        <f t="shared" si="8"/>
-        <v>1.8E-3</v>
-      </c>
-      <c r="R28">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U28">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V28">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W28">
-        <f t="shared" si="1"/>
-        <v>2E-3</v>
-      </c>
-      <c r="X28">
-        <f t="shared" si="10"/>
-        <v>0.74</v>
-      </c>
-      <c r="Y28">
-        <f t="shared" si="11"/>
-        <v>1.3019784960000013E-2</v>
-      </c>
-      <c r="Z28">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA28">
-        <f t="shared" si="12"/>
-        <v>1.5711713472E-3</v>
-      </c>
-      <c r="AB28">
-        <f t="shared" si="13"/>
-        <v>104.5488732288001</v>
-      </c>
-      <c r="AC28">
-        <f t="shared" si="14"/>
-        <v>12.616505918016001</v>
-      </c>
-      <c r="AD28">
-        <f t="shared" si="15"/>
-        <v>0.11716537914681611</v>
-      </c>
-      <c r="AE28" s="11">
-        <f t="shared" si="2"/>
-        <v>317185</v>
-      </c>
-      <c r="AF28">
-        <f t="shared" si="3"/>
-        <v>0.99686714285714295</v>
-      </c>
-      <c r="AI28" s="2" t="s">
+        <v>0.61755919499999989</v>
+      </c>
+      <c r="AJ28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AJ28" s="2">
+      <c r="AK28" s="2">
         <v>0.7</v>
       </c>
-      <c r="AL28" s="2"/>
       <c r="AM28" s="2"/>
-    </row>
-    <row r="29" spans="1:41">
+      <c r="AN28" s="2"/>
+    </row>
+    <row r="29" spans="1:42">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
@@ -3529,7 +3765,7 @@
         <v>57</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
         <v>104</v>
@@ -3542,102 +3778,114 @@
         <v>69</v>
       </c>
       <c r="J29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.91</v>
       </c>
       <c r="K29">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L29" t="s">
         <v>58</v>
       </c>
       <c r="M29">
+        <f t="shared" si="8"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="9"/>
+        <v>0.95</v>
+      </c>
+      <c r="O29">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P29">
+        <f t="shared" si="10"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="11"/>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="R29">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="S29">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
+      <c r="T29">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U29">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V29">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="2"/>
+        <v>2E-3</v>
+      </c>
+      <c r="X29">
+        <f t="shared" si="13"/>
+        <v>0.7</v>
+      </c>
+      <c r="Y29">
+        <f t="shared" si="14"/>
+        <v>4.1053376000000034E-3</v>
+      </c>
+      <c r="Z29">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA29">
+        <f t="shared" si="15"/>
+        <v>5.2372378239999996E-4</v>
+      </c>
+      <c r="AB29">
+        <f t="shared" si="16"/>
+        <v>34.464309152000027</v>
+      </c>
+      <c r="AC29">
+        <f t="shared" si="17"/>
+        <v>4.396661153248</v>
+      </c>
+      <c r="AD29">
+        <f t="shared" si="18"/>
+        <v>3.8860970305248023E-2</v>
+      </c>
+      <c r="AE29" s="11">
+        <f t="shared" si="3"/>
+        <v>110813.99999999999</v>
+      </c>
+      <c r="AF29">
+        <f t="shared" si="4"/>
+        <v>0.34827257142857138</v>
+      </c>
+      <c r="AG29">
         <f t="shared" si="5"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N29">
+        <v>23270.939999999995</v>
+      </c>
+      <c r="AH29">
         <f t="shared" si="6"/>
-        <v>0.95</v>
-      </c>
-      <c r="O29">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P29">
-        <f t="shared" si="7"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q29">
-        <f t="shared" si="8"/>
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="R29">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="T29">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U29">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V29">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W29">
-        <f t="shared" si="1"/>
-        <v>2E-3</v>
-      </c>
-      <c r="X29">
-        <f t="shared" si="10"/>
-        <v>0.7</v>
-      </c>
-      <c r="Y29">
-        <f t="shared" si="11"/>
-        <v>4.1053376000000034E-3</v>
-      </c>
-      <c r="Z29">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA29">
-        <f t="shared" si="12"/>
-        <v>5.2372378239999996E-4</v>
-      </c>
-      <c r="AB29">
-        <f t="shared" si="13"/>
-        <v>34.464309152000027</v>
-      </c>
-      <c r="AC29">
-        <f t="shared" si="14"/>
-        <v>4.396661153248</v>
-      </c>
-      <c r="AD29">
-        <f t="shared" si="15"/>
-        <v>3.8860970305248023E-2</v>
-      </c>
-      <c r="AE29" s="11">
-        <f t="shared" si="2"/>
-        <v>110813.99999999999</v>
-      </c>
-      <c r="AF29">
-        <f t="shared" si="3"/>
-        <v>0.34827257142857138</v>
-      </c>
-      <c r="AI29" s="2" t="s">
+        <v>0.25598033999999997</v>
+      </c>
+      <c r="AJ29" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AJ29" s="2">
+      <c r="AK29" s="2">
         <v>0.74</v>
       </c>
-      <c r="AL29" s="2"/>
       <c r="AM29" s="2"/>
-    </row>
-    <row r="30" spans="1:41">
+      <c r="AN29" s="2"/>
+    </row>
+    <row r="30" spans="1:42">
       <c r="A30" s="2" t="s">
         <v>64</v>
       </c>
@@ -3651,7 +3899,7 @@
         <v>58</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s">
         <v>105</v>
@@ -3664,227 +3912,239 @@
         <v>70</v>
       </c>
       <c r="J30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.34</v>
       </c>
       <c r="K30">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L30" t="s">
         <v>58</v>
       </c>
       <c r="M30">
+        <f t="shared" si="8"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="9"/>
+        <v>0.95</v>
+      </c>
+      <c r="O30">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P30">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" si="11"/>
+        <v>1.8E-3</v>
+      </c>
+      <c r="R30">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
+      <c r="T30">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U30">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V30">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="W30">
+        <f t="shared" si="2"/>
+        <v>2E-3</v>
+      </c>
+      <c r="X30">
+        <f t="shared" si="13"/>
+        <v>0.74</v>
+      </c>
+      <c r="Y30">
+        <f t="shared" si="14"/>
+        <v>1.6215116800000018E-3</v>
+      </c>
+      <c r="Z30">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA30">
+        <f t="shared" si="15"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AB30">
+        <f t="shared" si="16"/>
+        <v>14.204442316800016</v>
+      </c>
+      <c r="AC30">
+        <f t="shared" si="17"/>
+        <v>1.7141306741760001</v>
+      </c>
+      <c r="AD30">
+        <f t="shared" si="18"/>
+        <v>1.5918572990976015E-2</v>
+      </c>
+      <c r="AE30" s="11">
+        <f t="shared" si="3"/>
+        <v>61320</v>
+      </c>
+      <c r="AF30">
+        <f t="shared" si="4"/>
+        <v>0.19272</v>
+      </c>
+      <c r="AG30">
         <f t="shared" si="5"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N30">
+        <v>12877.199999999999</v>
+      </c>
+      <c r="AH30">
         <f t="shared" si="6"/>
-        <v>0.95</v>
-      </c>
-      <c r="O30">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P30">
-        <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="Q30">
-        <f t="shared" si="8"/>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="R30">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U30">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V30">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="W30">
-        <f t="shared" si="1"/>
-        <v>2E-3</v>
-      </c>
-      <c r="X30">
-        <f t="shared" si="10"/>
-        <v>0.74</v>
-      </c>
-      <c r="Y30">
-        <f t="shared" si="11"/>
-        <v>1.6215116800000018E-3</v>
-      </c>
-      <c r="Z30">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA30">
-        <f t="shared" si="12"/>
-        <v>1.9567701760000002E-4</v>
-      </c>
-      <c r="AB30">
-        <f t="shared" si="13"/>
-        <v>14.204442316800016</v>
-      </c>
-      <c r="AC30">
-        <f t="shared" si="14"/>
-        <v>1.7141306741760001</v>
-      </c>
-      <c r="AD30">
-        <f t="shared" si="15"/>
-        <v>1.5918572990976015E-2</v>
-      </c>
-      <c r="AE30" s="11">
-        <f t="shared" si="2"/>
-        <v>61320</v>
-      </c>
-      <c r="AF30">
-        <f t="shared" si="3"/>
-        <v>0.19272</v>
-      </c>
-      <c r="AI30" s="2" t="s">
+        <v>3.6424079999999998E-2</v>
+      </c>
+      <c r="AJ30" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AJ30" s="2">
+      <c r="AK30" s="2">
         <v>0.76</v>
       </c>
-      <c r="AL30" s="2"/>
       <c r="AM30" s="2"/>
-    </row>
-    <row r="31" spans="1:41">
+      <c r="AN30" s="2"/>
+    </row>
+    <row r="31" spans="1:42">
       <c r="E31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="AN31" t="s">
+      <c r="AO31" t="s">
         <v>96</v>
       </c>
-      <c r="AO31" t="s">
+      <c r="AP31" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:41">
+    <row r="32" spans="1:42">
       <c r="E32" s="2"/>
-      <c r="AI32" s="2" t="s">
+      <c r="AJ32" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AN32" t="s">
+      <c r="AO32" t="s">
         <v>97</v>
       </c>
-      <c r="AO32" t="s">
+      <c r="AP32" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:41">
+    <row r="33" spans="1:42">
       <c r="E33" s="2"/>
-      <c r="AI33">
+      <c r="AJ33">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="AN33" t="s">
+      <c r="AO33" t="s">
         <v>98</v>
       </c>
-      <c r="AO33" t="s">
+      <c r="AP33" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:41">
+    <row r="34" spans="1:42">
       <c r="E34" s="2"/>
-      <c r="AN34" t="s">
+      <c r="AO34" t="s">
         <v>99</v>
       </c>
-      <c r="AO34" t="s">
+      <c r="AP34" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:41">
+    <row r="35" spans="1:42">
       <c r="E35" s="2"/>
-      <c r="AI35" t="s">
+      <c r="AJ35" t="s">
         <v>31</v>
       </c>
-      <c r="AN35" t="s">
+      <c r="AO35" t="s">
         <v>100</v>
       </c>
-      <c r="AO35" t="s">
+      <c r="AP35" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:41">
+    <row r="36" spans="1:42">
       <c r="E36" s="2"/>
-      <c r="AI36" t="s">
+      <c r="AJ36" t="s">
         <v>32</v>
       </c>
-      <c r="AN36" t="s">
+      <c r="AO36" t="s">
         <v>101</v>
       </c>
-      <c r="AO36" t="s">
+      <c r="AP36" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:41">
+    <row r="37" spans="1:42">
       <c r="E37" s="2"/>
-      <c r="AI37" t="s">
+      <c r="AJ37" t="s">
         <v>92</v>
       </c>
-      <c r="AJ37">
+      <c r="AK37">
         <v>0.66</v>
       </c>
-      <c r="AN37" t="s">
+      <c r="AO37" t="s">
         <v>102</v>
       </c>
-      <c r="AO37" t="s">
+      <c r="AP37" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:41">
+    <row r="38" spans="1:42">
       <c r="E38" s="2"/>
-      <c r="AI38">
+      <c r="AJ38">
         <v>11</v>
       </c>
-      <c r="AJ38">
+      <c r="AK38">
         <v>0.68</v>
       </c>
-      <c r="AN38" t="s">
+      <c r="AO38" t="s">
         <v>103</v>
       </c>
-      <c r="AO38" t="s">
+      <c r="AP38" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:41">
-      <c r="AI39">
+    <row r="39" spans="1:42">
+      <c r="AJ39">
         <v>12</v>
       </c>
-      <c r="AJ39">
+      <c r="AK39">
         <v>0.7</v>
       </c>
-      <c r="AN39" t="s">
+      <c r="AO39" t="s">
         <v>104</v>
       </c>
-      <c r="AO39" t="s">
+      <c r="AP39" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:41">
-      <c r="AI40">
+    <row r="40" spans="1:42">
+      <c r="AJ40">
         <v>13</v>
       </c>
-      <c r="AJ40">
+      <c r="AK40">
         <v>0.71</v>
       </c>
-      <c r="AN40" t="s">
+      <c r="AO40" t="s">
         <v>105</v>
       </c>
-      <c r="AO40" t="s">
+      <c r="AP40" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:41" ht="17">
+    <row r="41" spans="1:42" ht="17">
       <c r="A41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3907,11 +4167,11 @@
         <v>67</v>
       </c>
       <c r="J41">
-        <f>VLOOKUP(A41, $AI$11:$AJ$18,2,FALSE)</f>
+        <f>VLOOKUP(A41, $AJ$11:$AK$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K41">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L41" t="s">
@@ -3926,15 +4186,15 @@
         <v>0.95</v>
       </c>
       <c r="O41">
-        <f>$AJ$4</f>
+        <f>$AK$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P41">
-        <f>VLOOKUP(A41, $AI$11:$AK$18,3,FALSE)</f>
+        <f>VLOOKUP(A41, $AJ$11:$AL$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q41">
-        <f>VLOOKUP(E41,$AN$10:$AO$22,2,FALSE)</f>
+        <f>VLOOKUP(E41,$AO$10:$AP$22,2,FALSE)</f>
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="R41">
@@ -3942,19 +4202,19 @@
         <v>1</v>
       </c>
       <c r="T41">
-        <f>$AM$3</f>
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
       <c r="U41">
-        <f>$AM$4</f>
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
       <c r="V41">
-        <f>$AJ$5</f>
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
       <c r="X41">
-        <f>VLOOKUP(F41, $AI$37:$AJ$55, 2, FALSE)</f>
+        <f>VLOOKUP(F41, $AJ$37:$AK$55, 2, FALSE)</f>
         <v>0.66</v>
       </c>
       <c r="Y41">
@@ -3962,7 +4222,7 @@
         <v>1.1612240640000012E-2</v>
       </c>
       <c r="Z41">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA41">
@@ -3981,14 +4241,14 @@
         <f>(AB41+AC41)*10^-3</f>
         <v>2.4059726876640024E-2</v>
       </c>
-      <c r="AI41">
+      <c r="AJ41">
         <v>14</v>
       </c>
-      <c r="AJ41">
+      <c r="AK41">
         <v>0.73</v>
       </c>
     </row>
-    <row r="42" spans="1:41" ht="17">
+    <row r="42" spans="1:42" ht="17">
       <c r="A42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4011,11 +4271,11 @@
         <v>67</v>
       </c>
       <c r="J42">
-        <f>VLOOKUP(A42, $AI$11:$AJ$18,2,FALSE)</f>
+        <f>VLOOKUP(A42, $AJ$11:$AK$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K42">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L42" t="s">
@@ -4030,15 +4290,15 @@
         <v>0.95</v>
       </c>
       <c r="O42">
-        <f>$AJ$4</f>
+        <f>$AK$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P42">
-        <f>VLOOKUP(A42, $AI$11:$AK$18,3,FALSE)</f>
+        <f>VLOOKUP(A42, $AJ$11:$AL$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q42">
-        <f>VLOOKUP(E42,$AN$10:$AO$22,2,FALSE)</f>
+        <f>VLOOKUP(E42,$AO$10:$AP$22,2,FALSE)</f>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R42">
@@ -4046,19 +4306,19 @@
         <v>0</v>
       </c>
       <c r="T42">
-        <f>$AM$3</f>
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
       <c r="U42">
-        <f>$AM$4</f>
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
       <c r="V42">
-        <f>$AJ$5</f>
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
       <c r="X42">
-        <f t="shared" ref="X42:X60" si="16">VLOOKUP(F42, $AI$37:$AJ$55, 2, FALSE)</f>
+        <f t="shared" ref="X42:X60" si="19">VLOOKUP(F42, $AJ$37:$AK$55, 2, FALSE)</f>
         <v>0.68</v>
       </c>
       <c r="Y42">
@@ -4066,7 +4326,7 @@
         <v>1.1964126720000011E-2</v>
       </c>
       <c r="Z42">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA42">
@@ -4085,14 +4345,14 @@
         <f>(AB42+AC42)*10^-3</f>
         <v>2.9642302767168026E-2</v>
       </c>
-      <c r="AI42">
+      <c r="AJ42">
         <v>15</v>
       </c>
-      <c r="AJ42">
+      <c r="AK42">
         <v>0.74</v>
       </c>
     </row>
-    <row r="43" spans="1:41" ht="17">
+    <row r="43" spans="1:42" ht="17">
       <c r="A43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4115,88 +4375,88 @@
         <v>67</v>
       </c>
       <c r="J43">
-        <f t="shared" ref="J43:J60" si="17">VLOOKUP(A43, $AI$11:$AJ$18,2,FALSE)</f>
+        <f t="shared" ref="J43:J60" si="20">VLOOKUP(A43, $AJ$11:$AK$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K43">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L43" t="s">
         <v>58</v>
       </c>
       <c r="M43">
-        <f t="shared" ref="M43:M60" si="18">1-N43</f>
+        <f t="shared" ref="M43:M60" si="21">1-N43</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N43">
-        <f t="shared" ref="N43:N60" si="19">IF(L43="yes", 1, 0.95)</f>
+        <f t="shared" ref="N43:N60" si="22">IF(L43="yes", 1, 0.95)</f>
         <v>0.95</v>
       </c>
       <c r="O43">
-        <f>$AJ$4</f>
+        <f>$AK$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P43">
-        <f t="shared" ref="P43:P60" si="20">VLOOKUP(A43, $AI$11:$AK$18,3,FALSE)</f>
+        <f t="shared" ref="P43:P60" si="23">VLOOKUP(A43, $AJ$11:$AL$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q43">
-        <f t="shared" ref="Q43:Q60" si="21">VLOOKUP(E43,$AN$10:$AO$22,2,FALSE)</f>
+        <f t="shared" ref="Q43:Q60" si="24">VLOOKUP(E43,$AO$10:$AP$22,2,FALSE)</f>
         <v>1.8E-3</v>
       </c>
       <c r="R43">
-        <f t="shared" ref="R43:R60" si="22">IF(D43="yes", 1, 0)</f>
+        <f t="shared" ref="R43:R60" si="25">IF(D43="yes", 1, 0)</f>
         <v>1</v>
       </c>
       <c r="T43">
-        <f>$AM$3</f>
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
       <c r="U43">
-        <f>$AM$4</f>
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
       <c r="V43">
-        <f>$AJ$5</f>
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
       <c r="X43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
       <c r="Y43">
-        <f t="shared" ref="Y43:Y60" si="23">J43*K43*M43*X43*V43</f>
+        <f t="shared" ref="Y43:Y60" si="26">J43*K43*M43*X43*V43</f>
         <v>1.231601280000001E-2</v>
       </c>
       <c r="Z43">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA43">
-        <f t="shared" ref="AA43:AA60" si="24">J43*K43*N43*Z43*V43</f>
+        <f t="shared" ref="AA43:AA60" si="27">J43*K43*N43*Z43*V43</f>
         <v>1.5711713472E-3</v>
       </c>
       <c r="AB43">
-        <f t="shared" ref="AB43:AB60" si="25">C43*Y43*365</f>
+        <f t="shared" ref="AB43:AB60" si="28">C43*Y43*365</f>
         <v>31.467412704000026</v>
       </c>
       <c r="AC43">
-        <f t="shared" ref="AC43:AC60" si="26">C43*AA43*365</f>
+        <f t="shared" ref="AC43:AC60" si="29">C43*AA43*365</f>
         <v>4.0143427920960004</v>
       </c>
       <c r="AD43">
-        <f t="shared" ref="AD43:AD60" si="27">(AB43+AC43)*10^-3</f>
+        <f t="shared" ref="AD43:AD60" si="30">(AB43+AC43)*10^-3</f>
         <v>3.5481755496096029E-2</v>
       </c>
-      <c r="AI43">
+      <c r="AJ43">
         <v>16</v>
       </c>
-      <c r="AJ43">
+      <c r="AK43">
         <v>0.75</v>
       </c>
     </row>
-    <row r="44" spans="1:41" ht="17">
+    <row r="44" spans="1:42" ht="17">
       <c r="A44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,88 +4479,88 @@
         <v>67</v>
       </c>
       <c r="J44">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>2.73</v>
       </c>
       <c r="K44">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L44" t="s">
         <v>58</v>
       </c>
       <c r="M44">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N44">
+        <f t="shared" si="22"/>
+        <v>0.95</v>
+      </c>
+      <c r="O44">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P44">
+        <f t="shared" si="23"/>
+        <v>39.5</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="24"/>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="R44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U44">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V44">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X44">
         <f t="shared" si="19"/>
-        <v>0.95</v>
-      </c>
-      <c r="O44">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P44">
-        <f t="shared" si="20"/>
-        <v>39.5</v>
-      </c>
-      <c r="Q44">
-        <f t="shared" si="21"/>
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="R44">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="T44">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U44">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V44">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X44">
-        <f t="shared" si="16"/>
         <v>0.71</v>
       </c>
       <c r="Y44">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>1.2491955840000011E-2</v>
       </c>
       <c r="Z44">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>1.5711713472E-3</v>
       </c>
       <c r="AB44">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>36.476511052800035</v>
       </c>
       <c r="AC44">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4.5878203338240002</v>
       </c>
       <c r="AD44">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.1064331386624034E-2</v>
       </c>
-      <c r="AI44">
+      <c r="AJ44">
         <v>17</v>
       </c>
-      <c r="AJ44">
+      <c r="AK44">
         <v>0.76</v>
       </c>
     </row>
-    <row r="45" spans="1:41" ht="17">
+    <row r="45" spans="1:42" ht="17">
       <c r="A45" s="3" t="s">
         <v>25</v>
       </c>
@@ -4323,1226 +4583,1226 @@
         <v>67</v>
       </c>
       <c r="J45">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.34</v>
       </c>
       <c r="K45">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L45" t="s">
         <v>58</v>
       </c>
       <c r="M45">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N45">
+        <f t="shared" si="22"/>
+        <v>0.95</v>
+      </c>
+      <c r="O45">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P45">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="24"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R45">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="T45">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U45">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V45">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X45">
         <f t="shared" si="19"/>
+        <v>0.73</v>
+      </c>
+      <c r="Y45">
+        <f t="shared" si="26"/>
+        <v>1.5995993600000015E-3</v>
+      </c>
+      <c r="Z45">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA45">
+        <f t="shared" si="27"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AB45">
+        <f t="shared" si="28"/>
+        <v>5.254683897600005</v>
+      </c>
+      <c r="AC45">
+        <f t="shared" si="29"/>
+        <v>0.64279900281600011</v>
+      </c>
+      <c r="AD45">
+        <f t="shared" si="30"/>
+        <v>5.8974829004160047E-3</v>
+      </c>
+      <c r="AJ45">
+        <v>18</v>
+      </c>
+      <c r="AK45">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:42" ht="17">
+      <c r="A46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46">
+        <v>10</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F46">
+        <v>15</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="20"/>
+        <v>0.34</v>
+      </c>
+      <c r="K46">
+        <f>$AN$5</f>
+        <v>0.19</v>
+      </c>
+      <c r="L46" t="s">
+        <v>58</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="21"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="22"/>
         <v>0.95</v>
       </c>
-      <c r="O45">
-        <f>$AJ$4</f>
+      <c r="O46">
+        <f>$AK$4</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="P45">
+      <c r="P46">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="Q46">
+        <f t="shared" si="24"/>
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="R46">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U46">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V46">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X46">
+        <f t="shared" si="19"/>
+        <v>0.74</v>
+      </c>
+      <c r="Y46">
+        <f t="shared" si="26"/>
+        <v>1.6215116800000018E-3</v>
+      </c>
+      <c r="Z46">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA46">
+        <f t="shared" si="27"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AB46">
+        <f t="shared" si="28"/>
+        <v>5.9185176320000075</v>
+      </c>
+      <c r="AC46">
+        <f t="shared" si="29"/>
+        <v>0.71422111424000012</v>
+      </c>
+      <c r="AD46">
+        <f t="shared" si="30"/>
+        <v>6.6327387462400073E-3</v>
+      </c>
+      <c r="AJ46">
+        <v>19</v>
+      </c>
+      <c r="AK46">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:42" ht="17">
+      <c r="A47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47">
+        <v>11</v>
+      </c>
+      <c r="D47" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F47">
+        <v>16</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J47">
         <f t="shared" si="20"/>
+        <v>0.34</v>
+      </c>
+      <c r="K47">
+        <f>$AN$5</f>
+        <v>0.19</v>
+      </c>
+      <c r="L47" t="s">
+        <v>58</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="21"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="22"/>
+        <v>0.95</v>
+      </c>
+      <c r="O47">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P47">
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
-      <c r="Q45">
+      <c r="Q47">
+        <f t="shared" si="24"/>
+        <v>5.3E-3</v>
+      </c>
+      <c r="R47">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="T47">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U47">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V47">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X47">
+        <f t="shared" si="19"/>
+        <v>0.75</v>
+      </c>
+      <c r="Y47">
+        <f t="shared" si="26"/>
+        <v>1.6434240000000016E-3</v>
+      </c>
+      <c r="Z47">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA47">
+        <f t="shared" si="27"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AB47">
+        <f t="shared" si="28"/>
+        <v>6.5983473600000062</v>
+      </c>
+      <c r="AC47">
+        <f t="shared" si="29"/>
+        <v>0.78564322566400013</v>
+      </c>
+      <c r="AD47">
+        <f t="shared" si="30"/>
+        <v>7.383990585664006E-3</v>
+      </c>
+      <c r="AJ47">
+        <v>20</v>
+      </c>
+      <c r="AK47">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:42" ht="17">
+      <c r="A48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F48">
+        <v>17</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="20"/>
+        <v>0.34</v>
+      </c>
+      <c r="K48">
+        <f>$AN$5</f>
+        <v>0.19</v>
+      </c>
+      <c r="L48" t="s">
+        <v>58</v>
+      </c>
+      <c r="M48">
         <f t="shared" si="21"/>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="R45">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="22"/>
+        <v>0.95</v>
+      </c>
+      <c r="O48">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P48">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="Q48">
+        <f t="shared" si="24"/>
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="R48">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U48">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V48">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X48">
+        <f t="shared" si="19"/>
+        <v>0.76</v>
+      </c>
+      <c r="Y48">
+        <f t="shared" si="26"/>
+        <v>1.6653363200000019E-3</v>
+      </c>
+      <c r="Z48">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA48">
+        <f t="shared" si="27"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AB48">
+        <f t="shared" si="28"/>
+        <v>7.2941730816000083</v>
+      </c>
+      <c r="AC48">
+        <f t="shared" si="29"/>
+        <v>0.85706533708800003</v>
+      </c>
+      <c r="AD48">
+        <f t="shared" si="30"/>
+        <v>8.1512384186880078E-3</v>
+      </c>
+      <c r="AJ48">
+        <v>21</v>
+      </c>
+      <c r="AK48">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:37" ht="17">
+      <c r="A49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F49">
+        <v>18</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="20"/>
+        <v>0.34</v>
+      </c>
+      <c r="K49">
+        <f>$AN$5</f>
+        <v>0.19</v>
+      </c>
+      <c r="L49" t="s">
+        <v>58</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="21"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="22"/>
+        <v>0.95</v>
+      </c>
+      <c r="O49">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P49">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="Q49">
+        <f t="shared" si="24"/>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="R49">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="T49">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U49">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V49">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X49">
+        <f t="shared" si="19"/>
+        <v>0.77</v>
+      </c>
+      <c r="Y49">
+        <f t="shared" si="26"/>
+        <v>1.6872486400000017E-3</v>
+      </c>
+      <c r="Z49">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA49">
+        <f t="shared" si="27"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AB49">
+        <f t="shared" si="28"/>
+        <v>8.0059947968000085</v>
+      </c>
+      <c r="AC49">
+        <f t="shared" si="29"/>
+        <v>0.92848744851200005</v>
+      </c>
+      <c r="AD49">
+        <f t="shared" si="30"/>
+        <v>8.9344822453120091E-3</v>
+      </c>
+      <c r="AJ49">
+        <v>22</v>
+      </c>
+      <c r="AK49">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="50" spans="1:37" ht="17">
+      <c r="A50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50">
+        <v>14</v>
+      </c>
+      <c r="D50" t="s">
+        <v>58</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F50">
+        <v>19</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="20"/>
+        <v>0.34</v>
+      </c>
+      <c r="K50">
+        <f>$AN$5</f>
+        <v>0.19</v>
+      </c>
+      <c r="L50" t="s">
+        <v>58</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="21"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N50">
+        <f t="shared" si="22"/>
+        <v>0.95</v>
+      </c>
+      <c r="O50">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P50">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="Q50">
+        <f t="shared" si="24"/>
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="R50">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U50">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V50">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X50">
+        <f t="shared" si="19"/>
+        <v>0.77</v>
+      </c>
+      <c r="Y50">
+        <f t="shared" si="26"/>
+        <v>1.6872486400000017E-3</v>
+      </c>
+      <c r="Z50">
+        <f>$AJ$33</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="AA50">
+        <f t="shared" si="27"/>
+        <v>1.9567701760000002E-4</v>
+      </c>
+      <c r="AB50">
+        <f t="shared" si="28"/>
+        <v>8.6218405504000089</v>
+      </c>
+      <c r="AC50">
+        <f t="shared" si="29"/>
+        <v>0.99990955993600006</v>
+      </c>
+      <c r="AD50">
+        <f t="shared" si="30"/>
+        <v>9.6217501103360095E-3</v>
+      </c>
+      <c r="AJ50">
+        <v>23</v>
+      </c>
+      <c r="AK50">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:37" ht="17">
+      <c r="A51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>57</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F51">
+        <v>20</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="20"/>
+        <v>0.34</v>
+      </c>
+      <c r="K51">
+        <f>$AN$5</f>
+        <v>0.19</v>
+      </c>
+      <c r="L51" t="s">
+        <v>57</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="N51">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
-      <c r="T45">
-        <f>$AM$3</f>
+      <c r="O51">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P51">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="Q51">
+        <f t="shared" si="24"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="R51">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="T51">
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
-      <c r="U45">
-        <f>$AM$4</f>
+      <c r="U51">
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
-      <c r="V45">
-        <f>$AJ$5</f>
+      <c r="V51">
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
-      <c r="X45">
-        <f t="shared" si="16"/>
-        <v>0.73</v>
-      </c>
-      <c r="Y45">
-        <f t="shared" si="23"/>
-        <v>1.5995993600000015E-3</v>
-      </c>
-      <c r="Z45">
-        <f>$AI$33</f>
+      <c r="X51">
+        <f t="shared" si="19"/>
+        <v>0.78</v>
+      </c>
+      <c r="Y51">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="AA45">
-        <f t="shared" si="24"/>
-        <v>1.9567701760000002E-4</v>
-      </c>
-      <c r="AB45">
-        <f t="shared" si="25"/>
-        <v>5.254683897600005</v>
-      </c>
-      <c r="AC45">
-        <f t="shared" si="26"/>
-        <v>0.64279900281600011</v>
-      </c>
-      <c r="AD45">
+      <c r="AA51">
         <f t="shared" si="27"/>
-        <v>5.8974829004160047E-3</v>
-      </c>
-      <c r="AI45">
-        <v>18</v>
-      </c>
-      <c r="AJ45">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="46" spans="1:41" ht="17">
-      <c r="A46" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46">
-        <v>10</v>
-      </c>
-      <c r="D46" t="s">
+        <v>2.0597580800000003E-4</v>
+      </c>
+      <c r="AB51">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <f t="shared" si="29"/>
+        <v>1.1277175488000002</v>
+      </c>
+      <c r="AD51">
+        <f t="shared" si="30"/>
+        <v>1.1277175488000003E-3</v>
+      </c>
+      <c r="AJ51">
+        <v>24</v>
+      </c>
+      <c r="AK51">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:37" ht="17">
+      <c r="A52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52">
+        <v>16</v>
+      </c>
+      <c r="D52" t="s">
         <v>58</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F46">
-        <v>15</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J46">
-        <f t="shared" si="17"/>
-        <v>0.34</v>
-      </c>
-      <c r="K46">
-        <f>$AM$5</f>
+      <c r="E52" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F52">
+        <v>21</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="20"/>
+        <v>0.91</v>
+      </c>
+      <c r="K52">
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
-      <c r="L46" t="s">
-        <v>58</v>
-      </c>
-      <c r="M46">
-        <f t="shared" si="18"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N46">
-        <f t="shared" si="19"/>
-        <v>0.95</v>
-      </c>
-      <c r="O46">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P46">
-        <f t="shared" si="20"/>
-        <v>7</v>
-      </c>
-      <c r="Q46">
+      <c r="L52" t="s">
+        <v>57</v>
+      </c>
+      <c r="M52">
         <f t="shared" si="21"/>
-        <v>1.9900000000000001E-2</v>
-      </c>
-      <c r="R46">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="T46">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U46">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V46">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X46">
-        <f t="shared" si="16"/>
-        <v>0.74</v>
-      </c>
-      <c r="Y46">
-        <f t="shared" si="23"/>
-        <v>1.6215116800000018E-3</v>
-      </c>
-      <c r="Z46">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA46">
-        <f t="shared" si="24"/>
-        <v>1.9567701760000002E-4</v>
-      </c>
-      <c r="AB46">
-        <f t="shared" si="25"/>
-        <v>5.9185176320000075</v>
-      </c>
-      <c r="AC46">
-        <f t="shared" si="26"/>
-        <v>0.71422111424000012</v>
-      </c>
-      <c r="AD46">
-        <f t="shared" si="27"/>
-        <v>6.6327387462400073E-3</v>
-      </c>
-      <c r="AI46">
-        <v>19</v>
-      </c>
-      <c r="AJ46">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="47" spans="1:41" ht="17">
-      <c r="A47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47">
-        <v>11</v>
-      </c>
-      <c r="D47" t="s">
-        <v>57</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F47">
-        <v>16</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J47">
-        <f t="shared" si="17"/>
-        <v>0.34</v>
-      </c>
-      <c r="K47">
-        <f>$AM$5</f>
-        <v>0.19</v>
-      </c>
-      <c r="L47" t="s">
-        <v>58</v>
-      </c>
-      <c r="M47">
-        <f t="shared" si="18"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N47">
-        <f t="shared" si="19"/>
-        <v>0.95</v>
-      </c>
-      <c r="O47">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P47">
-        <f t="shared" si="20"/>
-        <v>7</v>
-      </c>
-      <c r="Q47">
-        <f t="shared" si="21"/>
-        <v>5.3E-3</v>
-      </c>
-      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="N52">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
-      <c r="T47">
-        <f>$AM$3</f>
+      <c r="O52">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P52">
+        <f t="shared" si="23"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" si="24"/>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="R52">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
-      <c r="U47">
-        <f>$AM$4</f>
+      <c r="U52">
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
-      <c r="V47">
-        <f>$AJ$5</f>
+      <c r="V52">
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
-      <c r="X47">
-        <f t="shared" si="16"/>
-        <v>0.75</v>
-      </c>
-      <c r="Y47">
-        <f t="shared" si="23"/>
-        <v>1.6434240000000016E-3</v>
-      </c>
-      <c r="Z47">
-        <f>$AI$33</f>
+      <c r="X52">
+        <f t="shared" si="19"/>
+        <v>0.78</v>
+      </c>
+      <c r="Y52">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="AA47">
-        <f t="shared" si="24"/>
-        <v>1.9567701760000002E-4</v>
-      </c>
-      <c r="AB47">
-        <f t="shared" si="25"/>
-        <v>6.5983473600000062</v>
-      </c>
-      <c r="AC47">
-        <f t="shared" si="26"/>
-        <v>0.78564322566400013</v>
-      </c>
-      <c r="AD47">
+      <c r="AA52">
         <f t="shared" si="27"/>
-        <v>7.383990585664006E-3</v>
-      </c>
-      <c r="AI47">
-        <v>20</v>
-      </c>
-      <c r="AJ47">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="48" spans="1:41" ht="17">
-      <c r="A48" s="3" t="s">
+        <v>5.5128819200000003E-4</v>
+      </c>
+      <c r="AB52">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <f t="shared" si="29"/>
+        <v>3.21952304128</v>
+      </c>
+      <c r="AD52">
+        <f t="shared" si="30"/>
+        <v>3.21952304128E-3</v>
+      </c>
+      <c r="AJ52">
         <v>25</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48">
-        <v>12</v>
-      </c>
-      <c r="D48" t="s">
-        <v>58</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F48">
+      <c r="AK52">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:37" ht="17">
+      <c r="A53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53">
         <v>17</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J48">
-        <f t="shared" si="17"/>
-        <v>0.34</v>
-      </c>
-      <c r="K48">
-        <f>$AM$5</f>
+      <c r="D53" t="s">
+        <v>57</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F53">
+        <v>22</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="20"/>
+        <v>0.91</v>
+      </c>
+      <c r="K53">
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
-      <c r="L48" t="s">
-        <v>58</v>
-      </c>
-      <c r="M48">
-        <f t="shared" si="18"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N48">
-        <f t="shared" si="19"/>
-        <v>0.95</v>
-      </c>
-      <c r="O48">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P48">
-        <f t="shared" si="20"/>
-        <v>7</v>
-      </c>
-      <c r="Q48">
+      <c r="L53" t="s">
+        <v>57</v>
+      </c>
+      <c r="M53">
         <f t="shared" si="21"/>
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="R48">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U48">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V48">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X48">
-        <f t="shared" si="16"/>
-        <v>0.76</v>
-      </c>
-      <c r="Y48">
-        <f t="shared" si="23"/>
-        <v>1.6653363200000019E-3</v>
-      </c>
-      <c r="Z48">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA48">
-        <f t="shared" si="24"/>
-        <v>1.9567701760000002E-4</v>
-      </c>
-      <c r="AB48">
-        <f t="shared" si="25"/>
-        <v>7.2941730816000083</v>
-      </c>
-      <c r="AC48">
-        <f t="shared" si="26"/>
-        <v>0.85706533708800003</v>
-      </c>
-      <c r="AD48">
-        <f t="shared" si="27"/>
-        <v>8.1512384186880078E-3</v>
-      </c>
-      <c r="AI48">
-        <v>21</v>
-      </c>
-      <c r="AJ48">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="49" spans="1:36" ht="17">
-      <c r="A49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49">
-        <v>13</v>
-      </c>
-      <c r="D49" t="s">
-        <v>57</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F49">
-        <v>18</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J49">
-        <f t="shared" si="17"/>
-        <v>0.34</v>
-      </c>
-      <c r="K49">
-        <f>$AM$5</f>
-        <v>0.19</v>
-      </c>
-      <c r="L49" t="s">
-        <v>58</v>
-      </c>
-      <c r="M49">
-        <f t="shared" si="18"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N49">
-        <f t="shared" si="19"/>
-        <v>0.95</v>
-      </c>
-      <c r="O49">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P49">
-        <f t="shared" si="20"/>
-        <v>7</v>
-      </c>
-      <c r="Q49">
-        <f t="shared" si="21"/>
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="N53">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
-      <c r="T49">
-        <f>$AM$3</f>
+      <c r="O53">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P53">
+        <f t="shared" si="23"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="24"/>
+        <v>1.8E-3</v>
+      </c>
+      <c r="R53">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="T53">
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
-      <c r="U49">
-        <f>$AM$4</f>
+      <c r="U53">
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
-      <c r="V49">
-        <f>$AJ$5</f>
+      <c r="V53">
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
-      <c r="X49">
-        <f t="shared" si="16"/>
-        <v>0.77</v>
-      </c>
-      <c r="Y49">
-        <f t="shared" si="23"/>
-        <v>1.6872486400000017E-3</v>
-      </c>
-      <c r="Z49">
-        <f>$AI$33</f>
+      <c r="X53">
+        <f t="shared" si="19"/>
+        <v>0.78</v>
+      </c>
+      <c r="Y53">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="AA49">
-        <f t="shared" si="24"/>
-        <v>1.9567701760000002E-4</v>
-      </c>
-      <c r="AB49">
-        <f t="shared" si="25"/>
-        <v>8.0059947968000085</v>
-      </c>
-      <c r="AC49">
-        <f t="shared" si="26"/>
-        <v>0.92848744851200005</v>
-      </c>
-      <c r="AD49">
+      <c r="AA53">
         <f t="shared" si="27"/>
-        <v>8.9344822453120091E-3</v>
-      </c>
-      <c r="AI49">
-        <v>22</v>
-      </c>
-      <c r="AJ49">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="50" spans="1:36" ht="17">
-      <c r="A50" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50">
-        <v>14</v>
-      </c>
-      <c r="D50" t="s">
+        <v>5.5128819200000003E-4</v>
+      </c>
+      <c r="AB53">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AC53">
+        <f t="shared" si="29"/>
+        <v>3.4207432313599999</v>
+      </c>
+      <c r="AD53">
+        <f t="shared" si="30"/>
+        <v>3.4207432313600001E-3</v>
+      </c>
+      <c r="AJ53">
+        <v>26</v>
+      </c>
+      <c r="AK53">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:37" ht="17">
+      <c r="A54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54">
+        <v>18</v>
+      </c>
+      <c r="D54" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F50">
-        <v>19</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J50">
-        <f t="shared" si="17"/>
-        <v>0.34</v>
-      </c>
-      <c r="K50">
-        <f>$AM$5</f>
+      <c r="E54" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F54">
+        <v>23</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="20"/>
+        <v>0.91</v>
+      </c>
+      <c r="K54">
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
-      <c r="L50" t="s">
-        <v>58</v>
-      </c>
-      <c r="M50">
-        <f t="shared" si="18"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N50">
-        <f t="shared" si="19"/>
-        <v>0.95</v>
-      </c>
-      <c r="O50">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P50">
-        <f t="shared" si="20"/>
-        <v>7</v>
-      </c>
-      <c r="Q50">
+      <c r="L54" t="s">
+        <v>57</v>
+      </c>
+      <c r="M54">
         <f t="shared" si="21"/>
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="R50">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="T50">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U50">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V50">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X50">
-        <f t="shared" si="16"/>
-        <v>0.77</v>
-      </c>
-      <c r="Y50">
-        <f t="shared" si="23"/>
-        <v>1.6872486400000017E-3</v>
-      </c>
-      <c r="Z50">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA50">
-        <f t="shared" si="24"/>
-        <v>1.9567701760000002E-4</v>
-      </c>
-      <c r="AB50">
-        <f t="shared" si="25"/>
-        <v>8.6218405504000089</v>
-      </c>
-      <c r="AC50">
-        <f t="shared" si="26"/>
-        <v>0.99990955993600006</v>
-      </c>
-      <c r="AD50">
-        <f t="shared" si="27"/>
-        <v>9.6217501103360095E-3</v>
-      </c>
-      <c r="AI50">
-        <v>23</v>
-      </c>
-      <c r="AJ50">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="51" spans="1:36" ht="17">
-      <c r="A51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51">
-        <v>15</v>
-      </c>
-      <c r="D51" t="s">
-        <v>57</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F51">
-        <v>20</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J51">
-        <f t="shared" si="17"/>
-        <v>0.34</v>
-      </c>
-      <c r="K51">
-        <f>$AM$5</f>
-        <v>0.19</v>
-      </c>
-      <c r="L51" t="s">
-        <v>57</v>
-      </c>
-      <c r="M51">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="O51">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P51">
-        <f t="shared" si="20"/>
-        <v>7</v>
-      </c>
-      <c r="Q51">
-        <f t="shared" si="21"/>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="N54">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
-      <c r="T51">
-        <f>$AM$3</f>
+      <c r="O54">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P54">
+        <f t="shared" si="23"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q54">
+        <f t="shared" si="24"/>
+        <v>1.8E-3</v>
+      </c>
+      <c r="R54">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
-      <c r="U51">
-        <f>$AM$4</f>
+      <c r="U54">
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
-      <c r="V51">
-        <f>$AJ$5</f>
+      <c r="V54">
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
-      <c r="X51">
-        <f t="shared" si="16"/>
-        <v>0.78</v>
-      </c>
-      <c r="Y51">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="Z51">
-        <f>$AI$33</f>
+      <c r="X54">
+        <f t="shared" si="19"/>
+        <v>0.79</v>
+      </c>
+      <c r="Y54">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="AA51">
-        <f t="shared" si="24"/>
-        <v>2.0597580800000003E-4</v>
-      </c>
-      <c r="AB51">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AC51">
-        <f t="shared" si="26"/>
-        <v>1.1277175488000002</v>
-      </c>
-      <c r="AD51">
+      <c r="AA54">
         <f t="shared" si="27"/>
-        <v>1.1277175488000003E-3</v>
-      </c>
-      <c r="AI51">
+        <v>5.5128819200000003E-4</v>
+      </c>
+      <c r="AB54">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <f t="shared" si="29"/>
+        <v>3.6219634214399998</v>
+      </c>
+      <c r="AD54">
+        <f t="shared" si="30"/>
+        <v>3.6219634214399998E-3</v>
+      </c>
+      <c r="AJ54">
+        <v>27</v>
+      </c>
+      <c r="AK54">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:37" ht="17">
+      <c r="A55" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AJ51">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:36" ht="17">
-      <c r="A52" s="3" t="s">
+      <c r="B55" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55">
+        <v>19</v>
+      </c>
+      <c r="D55" t="s">
+        <v>57</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F55">
         <v>24</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C52">
-        <v>16</v>
-      </c>
-      <c r="D52" t="s">
-        <v>58</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F52">
-        <v>21</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J52">
-        <f t="shared" si="17"/>
+      <c r="I55" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="20"/>
         <v>0.91</v>
       </c>
-      <c r="K52">
-        <f>$AM$5</f>
+      <c r="K55">
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
-      <c r="L52" t="s">
+      <c r="L55" t="s">
         <v>57</v>
       </c>
-      <c r="M52">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="O52">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P52">
-        <f t="shared" si="20"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q52">
+      <c r="M55">
         <f t="shared" si="21"/>
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="R52">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="T52">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U52">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V52">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X52">
-        <f t="shared" si="16"/>
-        <v>0.78</v>
-      </c>
-      <c r="Y52">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="Z52">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA52">
-        <f t="shared" si="24"/>
-        <v>5.5128819200000003E-4</v>
-      </c>
-      <c r="AB52">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AC52">
-        <f t="shared" si="26"/>
-        <v>3.21952304128</v>
-      </c>
-      <c r="AD52">
-        <f t="shared" si="27"/>
-        <v>3.21952304128E-3</v>
-      </c>
-      <c r="AI52">
-        <v>25</v>
-      </c>
-      <c r="AJ52">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="53" spans="1:36" ht="17">
-      <c r="A53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53">
-        <v>17</v>
-      </c>
-      <c r="D53" t="s">
-        <v>57</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F53">
-        <v>22</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J53">
-        <f t="shared" si="17"/>
-        <v>0.91</v>
-      </c>
-      <c r="K53">
-        <f>$AM$5</f>
-        <v>0.19</v>
-      </c>
-      <c r="L53" t="s">
-        <v>57</v>
-      </c>
-      <c r="M53">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="N53">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="O53">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P53">
-        <f t="shared" si="20"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q53">
-        <f t="shared" si="21"/>
-        <v>1.8E-3</v>
-      </c>
-      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="N55">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
-      <c r="T53">
-        <f>$AM$3</f>
+      <c r="O55">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P55">
+        <f t="shared" si="23"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="24"/>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="R55">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
+      <c r="T55">
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
-      <c r="U53">
-        <f>$AM$4</f>
+      <c r="U55">
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
-      <c r="V53">
-        <f>$AJ$5</f>
+      <c r="V55">
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
-      <c r="X53">
-        <f t="shared" si="16"/>
-        <v>0.78</v>
-      </c>
-      <c r="Y53">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="Z53">
-        <f>$AI$33</f>
+      <c r="X55">
+        <f t="shared" si="19"/>
+        <v>0.79</v>
+      </c>
+      <c r="Y55">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="AA53">
-        <f t="shared" si="24"/>
+      <c r="AA55">
+        <f t="shared" si="27"/>
         <v>5.5128819200000003E-4</v>
       </c>
-      <c r="AB53">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AC53">
-        <f t="shared" si="26"/>
-        <v>3.4207432313599999</v>
-      </c>
-      <c r="AD53">
-        <f t="shared" si="27"/>
-        <v>3.4207432313600001E-3</v>
-      </c>
-      <c r="AI53">
-        <v>26</v>
-      </c>
-      <c r="AJ53">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="54" spans="1:36" ht="17">
-      <c r="A54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54">
-        <v>18</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="AB55">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <f t="shared" si="29"/>
+        <v>3.8231836115200006</v>
+      </c>
+      <c r="AD55">
+        <f t="shared" si="30"/>
+        <v>3.8231836115200008E-3</v>
+      </c>
+      <c r="AJ55" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK55">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:37">
+      <c r="A56" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56">
+        <v>20</v>
+      </c>
+      <c r="D56" t="s">
         <v>58</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F54">
-        <v>23</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J54">
-        <f t="shared" si="17"/>
-        <v>0.91</v>
-      </c>
-      <c r="K54">
-        <f>$AM$5</f>
+      <c r="E56" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F56">
+        <v>25</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="20"/>
+        <v>2.73</v>
+      </c>
+      <c r="K56">
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
-      <c r="L54" t="s">
+      <c r="L56" t="s">
         <v>57</v>
       </c>
-      <c r="M54">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="N54">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="O54">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P54">
-        <f t="shared" si="20"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q54">
+      <c r="M56">
         <f t="shared" si="21"/>
-        <v>1.8E-3</v>
-      </c>
-      <c r="R54">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="T54">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U54">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V54">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X54">
-        <f t="shared" si="16"/>
-        <v>0.79</v>
-      </c>
-      <c r="Y54">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="Z54">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA54">
-        <f t="shared" si="24"/>
-        <v>5.5128819200000003E-4</v>
-      </c>
-      <c r="AB54">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AC54">
-        <f t="shared" si="26"/>
-        <v>3.6219634214399998</v>
-      </c>
-      <c r="AD54">
-        <f t="shared" si="27"/>
-        <v>3.6219634214399998E-3</v>
-      </c>
-      <c r="AI54">
-        <v>27</v>
-      </c>
-      <c r="AJ54">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:36" ht="17">
-      <c r="A55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C55">
-        <v>19</v>
-      </c>
-      <c r="D55" t="s">
-        <v>57</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F55">
-        <v>24</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J55">
-        <f t="shared" si="17"/>
-        <v>0.91</v>
-      </c>
-      <c r="K55">
-        <f>$AM$5</f>
-        <v>0.19</v>
-      </c>
-      <c r="L55" t="s">
-        <v>57</v>
-      </c>
-      <c r="M55">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="N55">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="O55">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P55">
-        <f t="shared" si="20"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q55">
-        <f t="shared" si="21"/>
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="N56">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
-      <c r="T55">
-        <f>$AM$3</f>
+      <c r="O56">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P56">
+        <f t="shared" si="23"/>
+        <v>39.5</v>
+      </c>
+      <c r="Q56">
+        <f t="shared" si="24"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R56">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
-      <c r="U55">
-        <f>$AM$4</f>
+      <c r="U56">
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
-      <c r="V55">
-        <f>$AJ$5</f>
+      <c r="V56">
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
-      <c r="X55">
-        <f t="shared" si="16"/>
+      <c r="X56">
+        <f t="shared" si="19"/>
         <v>0.79</v>
       </c>
-      <c r="Y55">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="Z55">
-        <f>$AI$33</f>
+      <c r="Y56">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="AA55">
-        <f t="shared" si="24"/>
-        <v>5.5128819200000003E-4</v>
-      </c>
-      <c r="AB55">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AC55">
-        <f t="shared" si="26"/>
-        <v>3.8231836115200006</v>
-      </c>
-      <c r="AD55">
+      <c r="AA56">
         <f t="shared" si="27"/>
-        <v>3.8231836115200008E-3</v>
-      </c>
-      <c r="AI55" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ55">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:36">
-      <c r="A56" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C56">
-        <v>20</v>
-      </c>
-      <c r="D56" t="s">
-        <v>58</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F56">
-        <v>25</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J56">
-        <f t="shared" si="17"/>
-        <v>2.73</v>
-      </c>
-      <c r="K56">
-        <f>$AM$5</f>
-        <v>0.19</v>
-      </c>
-      <c r="L56" t="s">
-        <v>57</v>
-      </c>
-      <c r="M56">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="O56">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P56">
-        <f t="shared" si="20"/>
-        <v>39.5</v>
-      </c>
-      <c r="Q56">
-        <f t="shared" si="21"/>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="R56">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="T56">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U56">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V56">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X56">
-        <f t="shared" si="16"/>
-        <v>0.79</v>
-      </c>
-      <c r="Y56">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="Z56">
-        <f>$AI$33</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="AA56">
-        <f t="shared" si="24"/>
         <v>1.6538645760000002E-3</v>
       </c>
       <c r="AB56">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AC56">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>12.0732114048</v>
       </c>
       <c r="AD56">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1.2073211404800001E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:36">
+    <row r="57" spans="1:37">
       <c r="A57" s="2" t="s">
         <v>20</v>
       </c>
@@ -5565,82 +5825,82 @@
         <v>67</v>
       </c>
       <c r="J57">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.34</v>
       </c>
       <c r="K57">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L57" t="s">
         <v>57</v>
       </c>
       <c r="M57">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N57">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="O57">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P57">
-        <f t="shared" si="20"/>
-        <v>7</v>
-      </c>
-      <c r="Q57">
-        <f t="shared" si="21"/>
-        <v>1.9900000000000001E-2</v>
-      </c>
-      <c r="R57">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
+      <c r="O57">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P57">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="Q57">
+        <f t="shared" si="24"/>
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="R57">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
       <c r="T57">
-        <f>$AM$3</f>
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
       <c r="U57">
-        <f>$AM$4</f>
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
       <c r="V57">
-        <f>$AJ$5</f>
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
       <c r="X57">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.79</v>
       </c>
       <c r="Y57">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Z57">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA57">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB57">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AC57">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1.57880456832</v>
       </c>
       <c r="AD57">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1.5788045683200001E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:36">
+    <row r="58" spans="1:37">
       <c r="A58" s="2" t="s">
         <v>21</v>
       </c>
@@ -5663,82 +5923,82 @@
         <v>68</v>
       </c>
       <c r="J58">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>2.73</v>
       </c>
       <c r="K58">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L58" t="s">
         <v>57</v>
       </c>
       <c r="M58">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N58">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="O58">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P58">
+        <f t="shared" si="23"/>
+        <v>39.5</v>
+      </c>
+      <c r="Q58">
+        <f t="shared" si="24"/>
+        <v>5.3E-3</v>
+      </c>
+      <c r="R58">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U58">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V58">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X58">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="O58">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P58">
-        <f t="shared" si="20"/>
-        <v>39.5</v>
-      </c>
-      <c r="Q58">
-        <f t="shared" si="21"/>
-        <v>5.3E-3</v>
-      </c>
-      <c r="R58">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="T58">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U58">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V58">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X58">
-        <f t="shared" si="16"/>
         <v>0.8</v>
       </c>
       <c r="Y58">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Z58">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA58">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>1.6538645760000002E-3</v>
       </c>
       <c r="AB58">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AC58">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>13.28053254528</v>
       </c>
       <c r="AD58">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1.3280532545279999E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:36">
+    <row r="59" spans="1:37">
       <c r="A59" s="2" t="s">
         <v>22</v>
       </c>
@@ -5761,82 +6021,82 @@
         <v>69</v>
       </c>
       <c r="J59">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.91</v>
       </c>
       <c r="K59">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L59" t="s">
         <v>57</v>
       </c>
       <c r="M59">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N59">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="O59">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P59">
-        <f t="shared" si="20"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q59">
-        <f t="shared" si="21"/>
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="R59">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
+      <c r="O59">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P59">
+        <f t="shared" si="23"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q59">
+        <f t="shared" si="24"/>
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="R59">
+        <f t="shared" si="25"/>
+        <v>1</v>
+      </c>
       <c r="T59">
-        <f>$AM$3</f>
+        <f>$AN$3</f>
         <v>0.24</v>
       </c>
       <c r="U59">
-        <f>$AM$4</f>
+        <f>$AN$4</f>
         <v>0.11</v>
       </c>
       <c r="V59">
-        <f>$AJ$5</f>
+        <f>$AK$5</f>
         <v>0.6784</v>
       </c>
       <c r="X59">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.8</v>
       </c>
       <c r="Y59">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Z59">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA59">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB59">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AC59">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4.6280643718399999</v>
       </c>
       <c r="AD59">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.6280643718400001E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:36">
+    <row r="60" spans="1:37">
       <c r="A60" s="2" t="s">
         <v>64</v>
       </c>
@@ -5859,97 +6119,98 @@
         <v>70</v>
       </c>
       <c r="J60">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.34</v>
       </c>
       <c r="K60">
-        <f>$AM$5</f>
+        <f>$AN$5</f>
         <v>0.19</v>
       </c>
       <c r="L60" t="s">
         <v>57</v>
       </c>
       <c r="M60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N60">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="O60">
+        <f>$AK$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P60">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="Q60">
+        <f t="shared" si="24"/>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="R60">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <f>$AN$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U60">
+        <f>$AN$4</f>
+        <v>0.11</v>
+      </c>
+      <c r="V60">
+        <f>$AK$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X60">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="O60">
-        <f>$AJ$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P60">
-        <f t="shared" si="20"/>
-        <v>7</v>
-      </c>
-      <c r="Q60">
-        <f t="shared" si="21"/>
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="R60">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="T60">
-        <f>$AM$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U60">
-        <f>$AM$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V60">
-        <f>$AJ$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X60">
-        <f t="shared" si="16"/>
         <v>0.78</v>
       </c>
       <c r="Y60">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Z60">
-        <f>$AI$33</f>
+        <f>$AJ$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA60">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB60">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AC60">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1.8043480780800005</v>
       </c>
       <c r="AD60">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1.8043480780800005E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:36">
+    <row r="61" spans="1:37">
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:36">
+    <row r="62" spans="1:37">
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:36">
+    <row r="63" spans="1:37">
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:36">
+    <row r="64" spans="1:37">
       <c r="E64" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="AM18:AM19"/>
+    <mergeCell ref="AN18:AN19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/packages/calculators/src/modules/test/4.7-other-livestock-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.7-other-livestock-manure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89528F04-08AE-A242-B0AD-391DD2A41BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456E6BE9-C8F6-484B-AE45-13CCB9F1ED40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51220" yWindow="-3180" windowWidth="28800" windowHeight="25760" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="111">
   <si>
     <t>Livestock type</t>
   </si>
@@ -455,6 +455,12 @@
   </si>
   <si>
     <t>expression</t>
+  </si>
+  <si>
+    <t>En2o,leach</t>
+  </si>
+  <si>
+    <t>Mleach</t>
   </si>
 </sst>
 </file>
@@ -891,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A5655F-5BFE-554E-A3D3-9DFA9517010F}">
-  <dimension ref="A1:AP64"/>
+  <dimension ref="A1:AS64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="3" customWidth="1"/>
@@ -919,19 +925,19 @@
     <col min="28" max="28" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="12.1640625" customWidth="1"/>
-    <col min="32" max="34" width="16.5" customWidth="1"/>
-    <col min="36" max="37" width="16" customWidth="1"/>
-    <col min="39" max="39" width="36" customWidth="1"/>
-    <col min="41" max="41" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="37" width="16.5" customWidth="1"/>
+    <col min="39" max="40" width="16" customWidth="1"/>
+    <col min="42" max="42" width="36" customWidth="1"/>
+    <col min="44" max="44" width="35.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42">
-      <c r="AK1" s="1"/>
+    <row r="1" spans="1:45">
+      <c r="AN1" s="1"/>
     </row>
-    <row r="2" spans="1:42">
-      <c r="AK2" s="1"/>
+    <row r="2" spans="1:45">
+      <c r="AN2" s="1"/>
     </row>
-    <row r="3" spans="1:42">
+    <row r="3" spans="1:45">
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -943,20 +949,20 @@
       </c>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
-      <c r="AJ3" t="s">
+      <c r="AM3" t="s">
         <v>48</v>
       </c>
-      <c r="AK3">
+      <c r="AN3">
         <v>0.21</v>
       </c>
-      <c r="AM3" s="7" t="s">
+      <c r="AP3" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AN3">
+      <c r="AQ3">
         <v>0.24</v>
       </c>
     </row>
-    <row r="4" spans="1:42">
+    <row r="4" spans="1:45">
       <c r="C4">
         <v>1776</v>
       </c>
@@ -1017,21 +1023,21 @@
       <c r="AG4">
         <v>1753</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AM4" t="s">
         <v>38</v>
       </c>
-      <c r="AK4">
+      <c r="AN4">
         <f>44/28</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AP4" t="s">
         <v>50</v>
       </c>
-      <c r="AN4">
-        <v>0.11</v>
+      <c r="AQ4">
+        <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:42">
+    <row r="5" spans="1:45">
       <c r="C5" t="s">
         <v>88</v>
       </c>
@@ -1086,61 +1092,61 @@
       <c r="AG5" t="s">
         <v>108</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AM5" t="s">
         <v>39</v>
       </c>
-      <c r="AK5">
+      <c r="AN5">
         <v>0.6784</v>
       </c>
-      <c r="AM5" t="s">
+      <c r="AP5" t="s">
         <v>61</v>
       </c>
-      <c r="AN5">
+      <c r="AQ5">
         <v>0.19</v>
       </c>
     </row>
-    <row r="6" spans="1:42">
+    <row r="6" spans="1:45">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
-      <c r="AI6" t="s">
+      <c r="AL6" t="s">
         <v>40</v>
       </c>
-      <c r="AJ6" t="s">
+      <c r="AM6" t="s">
         <v>41</v>
       </c>
-      <c r="AK6">
+      <c r="AN6">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:42">
-      <c r="AJ7" t="s">
+    <row r="7" spans="1:45">
+      <c r="AM7" t="s">
         <v>42</v>
       </c>
-      <c r="AK7">
+      <c r="AN7">
         <v>2E-3</v>
       </c>
-      <c r="AM7" s="2"/>
-      <c r="AN7" s="2"/>
+      <c r="AP7" s="2"/>
+      <c r="AQ7" s="2"/>
     </row>
-    <row r="8" spans="1:42">
-      <c r="AM8" s="2"/>
-      <c r="AN8" s="2"/>
+    <row r="8" spans="1:45">
+      <c r="AP8" s="2"/>
+      <c r="AQ8" s="2"/>
     </row>
-    <row r="9" spans="1:42">
+    <row r="9" spans="1:45">
       <c r="A9" s="4"/>
       <c r="C9" t="s">
         <v>51</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="AN9" t="s">
         <v>36</v>
       </c>
-      <c r="AM9" s="2"/>
-      <c r="AN9" s="2"/>
-      <c r="AP9" t="s">
+      <c r="AP9" s="2"/>
+      <c r="AQ9" s="2"/>
+      <c r="AS9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:42" ht="17">
+    <row r="10" spans="1:45" ht="17">
       <c r="A10" s="5" t="s">
         <v>0</v>
       </c>
@@ -1243,25 +1249,32 @@
       <c r="AH10" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AJ10" t="s">
+      <c r="AI10" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ10" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="AK10" s="11"/>
+      <c r="AM10" t="s">
         <v>35</v>
       </c>
-      <c r="AK10" t="s">
+      <c r="AN10" t="s">
         <v>35</v>
       </c>
-      <c r="AL10" t="s">
+      <c r="AO10" t="s">
         <v>44</v>
       </c>
-      <c r="AM10" s="2"/>
-      <c r="AN10" s="2"/>
-      <c r="AO10" s="2" t="s">
+      <c r="AP10" s="2"/>
+      <c r="AQ10" s="2"/>
+      <c r="AR10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AP10" s="2">
+      <c r="AS10" s="2">
         <v>5.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:42" ht="17">
+    <row r="11" spans="1:45" ht="17">
       <c r="A11" s="3" t="s">
         <v>3</v>
       </c>
@@ -1281,18 +1294,18 @@
         <v>96</v>
       </c>
       <c r="H11" t="str">
-        <f>VLOOKUP(G11,$AO$31:$AP$40,2,FALSE)</f>
+        <f>VLOOKUP(G11,$AR$31:$AS$40,2,FALSE)</f>
         <v>wet</v>
       </c>
       <c r="I11" t="s">
         <v>67</v>
       </c>
       <c r="J11">
-        <f>VLOOKUP(A11, $AJ$11:$AK$18,2,FALSE)</f>
+        <f>VLOOKUP(A11, $AM$11:$AN$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K11">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L11" t="s">
@@ -1307,15 +1320,15 @@
         <v>1</v>
       </c>
       <c r="O11">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P11">
-        <f>VLOOKUP(A11, $AJ$11:$AL$18,3,FALSE)</f>
+        <f>VLOOKUP(A11, $AM$11:$AO$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q11">
-        <f>VLOOKUP(E11,$AO$10:$AP$22,2,FALSE)</f>
+        <f>VLOOKUP(E11,$AR$10:$AS$22,2,FALSE)</f>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R11">
@@ -1323,27 +1336,27 @@
         <v>1</v>
       </c>
       <c r="S11">
-        <f>$AK$3</f>
+        <f>$AN$3</f>
         <v>0.21</v>
       </c>
       <c r="T11">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U11">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V11">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W11">
-        <f>IF(H11="wet",$AK$6,$AK$7)</f>
+        <f>IF(H11="wet",$AN$6,$AN$7)</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X11">
-        <f>VLOOKUP(I11,$AJ$23:$AK$30,2,FALSE)</f>
+        <f>VLOOKUP(I11,$AM$23:$AN$30,2,FALSE)</f>
         <v>0.78</v>
       </c>
       <c r="Y11">
@@ -1351,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA11">
@@ -1386,25 +1399,33 @@
         <f>AG11*Q11*O11*10^-3</f>
         <v>0.16652212499999999</v>
       </c>
-      <c r="AJ11" s="2" t="s">
+      <c r="AI11">
+        <f>AE11*R11*T11</f>
+        <v>17301</v>
+      </c>
+      <c r="AJ11">
+        <f>AI11*U11*O11*10^-3</f>
+        <v>0.29906014285714283</v>
+      </c>
+      <c r="AM11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="AK11" s="2">
+      <c r="AN11" s="2">
         <v>2.73</v>
       </c>
-      <c r="AL11" s="2">
+      <c r="AO11" s="2">
         <v>39.5</v>
       </c>
-      <c r="AM11" s="2"/>
-      <c r="AN11" s="2"/>
-      <c r="AO11" s="2" t="s">
+      <c r="AP11" s="2"/>
+      <c r="AQ11" s="2"/>
+      <c r="AR11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AP11" s="2">
+      <c r="AS11" s="2">
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:42" ht="17">
+    <row r="12" spans="1:45" ht="17">
       <c r="A12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1424,18 +1445,18 @@
         <v>97</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" ref="H12:H30" si="0">VLOOKUP(G12,$AO$31:$AP$40,2,FALSE)</f>
+        <f t="shared" ref="H12:H30" si="0">VLOOKUP(G12,$AR$31:$AS$40,2,FALSE)</f>
         <v>wet</v>
       </c>
       <c r="I12" t="s">
         <v>67</v>
       </c>
       <c r="J12">
-        <f>VLOOKUP(A12, $AJ$11:$AK$18,2,FALSE)</f>
+        <f>VLOOKUP(A12, $AM$11:$AN$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K12">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L12" t="s">
@@ -1450,15 +1471,15 @@
         <v>1</v>
       </c>
       <c r="O12">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P12">
-        <f>VLOOKUP(A12, $AJ$11:$AL$18,3,FALSE)</f>
+        <f>VLOOKUP(A12, $AM$11:$AO$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q12">
-        <f>VLOOKUP(E12,$AO$10:$AP$22,2,FALSE)</f>
+        <f>VLOOKUP(E12,$AR$10:$AS$22,2,FALSE)</f>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R12">
@@ -1466,27 +1487,27 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <f t="shared" ref="S12:S30" si="1">$AK$3</f>
+        <f t="shared" ref="S12:S30" si="1">$AN$3</f>
         <v>0.21</v>
       </c>
       <c r="T12">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U12">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V12">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W12">
-        <f t="shared" ref="W12:W30" si="2">IF(H12="wet",$AK$6,$AK$7)</f>
+        <f t="shared" ref="W12:W30" si="2">IF(H12="wet",$AN$6,$AN$7)</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X12">
-        <f>VLOOKUP(I12,$AJ$23:$AK$30,2,FALSE)</f>
+        <f>VLOOKUP(I12,$AM$23:$AN$30,2,FALSE)</f>
         <v>0.78</v>
       </c>
       <c r="Y12">
@@ -1494,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA12">
@@ -1529,25 +1550,33 @@
         <f t="shared" ref="AH12:AH30" si="6">AG12*Q12*O12*10^-3</f>
         <v>0.19982654999999999</v>
       </c>
-      <c r="AJ12" s="2" t="s">
+      <c r="AI12">
+        <f t="shared" ref="AI12:AI30" si="7">AE12*R12*T12</f>
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <f t="shared" ref="AJ12:AJ30" si="8">AI12*U12*O12*10^-3</f>
+        <v>0</v>
+      </c>
+      <c r="AM12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AK12" s="2">
+      <c r="AN12" s="2">
         <v>0.34</v>
       </c>
-      <c r="AL12" s="2">
+      <c r="AO12" s="2">
         <v>7</v>
       </c>
-      <c r="AM12" s="2"/>
-      <c r="AN12" s="2"/>
-      <c r="AO12" s="2" t="s">
+      <c r="AP12" s="2"/>
+      <c r="AQ12" s="2"/>
+      <c r="AR12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AP12" s="2">
+      <c r="AS12" s="2">
         <v>1.8E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:42" ht="17">
+    <row r="13" spans="1:45" ht="17">
       <c r="A13" s="3" t="s">
         <v>3</v>
       </c>
@@ -1574,38 +1603,38 @@
         <v>67</v>
       </c>
       <c r="J13">
-        <f t="shared" ref="J13:J30" si="7">VLOOKUP(A13, $AJ$11:$AK$18,2,FALSE)</f>
+        <f t="shared" ref="J13:J30" si="9">VLOOKUP(A13, $AM$11:$AN$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K13">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L13" t="s">
         <v>57</v>
       </c>
       <c r="M13">
-        <f t="shared" ref="M13:M30" si="8">1-N13</f>
+        <f t="shared" ref="M13:M30" si="10">1-N13</f>
         <v>0</v>
       </c>
       <c r="N13">
-        <f t="shared" ref="N13:N30" si="9">IF(L13="yes", 1, 0.95)</f>
+        <f t="shared" ref="N13:N30" si="11">IF(L13="yes", 1, 0.95)</f>
         <v>1</v>
       </c>
       <c r="O13">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P13">
-        <f t="shared" ref="P13:P30" si="10">VLOOKUP(A13, $AJ$11:$AL$18,3,FALSE)</f>
+        <f t="shared" ref="P13:P30" si="12">VLOOKUP(A13, $AM$11:$AO$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q13">
-        <f t="shared" ref="Q13:Q30" si="11">VLOOKUP(E13,$AO$10:$AP$22,2,FALSE)</f>
+        <f t="shared" ref="Q13:Q30" si="13">VLOOKUP(E13,$AR$10:$AS$22,2,FALSE)</f>
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="R13">
-        <f t="shared" ref="R13:R30" si="12">IF(D13="yes", 1, 0)</f>
+        <f t="shared" ref="R13:R30" si="14">IF(D13="yes", 1, 0)</f>
         <v>1</v>
       </c>
       <c r="S13">
@@ -1613,15 +1642,15 @@
         <v>0.21</v>
       </c>
       <c r="T13">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U13">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V13">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W13">
@@ -1629,31 +1658,31 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X13">
-        <f t="shared" ref="X13:X30" si="13">VLOOKUP(I13,$AJ$23:$AK$30,2,FALSE)</f>
+        <f t="shared" ref="X13:X30" si="15">VLOOKUP(I13,$AM$23:$AN$30,2,FALSE)</f>
         <v>0.78</v>
       </c>
       <c r="Y13">
-        <f t="shared" ref="Y13:Y30" si="14">J13*K13*M13*X13*V13</f>
+        <f t="shared" ref="Y13:Y30" si="16">J13*K13*M13*X13*V13</f>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA13">
-        <f t="shared" ref="AA13:AA30" si="15">J13*K13*N13*Z13*V13</f>
+        <f t="shared" ref="AA13:AA30" si="17">J13*K13*N13*Z13*V13</f>
         <v>1.6538645760000002E-3</v>
       </c>
       <c r="AB13">
-        <f t="shared" ref="AB13:AB30" si="16">C13*Y13*365</f>
+        <f t="shared" ref="AB13:AB30" si="18">C13*Y13*365</f>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f t="shared" ref="AC13:AC30" si="17">C13*AA13*365</f>
+        <f t="shared" ref="AC13:AC30" si="19">C13*AA13*365</f>
         <v>4.22562399168</v>
       </c>
       <c r="AD13">
-        <f t="shared" ref="AD13:AD30" si="18">(AB13+AC13)*10^-3</f>
+        <f t="shared" ref="AD13:AD30" si="20">(AB13+AC13)*10^-3</f>
         <v>4.2256239916799998E-3</v>
       </c>
       <c r="AE13" s="11">
@@ -1672,25 +1701,33 @@
         <f t="shared" si="6"/>
         <v>0.19649610749999999</v>
       </c>
-      <c r="AJ13" s="2" t="s">
+      <c r="AI13">
+        <f t="shared" si="7"/>
+        <v>24221.399999999998</v>
+      </c>
+      <c r="AJ13">
+        <f t="shared" si="8"/>
+        <v>0.41868419999999995</v>
+      </c>
+      <c r="AM13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AK13" s="2">
+      <c r="AN13" s="2">
         <v>0.91</v>
       </c>
-      <c r="AL13" s="2">
+      <c r="AO13" s="2">
         <v>13.2</v>
       </c>
-      <c r="AM13" s="2"/>
-      <c r="AN13" s="2"/>
-      <c r="AO13" s="2" t="s">
+      <c r="AP13" s="2"/>
+      <c r="AQ13" s="2"/>
+      <c r="AR13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AP13" s="2">
+      <c r="AS13" s="2">
         <v>2.8999999999999998E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:42" ht="17">
+    <row r="14" spans="1:45" ht="17">
       <c r="A14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1717,38 +1754,38 @@
         <v>67</v>
       </c>
       <c r="J14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2.73</v>
       </c>
       <c r="K14">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L14" t="s">
         <v>57</v>
       </c>
       <c r="M14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O14">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>39.5</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S14">
@@ -1756,15 +1793,15 @@
         <v>0.21</v>
       </c>
       <c r="T14">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U14">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V14">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W14">
@@ -1772,31 +1809,31 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.78</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.6538645760000002E-3</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>4.8292845619200007</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>4.8292845619200006E-3</v>
       </c>
       <c r="AE14" s="11">
@@ -1815,25 +1852,33 @@
         <f t="shared" si="6"/>
         <v>0.26643539999999999</v>
       </c>
-      <c r="AJ14" s="2" t="s">
+      <c r="AI14">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AM14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AK14" s="2">
+      <c r="AN14" s="2">
         <v>2.73</v>
       </c>
-      <c r="AL14" s="2">
+      <c r="AO14" s="2">
         <v>39.5</v>
       </c>
-      <c r="AM14" s="2"/>
-      <c r="AN14" s="2"/>
-      <c r="AO14" s="2" t="s">
+      <c r="AP14" s="2"/>
+      <c r="AQ14" s="2"/>
+      <c r="AR14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AP14" s="2">
+      <c r="AS14" s="2">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:42" ht="17">
+    <row r="15" spans="1:45" ht="17">
       <c r="A15" s="3" t="s">
         <v>25</v>
       </c>
@@ -1860,38 +1905,38 @@
         <v>67</v>
       </c>
       <c r="J15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.34</v>
       </c>
       <c r="K15">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L15" t="s">
         <v>57</v>
       </c>
       <c r="M15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O15">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.8E-3</v>
       </c>
       <c r="R15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="S15">
@@ -1899,15 +1944,15 @@
         <v>0.21</v>
       </c>
       <c r="T15">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U15">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V15">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W15">
@@ -1915,31 +1960,31 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.78</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.67663052928000011</v>
       </c>
       <c r="AD15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>6.7663052928000015E-4</v>
       </c>
       <c r="AE15" s="11">
@@ -1958,25 +2003,33 @@
         <f t="shared" si="6"/>
         <v>1.3659029999999999E-2</v>
       </c>
-      <c r="AJ15" s="2" t="s">
+      <c r="AI15">
+        <f t="shared" si="7"/>
+        <v>5518.8</v>
+      </c>
+      <c r="AJ15">
+        <f t="shared" si="8"/>
+        <v>9.5396400000000006E-2</v>
+      </c>
+      <c r="AM15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AK15" s="2">
+      <c r="AN15" s="2">
         <v>0.34</v>
       </c>
-      <c r="AL15" s="2">
+      <c r="AO15" s="2">
         <v>7</v>
       </c>
-      <c r="AM15" s="2"/>
-      <c r="AN15" s="2"/>
-      <c r="AO15" s="2" t="s">
+      <c r="AP15" s="2"/>
+      <c r="AQ15" s="2"/>
+      <c r="AR15" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AP15" s="2">
+      <c r="AS15" s="2">
         <v>1.9900000000000001E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:42" ht="17">
+    <row r="16" spans="1:45" ht="17">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -2003,38 +2056,38 @@
         <v>28</v>
       </c>
       <c r="J16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.34</v>
       </c>
       <c r="K16">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L16" t="s">
         <v>57</v>
       </c>
       <c r="M16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O16">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="R16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S16">
@@ -2042,15 +2095,15 @@
         <v>0.21</v>
       </c>
       <c r="T16">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U16">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V16">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W16">
@@ -2058,31 +2111,31 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.71</v>
       </c>
       <c r="Y16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z16">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AC16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.75181169920000002</v>
       </c>
       <c r="AD16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>7.518116992E-4</v>
       </c>
       <c r="AE16" s="11">
@@ -2101,25 +2154,33 @@
         <f t="shared" si="6"/>
         <v>2.4451349999999997E-2</v>
       </c>
-      <c r="AJ16" s="2" t="s">
+      <c r="AI16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AM16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AK16" s="2">
+      <c r="AN16" s="2">
         <v>2.73</v>
       </c>
-      <c r="AL16" s="2">
+      <c r="AO16" s="2">
         <v>39.5</v>
       </c>
-      <c r="AM16" s="2"/>
-      <c r="AN16" s="2"/>
-      <c r="AO16" s="2" t="s">
+      <c r="AP16" s="2"/>
+      <c r="AQ16" s="2"/>
+      <c r="AR16" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AP16" s="2">
+      <c r="AS16" s="2">
         <v>5.3E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:42" ht="17">
+    <row r="17" spans="1:45" ht="17">
       <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
@@ -2146,38 +2207,38 @@
         <v>65</v>
       </c>
       <c r="J17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.34</v>
       </c>
       <c r="K17">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L17" t="s">
         <v>57</v>
       </c>
       <c r="M17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O17">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="R17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="S17">
@@ -2185,15 +2246,15 @@
         <v>0.21</v>
       </c>
       <c r="T17">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U17">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V17">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W17">
@@ -2201,31 +2262,31 @@
         <v>2E-3</v>
       </c>
       <c r="X17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.75</v>
       </c>
       <c r="Y17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.82699286912000003</v>
       </c>
       <c r="AD17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>8.2699286912000006E-4</v>
       </c>
       <c r="AE17" s="11">
@@ -2244,25 +2305,33 @@
         <f t="shared" si="6"/>
         <v>7.4197199999999991E-2</v>
       </c>
-      <c r="AJ17" s="2" t="s">
+      <c r="AI17">
+        <f t="shared" si="7"/>
+        <v>6745.2</v>
+      </c>
+      <c r="AJ17">
+        <f t="shared" si="8"/>
+        <v>0.11659559999999999</v>
+      </c>
+      <c r="AM17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AK17" s="2">
+      <c r="AN17" s="2">
         <v>0.91</v>
       </c>
-      <c r="AL17" s="2">
+      <c r="AO17" s="2">
         <v>13.2</v>
       </c>
-      <c r="AM17" s="2"/>
-      <c r="AN17" s="2"/>
-      <c r="AO17" s="2" t="s">
+      <c r="AP17" s="2"/>
+      <c r="AQ17" s="2"/>
+      <c r="AR17" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AP17" s="2">
+      <c r="AS17" s="2">
         <v>6.4000000000000003E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:42" ht="17">
+    <row r="18" spans="1:45" ht="17">
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
@@ -2289,38 +2358,38 @@
         <v>66</v>
       </c>
       <c r="J18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.34</v>
       </c>
       <c r="K18">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L18" t="s">
         <v>57</v>
       </c>
       <c r="M18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O18">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="R18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S18">
@@ -2328,15 +2397,15 @@
         <v>0.21</v>
       </c>
       <c r="T18">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U18">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V18">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W18">
@@ -2344,31 +2413,31 @@
         <v>2E-3</v>
       </c>
       <c r="X18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.8</v>
       </c>
       <c r="Y18">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z18">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA18">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AC18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.90217403904000026</v>
       </c>
       <c r="AD18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>9.0217403904000024E-4</v>
       </c>
       <c r="AE18" s="11">
@@ -2387,25 +2456,33 @@
         <f t="shared" si="6"/>
         <v>5.9695019999999994E-2</v>
       </c>
-      <c r="AJ18" s="2" t="s">
+      <c r="AI18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AM18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AK18" s="2">
+      <c r="AN18" s="2">
         <v>0.34</v>
       </c>
-      <c r="AL18" s="2">
+      <c r="AO18" s="2">
         <v>7</v>
       </c>
-      <c r="AM18" s="2"/>
-      <c r="AN18" s="10"/>
-      <c r="AO18" s="2" t="s">
+      <c r="AP18" s="2"/>
+      <c r="AQ18" s="10"/>
+      <c r="AR18" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AP18" s="2">
+      <c r="AS18" s="2">
         <v>2.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:42" ht="17">
+    <row r="19" spans="1:45" ht="17">
       <c r="A19" s="3" t="s">
         <v>25</v>
       </c>
@@ -2432,38 +2509,38 @@
         <v>67</v>
       </c>
       <c r="J19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.34</v>
       </c>
       <c r="K19">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L19" t="s">
         <v>57</v>
       </c>
       <c r="M19">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O19">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="S19">
@@ -2471,15 +2548,15 @@
         <v>0.21</v>
       </c>
       <c r="T19">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U19">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V19">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W19">
@@ -2487,31 +2564,31 @@
         <v>2E-3</v>
       </c>
       <c r="X19">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.78</v>
       </c>
       <c r="Y19">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z19">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA19">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB19">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AC19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.97735520896000017</v>
       </c>
       <c r="AD19">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>9.7735520896000019E-4</v>
       </c>
       <c r="AE19" s="11">
@@ -2530,16 +2607,24 @@
         <f t="shared" si="6"/>
         <v>7.6726649999999993E-2</v>
       </c>
-      <c r="AM19" s="2"/>
-      <c r="AN19" s="10"/>
-      <c r="AO19" s="2" t="s">
+      <c r="AI19">
+        <f t="shared" si="7"/>
+        <v>7971.5999999999995</v>
+      </c>
+      <c r="AJ19">
+        <f t="shared" si="8"/>
+        <v>0.1377948</v>
+      </c>
+      <c r="AP19" s="2"/>
+      <c r="AQ19" s="10"/>
+      <c r="AR19" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="AP19" s="2">
+      <c r="AS19" s="2">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:42" ht="17">
+    <row r="20" spans="1:45" ht="17">
       <c r="A20" s="3" t="s">
         <v>25</v>
       </c>
@@ -2566,38 +2651,38 @@
         <v>68</v>
       </c>
       <c r="J20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.34</v>
       </c>
       <c r="K20">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L20" t="s">
         <v>57</v>
       </c>
       <c r="M20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N20">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O20">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P20">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="Q20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.8E-3</v>
       </c>
       <c r="R20">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S20">
@@ -2605,15 +2690,15 @@
         <v>0.21</v>
       </c>
       <c r="T20">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U20">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V20">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W20">
@@ -2621,31 +2706,31 @@
         <v>2E-3</v>
       </c>
       <c r="X20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.74</v>
       </c>
       <c r="Y20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z20">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB20">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AC20">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1.0525363788800002</v>
       </c>
       <c r="AD20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1.0525363788800003E-3</v>
       </c>
       <c r="AE20" s="11">
@@ -2664,16 +2749,24 @@
         <f t="shared" si="6"/>
         <v>2.1247379999999996E-2</v>
       </c>
-      <c r="AM20" s="2"/>
-      <c r="AN20" s="2"/>
-      <c r="AO20" s="2" t="s">
+      <c r="AI20">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AP20" s="2"/>
+      <c r="AQ20" s="2"/>
+      <c r="AR20" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AP20" s="2">
+      <c r="AS20" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:42" ht="17">
+    <row r="21" spans="1:45" ht="17">
       <c r="A21" s="3" t="s">
         <v>25</v>
       </c>
@@ -2700,38 +2793,38 @@
         <v>69</v>
       </c>
       <c r="J21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.34</v>
       </c>
       <c r="K21">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L21" t="s">
         <v>57</v>
       </c>
       <c r="M21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O21">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="R21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="S21">
@@ -2739,15 +2832,15 @@
         <v>0.21</v>
       </c>
       <c r="T21">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U21">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V21">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W21">
@@ -2755,31 +2848,31 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.7</v>
       </c>
       <c r="Y21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z21">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AC21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1.1277175488000002</v>
       </c>
       <c r="AD21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1.1277175488000003E-3</v>
       </c>
       <c r="AE21" s="11">
@@ -2798,22 +2891,30 @@
         <f t="shared" si="6"/>
         <v>3.6677024999999995E-2</v>
       </c>
-      <c r="AJ21" s="2" t="s">
+      <c r="AI21">
+        <f t="shared" si="7"/>
+        <v>9198</v>
+      </c>
+      <c r="AJ21">
+        <f t="shared" si="8"/>
+        <v>0.158994</v>
+      </c>
+      <c r="AM21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AK21" t="s">
+      <c r="AN21" t="s">
         <v>29</v>
       </c>
-      <c r="AM21" s="2"/>
-      <c r="AN21" s="2"/>
-      <c r="AO21" s="2" t="s">
+      <c r="AP21" s="2"/>
+      <c r="AQ21" s="2"/>
+      <c r="AR21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AP21" s="2">
+      <c r="AS21" s="2">
         <v>2.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:42" ht="17">
+    <row r="22" spans="1:45" ht="17">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -2840,38 +2941,38 @@
         <v>70</v>
       </c>
       <c r="J22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.91</v>
       </c>
       <c r="K22">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L22" t="s">
         <v>57</v>
       </c>
       <c r="M22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O22">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P22">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>13.2</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="R22">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S22">
@@ -2879,15 +2980,15 @@
         <v>0.21</v>
       </c>
       <c r="T22">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U22">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V22">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W22">
@@ -2895,31 +2996,31 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.74</v>
       </c>
       <c r="Y22">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z22">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB22">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AC22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3.21952304128</v>
       </c>
       <c r="AD22">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>3.21952304128E-3</v>
       </c>
       <c r="AE22" s="11">
@@ -2938,17 +3039,25 @@
         <f t="shared" si="6"/>
         <v>0.20351232</v>
       </c>
-      <c r="AJ22" s="2" t="s">
+      <c r="AI22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AM22" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AO22" s="2" t="s">
+      <c r="AR22" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AP22" s="2">
+      <c r="AS22" s="2">
         <v>1.8E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:42" ht="17">
+    <row r="23" spans="1:45" ht="17">
       <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
@@ -2975,38 +3084,38 @@
         <v>71</v>
       </c>
       <c r="J23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.91</v>
       </c>
       <c r="K23">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L23" t="s">
         <v>57</v>
       </c>
       <c r="M23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O23">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>13.2</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="R23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="S23">
@@ -3014,15 +3123,15 @@
         <v>0.21</v>
       </c>
       <c r="T23">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U23">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V23">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W23">
@@ -3030,31 +3139,31 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.76</v>
       </c>
       <c r="Y23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z23">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AC23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3.4207432313599999</v>
       </c>
       <c r="AD23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>3.4207432313600001E-3</v>
       </c>
       <c r="AE23" s="11">
@@ -3073,15 +3182,23 @@
         <f t="shared" si="6"/>
         <v>0.15947098199999993</v>
       </c>
-      <c r="AJ23" s="2" t="s">
+      <c r="AI23">
+        <f t="shared" si="7"/>
+        <v>19657.439999999995</v>
+      </c>
+      <c r="AJ23">
+        <f t="shared" si="8"/>
+        <v>0.33979289142857128</v>
+      </c>
+      <c r="AM23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AK23" s="2">
+      <c r="AN23" s="2">
         <v>0.71</v>
       </c>
-      <c r="AM23" s="2"/>
+      <c r="AP23" s="2"/>
     </row>
-    <row r="24" spans="1:42" ht="17">
+    <row r="24" spans="1:45" ht="17">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
@@ -3108,38 +3225,38 @@
         <v>28</v>
       </c>
       <c r="J24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.91</v>
       </c>
       <c r="K24">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L24" t="s">
         <v>58</v>
       </c>
       <c r="M24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.95</v>
       </c>
       <c r="O24">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>13.2</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S24">
@@ -3147,15 +3264,15 @@
         <v>0.21</v>
       </c>
       <c r="T24">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U24">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V24">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W24">
@@ -3163,31 +3280,31 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.71</v>
       </c>
       <c r="Y24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>4.1639852800000035E-3</v>
       </c>
       <c r="Z24">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA24">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>5.2372378239999996E-4</v>
       </c>
       <c r="AB24">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>27.357383289600023</v>
       </c>
       <c r="AC24">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3.4408652503679997</v>
       </c>
       <c r="AD24">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>3.0798248539968022E-2</v>
       </c>
       <c r="AE24" s="11">
@@ -3206,16 +3323,24 @@
         <f t="shared" si="6"/>
         <v>0.20033244000000003</v>
       </c>
-      <c r="AJ24" s="2" t="s">
+      <c r="AI24">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AM24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AK24" s="2">
+      <c r="AN24" s="2">
         <v>0.75</v>
       </c>
-      <c r="AM24" s="2"/>
-      <c r="AN24" s="2"/>
+      <c r="AP24" s="2"/>
+      <c r="AQ24" s="2"/>
     </row>
-    <row r="25" spans="1:42" ht="17">
+    <row r="25" spans="1:45" ht="17">
       <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
@@ -3242,38 +3367,38 @@
         <v>65</v>
       </c>
       <c r="J25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.91</v>
       </c>
       <c r="K25">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L25" t="s">
         <v>58</v>
       </c>
       <c r="M25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.95</v>
       </c>
       <c r="O25">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>13.2</v>
       </c>
       <c r="Q25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.8E-3</v>
       </c>
       <c r="R25">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="S25">
@@ -3281,15 +3406,15 @@
         <v>0.21</v>
       </c>
       <c r="T25">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U25">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V25">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W25">
@@ -3297,31 +3422,31 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.75</v>
       </c>
       <c r="Y25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>4.3985760000000039E-3</v>
       </c>
       <c r="Z25">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA25">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>5.2372378239999996E-4</v>
       </c>
       <c r="AB25">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>30.504124560000029</v>
       </c>
       <c r="AC25">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3.6320244309439995</v>
       </c>
       <c r="AD25">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>3.4136148990944033E-2</v>
       </c>
       <c r="AE25" s="11">
@@ -3340,16 +3465,24 @@
         <f t="shared" si="6"/>
         <v>5.4375948E-2</v>
       </c>
-      <c r="AJ25" s="2" t="s">
+      <c r="AI25">
+        <f t="shared" si="7"/>
+        <v>21970.079999999998</v>
+      </c>
+      <c r="AJ25">
+        <f t="shared" si="8"/>
+        <v>0.37976852571428565</v>
+      </c>
+      <c r="AM25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AK25" s="2">
+      <c r="AN25" s="2">
         <v>0.8</v>
       </c>
-      <c r="AM25" s="2"/>
-      <c r="AN25" s="2"/>
+      <c r="AP25" s="2"/>
+      <c r="AQ25" s="2"/>
     </row>
-    <row r="26" spans="1:42">
+    <row r="26" spans="1:45">
       <c r="A26" s="2" t="s">
         <v>19</v>
       </c>
@@ -3376,38 +3509,38 @@
         <v>66</v>
       </c>
       <c r="J26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2.73</v>
       </c>
       <c r="K26">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L26" t="s">
         <v>58</v>
       </c>
       <c r="M26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.95</v>
       </c>
       <c r="O26">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>39.5</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="R26">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S26">
@@ -3415,15 +3548,15 @@
         <v>0.21</v>
       </c>
       <c r="T26">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U26">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V26">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W26">
@@ -3431,31 +3564,31 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X26">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.8</v>
       </c>
       <c r="Y26">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1.4075443200000013E-2</v>
       </c>
       <c r="Z26">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.5711713472E-3</v>
       </c>
       <c r="AB26">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>102.75073536000009</v>
       </c>
       <c r="AC26">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>11.46955083456</v>
       </c>
       <c r="AD26">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.11422028619456009</v>
       </c>
       <c r="AE26" s="11">
@@ -3474,16 +3607,24 @@
         <f t="shared" si="6"/>
         <v>0.27595094999999997</v>
       </c>
-      <c r="AJ26" s="2" t="s">
+      <c r="AI26">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AM26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AK26" s="2">
+      <c r="AN26" s="2">
         <v>0.78</v>
       </c>
-      <c r="AM26" s="2"/>
-      <c r="AN26" s="2"/>
+      <c r="AP26" s="2"/>
+      <c r="AQ26" s="2"/>
     </row>
-    <row r="27" spans="1:42">
+    <row r="27" spans="1:45">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -3510,38 +3651,38 @@
         <v>67</v>
       </c>
       <c r="J27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.34</v>
       </c>
       <c r="K27">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L27" t="s">
         <v>58</v>
       </c>
       <c r="M27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.95</v>
       </c>
       <c r="O27">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="R27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="S27">
@@ -3549,15 +3690,15 @@
         <v>0.21</v>
       </c>
       <c r="T27">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U27">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V27">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W27">
@@ -3565,31 +3706,31 @@
         <v>2E-3</v>
       </c>
       <c r="X27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.78</v>
       </c>
       <c r="Y27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1.709160960000002E-3</v>
       </c>
       <c r="Z27">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB27">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>13.100718758400015</v>
       </c>
       <c r="AC27">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1.4998643399039999</v>
       </c>
       <c r="AD27">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1.4600583098304016E-2</v>
       </c>
       <c r="AE27" s="11">
@@ -3608,16 +3749,24 @@
         <f t="shared" si="6"/>
         <v>0.1416492</v>
       </c>
-      <c r="AJ27" s="2" t="s">
+      <c r="AI27">
+        <f t="shared" si="7"/>
+        <v>12877.199999999999</v>
+      </c>
+      <c r="AJ27">
+        <f t="shared" si="8"/>
+        <v>0.22259159999999997</v>
+      </c>
+      <c r="AM27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AK27" s="2">
+      <c r="AN27" s="2">
         <v>0.74</v>
       </c>
-      <c r="AM27" s="2"/>
-      <c r="AN27" s="2"/>
+      <c r="AP27" s="2"/>
+      <c r="AQ27" s="2"/>
     </row>
-    <row r="28" spans="1:42">
+    <row r="28" spans="1:45">
       <c r="A28" s="2" t="s">
         <v>21</v>
       </c>
@@ -3644,38 +3793,38 @@
         <v>68</v>
       </c>
       <c r="J28">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2.73</v>
       </c>
       <c r="K28">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L28" t="s">
         <v>58</v>
       </c>
       <c r="M28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N28">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.95</v>
       </c>
       <c r="O28">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>39.5</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="R28">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S28">
@@ -3683,15 +3832,15 @@
         <v>0.21</v>
       </c>
       <c r="T28">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U28">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V28">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W28">
@@ -3699,31 +3848,31 @@
         <v>2E-3</v>
       </c>
       <c r="X28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.74</v>
       </c>
       <c r="Y28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1.3019784960000013E-2</v>
       </c>
       <c r="Z28">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.5711713472E-3</v>
       </c>
       <c r="AB28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>104.5488732288001</v>
       </c>
       <c r="AC28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>12.616505918016001</v>
       </c>
       <c r="AD28">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.11716537914681611</v>
       </c>
       <c r="AE28" s="11">
@@ -3742,16 +3891,24 @@
         <f t="shared" si="6"/>
         <v>0.61755919499999989</v>
       </c>
-      <c r="AJ28" s="2" t="s">
+      <c r="AI28">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AM28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AK28" s="2">
+      <c r="AN28" s="2">
         <v>0.7</v>
       </c>
-      <c r="AM28" s="2"/>
-      <c r="AN28" s="2"/>
+      <c r="AP28" s="2"/>
+      <c r="AQ28" s="2"/>
     </row>
-    <row r="29" spans="1:42">
+    <row r="29" spans="1:45">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
@@ -3778,38 +3935,38 @@
         <v>69</v>
       </c>
       <c r="J29">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.91</v>
       </c>
       <c r="K29">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L29" t="s">
         <v>58</v>
       </c>
       <c r="M29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N29">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.95</v>
       </c>
       <c r="O29">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>13.2</v>
       </c>
       <c r="Q29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="S29">
@@ -3817,15 +3974,15 @@
         <v>0.21</v>
       </c>
       <c r="T29">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U29">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V29">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W29">
@@ -3833,31 +3990,31 @@
         <v>2E-3</v>
       </c>
       <c r="X29">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.7</v>
       </c>
       <c r="Y29">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>4.1053376000000034E-3</v>
       </c>
       <c r="Z29">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>5.2372378239999996E-4</v>
       </c>
       <c r="AB29">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>34.464309152000027</v>
       </c>
       <c r="AC29">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>4.396661153248</v>
       </c>
       <c r="AD29">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>3.8860970305248023E-2</v>
       </c>
       <c r="AE29" s="11">
@@ -3876,16 +4033,24 @@
         <f t="shared" si="6"/>
         <v>0.25598033999999997</v>
       </c>
-      <c r="AJ29" s="2" t="s">
+      <c r="AI29">
+        <f t="shared" si="7"/>
+        <v>26595.359999999997</v>
+      </c>
+      <c r="AJ29">
+        <f t="shared" si="8"/>
+        <v>0.45971979428571424</v>
+      </c>
+      <c r="AM29" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AK29" s="2">
+      <c r="AN29" s="2">
         <v>0.74</v>
       </c>
-      <c r="AM29" s="2"/>
-      <c r="AN29" s="2"/>
+      <c r="AP29" s="2"/>
+      <c r="AQ29" s="2"/>
     </row>
-    <row r="30" spans="1:42">
+    <row r="30" spans="1:45">
       <c r="A30" s="2" t="s">
         <v>64</v>
       </c>
@@ -3912,38 +4077,38 @@
         <v>70</v>
       </c>
       <c r="J30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.34</v>
       </c>
       <c r="K30">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L30" t="s">
         <v>58</v>
       </c>
       <c r="M30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.95</v>
       </c>
       <c r="O30">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="Q30">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1.8E-3</v>
       </c>
       <c r="R30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S30">
@@ -3951,15 +4116,15 @@
         <v>0.21</v>
       </c>
       <c r="T30">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U30">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V30">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W30">
@@ -3967,31 +4132,31 @@
         <v>2E-3</v>
       </c>
       <c r="X30">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.74</v>
       </c>
       <c r="Y30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1.6215116800000018E-3</v>
       </c>
       <c r="Z30">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB30">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>14.204442316800016</v>
       </c>
       <c r="AC30">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1.7141306741760001</v>
       </c>
       <c r="AD30">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1.5918572990976015E-2</v>
       </c>
       <c r="AE30" s="11">
@@ -4010,141 +4175,149 @@
         <f t="shared" si="6"/>
         <v>3.6424079999999998E-2</v>
       </c>
-      <c r="AJ30" s="2" t="s">
+      <c r="AI30">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AM30" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AK30" s="2">
+      <c r="AN30" s="2">
         <v>0.76</v>
       </c>
-      <c r="AM30" s="2"/>
-      <c r="AN30" s="2"/>
+      <c r="AP30" s="2"/>
+      <c r="AQ30" s="2"/>
     </row>
-    <row r="31" spans="1:42">
+    <row r="31" spans="1:45">
       <c r="E31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="AO31" t="s">
+      <c r="AR31" t="s">
         <v>96</v>
       </c>
-      <c r="AP31" t="s">
+      <c r="AS31" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:42">
+    <row r="32" spans="1:45">
       <c r="E32" s="2"/>
-      <c r="AJ32" s="2" t="s">
+      <c r="AM32" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AO32" t="s">
+      <c r="AR32" t="s">
         <v>97</v>
       </c>
-      <c r="AP32" t="s">
+      <c r="AS32" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:42">
+    <row r="33" spans="1:45">
       <c r="E33" s="2"/>
-      <c r="AJ33">
+      <c r="AM33">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="AO33" t="s">
+      <c r="AR33" t="s">
         <v>98</v>
       </c>
-      <c r="AP33" t="s">
+      <c r="AS33" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:42">
+    <row r="34" spans="1:45">
       <c r="E34" s="2"/>
-      <c r="AO34" t="s">
+      <c r="AR34" t="s">
         <v>99</v>
       </c>
-      <c r="AP34" t="s">
+      <c r="AS34" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:42">
+    <row r="35" spans="1:45">
       <c r="E35" s="2"/>
-      <c r="AJ35" t="s">
+      <c r="AM35" t="s">
         <v>31</v>
       </c>
-      <c r="AO35" t="s">
+      <c r="AR35" t="s">
         <v>100</v>
       </c>
-      <c r="AP35" t="s">
+      <c r="AS35" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:42">
+    <row r="36" spans="1:45">
       <c r="E36" s="2"/>
-      <c r="AJ36" t="s">
+      <c r="AM36" t="s">
         <v>32</v>
       </c>
-      <c r="AO36" t="s">
+      <c r="AR36" t="s">
         <v>101</v>
       </c>
-      <c r="AP36" t="s">
+      <c r="AS36" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:42">
+    <row r="37" spans="1:45">
       <c r="E37" s="2"/>
-      <c r="AJ37" t="s">
+      <c r="AM37" t="s">
         <v>92</v>
       </c>
-      <c r="AK37">
+      <c r="AN37">
         <v>0.66</v>
       </c>
-      <c r="AO37" t="s">
+      <c r="AR37" t="s">
         <v>102</v>
       </c>
-      <c r="AP37" t="s">
+      <c r="AS37" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:42">
+    <row r="38" spans="1:45">
       <c r="E38" s="2"/>
-      <c r="AJ38">
+      <c r="AM38">
         <v>11</v>
       </c>
-      <c r="AK38">
+      <c r="AN38">
         <v>0.68</v>
       </c>
-      <c r="AO38" t="s">
+      <c r="AR38" t="s">
         <v>103</v>
       </c>
-      <c r="AP38" t="s">
+      <c r="AS38" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:42">
-      <c r="AJ39">
+    <row r="39" spans="1:45">
+      <c r="AM39">
         <v>12</v>
       </c>
-      <c r="AK39">
+      <c r="AN39">
         <v>0.7</v>
       </c>
-      <c r="AO39" t="s">
+      <c r="AR39" t="s">
         <v>104</v>
       </c>
-      <c r="AP39" t="s">
+      <c r="AS39" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:42">
-      <c r="AJ40">
+    <row r="40" spans="1:45">
+      <c r="AM40">
         <v>13</v>
       </c>
-      <c r="AK40">
+      <c r="AN40">
         <v>0.71</v>
       </c>
-      <c r="AO40" t="s">
+      <c r="AR40" t="s">
         <v>105</v>
       </c>
-      <c r="AP40" t="s">
+      <c r="AS40" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:42" ht="17">
+    <row r="41" spans="1:45" ht="17">
       <c r="A41" s="3" t="s">
         <v>3</v>
       </c>
@@ -4167,11 +4340,11 @@
         <v>67</v>
       </c>
       <c r="J41">
-        <f>VLOOKUP(A41, $AJ$11:$AK$18,2,FALSE)</f>
+        <f>VLOOKUP(A41, $AM$11:$AN$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K41">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L41" t="s">
@@ -4186,15 +4359,15 @@
         <v>0.95</v>
       </c>
       <c r="O41">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P41">
-        <f>VLOOKUP(A41, $AJ$11:$AL$18,3,FALSE)</f>
+        <f>VLOOKUP(A41, $AM$11:$AO$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q41">
-        <f>VLOOKUP(E41,$AO$10:$AP$22,2,FALSE)</f>
+        <f>VLOOKUP(E41,$AR$10:$AS$22,2,FALSE)</f>
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="R41">
@@ -4202,19 +4375,19 @@
         <v>1</v>
       </c>
       <c r="T41">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U41">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V41">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="X41">
-        <f>VLOOKUP(F41, $AJ$37:$AK$55, 2, FALSE)</f>
+        <f>VLOOKUP(F41, $AM$37:$AN$55, 2, FALSE)</f>
         <v>0.66</v>
       </c>
       <c r="Y41">
@@ -4222,7 +4395,7 @@
         <v>1.1612240640000012E-2</v>
       </c>
       <c r="Z41">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA41">
@@ -4241,14 +4414,14 @@
         <f>(AB41+AC41)*10^-3</f>
         <v>2.4059726876640024E-2</v>
       </c>
-      <c r="AJ41">
+      <c r="AM41">
         <v>14</v>
       </c>
-      <c r="AK41">
+      <c r="AN41">
         <v>0.73</v>
       </c>
     </row>
-    <row r="42" spans="1:42" ht="17">
+    <row r="42" spans="1:45" ht="17">
       <c r="A42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4271,11 +4444,11 @@
         <v>67</v>
       </c>
       <c r="J42">
-        <f>VLOOKUP(A42, $AJ$11:$AK$18,2,FALSE)</f>
+        <f>VLOOKUP(A42, $AM$11:$AN$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K42">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L42" t="s">
@@ -4290,15 +4463,15 @@
         <v>0.95</v>
       </c>
       <c r="O42">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P42">
-        <f>VLOOKUP(A42, $AJ$11:$AL$18,3,FALSE)</f>
+        <f>VLOOKUP(A42, $AM$11:$AO$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q42">
-        <f>VLOOKUP(E42,$AO$10:$AP$22,2,FALSE)</f>
+        <f>VLOOKUP(E42,$AR$10:$AS$22,2,FALSE)</f>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R42">
@@ -4306,19 +4479,19 @@
         <v>0</v>
       </c>
       <c r="T42">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U42">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V42">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="X42">
-        <f t="shared" ref="X42:X60" si="19">VLOOKUP(F42, $AJ$37:$AK$55, 2, FALSE)</f>
+        <f t="shared" ref="X42:X60" si="21">VLOOKUP(F42, $AM$37:$AN$55, 2, FALSE)</f>
         <v>0.68</v>
       </c>
       <c r="Y42">
@@ -4326,7 +4499,7 @@
         <v>1.1964126720000011E-2</v>
       </c>
       <c r="Z42">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA42">
@@ -4345,14 +4518,14 @@
         <f>(AB42+AC42)*10^-3</f>
         <v>2.9642302767168026E-2</v>
       </c>
-      <c r="AJ42">
+      <c r="AM42">
         <v>15</v>
       </c>
-      <c r="AK42">
+      <c r="AN42">
         <v>0.74</v>
       </c>
     </row>
-    <row r="43" spans="1:42" ht="17">
+    <row r="43" spans="1:45" ht="17">
       <c r="A43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4375,88 +4548,88 @@
         <v>67</v>
       </c>
       <c r="J43">
-        <f t="shared" ref="J43:J60" si="20">VLOOKUP(A43, $AJ$11:$AK$18,2,FALSE)</f>
+        <f t="shared" ref="J43:J60" si="22">VLOOKUP(A43, $AM$11:$AN$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K43">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L43" t="s">
         <v>58</v>
       </c>
       <c r="M43">
-        <f t="shared" ref="M43:M60" si="21">1-N43</f>
+        <f t="shared" ref="M43:M60" si="23">1-N43</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="N43">
-        <f t="shared" ref="N43:N60" si="22">IF(L43="yes", 1, 0.95)</f>
+        <f t="shared" ref="N43:N60" si="24">IF(L43="yes", 1, 0.95)</f>
         <v>0.95</v>
       </c>
       <c r="O43">
-        <f>$AK$4</f>
+        <f>$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P43">
-        <f t="shared" ref="P43:P60" si="23">VLOOKUP(A43, $AJ$11:$AL$18,3,FALSE)</f>
+        <f t="shared" ref="P43:P60" si="25">VLOOKUP(A43, $AM$11:$AO$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q43">
-        <f t="shared" ref="Q43:Q60" si="24">VLOOKUP(E43,$AO$10:$AP$22,2,FALSE)</f>
+        <f t="shared" ref="Q43:Q60" si="26">VLOOKUP(E43,$AR$10:$AS$22,2,FALSE)</f>
         <v>1.8E-3</v>
       </c>
       <c r="R43">
-        <f t="shared" ref="R43:R60" si="25">IF(D43="yes", 1, 0)</f>
+        <f t="shared" ref="R43:R60" si="27">IF(D43="yes", 1, 0)</f>
         <v>1</v>
       </c>
       <c r="T43">
-        <f>$AN$3</f>
+        <f>$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U43">
-        <f>$AN$4</f>
-        <v>0.11</v>
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="V43">
-        <f>$AK$5</f>
+        <f>$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="X43">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.7</v>
       </c>
       <c r="Y43">
-        <f t="shared" ref="Y43:Y60" si="26">J43*K43*M43*X43*V43</f>
+        <f t="shared" ref="Y43:Y60" si="28">J43*K43*M43*X43*V43</f>
         <v>1.231601280000001E-2</v>
       </c>
       <c r="Z43">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA43">
-        <f t="shared" ref="AA43:AA60" si="27">J43*K43*N43*Z43*V43</f>
+        <f t="shared" ref="AA43:AA60" si="29">J43*K43*N43*Z43*V43</f>
         <v>1.5711713472E-3</v>
       </c>
       <c r="AB43">
-        <f t="shared" ref="AB43:AB60" si="28">C43*Y43*365</f>
+        <f t="shared" ref="AB43:AB60" si="30">C43*Y43*365</f>
         <v>31.467412704000026</v>
       </c>
       <c r="AC43">
-        <f t="shared" ref="AC43:AC60" si="29">C43*AA43*365</f>
+        <f t="shared" ref="AC43:AC60" si="31">C43*AA43*365</f>
         <v>4.0143427920960004</v>
       </c>
       <c r="AD43">
-        <f t="shared" ref="AD43:AD60" si="30">(AB43+AC43)*10^-3</f>
+        <f t="shared" ref="AD43:AD60" si="32">(AB43+AC43)*10^-3</f>
         <v>3.5481755496096029E-2</v>
       </c>
-      <c r="AJ43">
+      <c r="AM43">
         <v>16</v>
       </c>
-      <c r="AK43">
+      <c r="AN43">
         <v>0.75</v>
       </c>
     </row>
-    <row r="44" spans="1:42" ht="17">
+    <row r="44" spans="1:45" ht="17">
       <c r="A44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4479,88 +4652,88 @@
         <v>67</v>
       </c>
       <c r="J44">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2.73</v>
       </c>
       <c r="K44">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L44" t="s">
         <v>58</v>
       </c>
       <c r="M44">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="24"/>
+        <v>0.95</v>
+      </c>
+      <c r="O44">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P44">
+        <f t="shared" si="25"/>
+        <v>39.5</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="26"/>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="R44">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U44">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V44">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X44">
         <f t="shared" si="21"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N44">
-        <f t="shared" si="22"/>
-        <v>0.95</v>
-      </c>
-      <c r="O44">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P44">
-        <f t="shared" si="23"/>
-        <v>39.5</v>
-      </c>
-      <c r="Q44">
-        <f t="shared" si="24"/>
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="R44">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="T44">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U44">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V44">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X44">
-        <f t="shared" si="19"/>
         <v>0.71</v>
       </c>
       <c r="Y44">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.2491955840000011E-2</v>
       </c>
       <c r="Z44">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA44">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.5711713472E-3</v>
       </c>
       <c r="AB44">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>36.476511052800035</v>
       </c>
       <c r="AC44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>4.5878203338240002</v>
       </c>
       <c r="AD44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>4.1064331386624034E-2</v>
       </c>
-      <c r="AJ44">
+      <c r="AM44">
         <v>17</v>
       </c>
-      <c r="AK44">
+      <c r="AN44">
         <v>0.76</v>
       </c>
     </row>
-    <row r="45" spans="1:42" ht="17">
+    <row r="45" spans="1:45" ht="17">
       <c r="A45" s="3" t="s">
         <v>25</v>
       </c>
@@ -4583,88 +4756,88 @@
         <v>67</v>
       </c>
       <c r="J45">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.34</v>
       </c>
       <c r="K45">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L45" t="s">
         <v>58</v>
       </c>
       <c r="M45">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="24"/>
+        <v>0.95</v>
+      </c>
+      <c r="O45">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P45">
+        <f t="shared" si="25"/>
+        <v>7</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="26"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R45">
+        <f t="shared" si="27"/>
+        <v>1</v>
+      </c>
+      <c r="T45">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U45">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V45">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X45">
         <f t="shared" si="21"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N45">
-        <f t="shared" si="22"/>
-        <v>0.95</v>
-      </c>
-      <c r="O45">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P45">
-        <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="Q45">
-        <f t="shared" si="24"/>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="R45">
-        <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="T45">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U45">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V45">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X45">
-        <f t="shared" si="19"/>
         <v>0.73</v>
       </c>
       <c r="Y45">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.5995993600000015E-3</v>
       </c>
       <c r="Z45">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA45">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB45">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>5.254683897600005</v>
       </c>
       <c r="AC45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.64279900281600011</v>
       </c>
       <c r="AD45">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5.8974829004160047E-3</v>
       </c>
-      <c r="AJ45">
+      <c r="AM45">
         <v>18</v>
       </c>
-      <c r="AK45">
+      <c r="AN45">
         <v>0.77</v>
       </c>
     </row>
-    <row r="46" spans="1:42" ht="17">
+    <row r="46" spans="1:45" ht="17">
       <c r="A46" s="3" t="s">
         <v>25</v>
       </c>
@@ -4687,88 +4860,88 @@
         <v>28</v>
       </c>
       <c r="J46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.34</v>
       </c>
       <c r="K46">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L46" t="s">
         <v>58</v>
       </c>
       <c r="M46">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="24"/>
+        <v>0.95</v>
+      </c>
+      <c r="O46">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P46">
+        <f t="shared" si="25"/>
+        <v>7</v>
+      </c>
+      <c r="Q46">
+        <f t="shared" si="26"/>
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="R46">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U46">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V46">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X46">
         <f t="shared" si="21"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N46">
-        <f t="shared" si="22"/>
-        <v>0.95</v>
-      </c>
-      <c r="O46">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P46">
-        <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="Q46">
-        <f t="shared" si="24"/>
-        <v>1.9900000000000001E-2</v>
-      </c>
-      <c r="R46">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="T46">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U46">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V46">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X46">
-        <f t="shared" si="19"/>
         <v>0.74</v>
       </c>
       <c r="Y46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.6215116800000018E-3</v>
       </c>
       <c r="Z46">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA46">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>5.9185176320000075</v>
       </c>
       <c r="AC46">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.71422111424000012</v>
       </c>
       <c r="AD46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>6.6327387462400073E-3</v>
       </c>
-      <c r="AJ46">
+      <c r="AM46">
         <v>19</v>
       </c>
-      <c r="AK46">
+      <c r="AN46">
         <v>0.77</v>
       </c>
     </row>
-    <row r="47" spans="1:42" ht="17">
+    <row r="47" spans="1:45" ht="17">
       <c r="A47" s="3" t="s">
         <v>25</v>
       </c>
@@ -4791,88 +4964,88 @@
         <v>65</v>
       </c>
       <c r="J47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.34</v>
       </c>
       <c r="K47">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L47" t="s">
         <v>58</v>
       </c>
       <c r="M47">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="24"/>
+        <v>0.95</v>
+      </c>
+      <c r="O47">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P47">
+        <f t="shared" si="25"/>
+        <v>7</v>
+      </c>
+      <c r="Q47">
+        <f t="shared" si="26"/>
+        <v>5.3E-3</v>
+      </c>
+      <c r="R47">
+        <f t="shared" si="27"/>
+        <v>1</v>
+      </c>
+      <c r="T47">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U47">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V47">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X47">
         <f t="shared" si="21"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N47">
-        <f t="shared" si="22"/>
-        <v>0.95</v>
-      </c>
-      <c r="O47">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P47">
-        <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="Q47">
-        <f t="shared" si="24"/>
-        <v>5.3E-3</v>
-      </c>
-      <c r="R47">
-        <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="T47">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U47">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V47">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X47">
-        <f t="shared" si="19"/>
         <v>0.75</v>
       </c>
       <c r="Y47">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.6434240000000016E-3</v>
       </c>
       <c r="Z47">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>6.5983473600000062</v>
       </c>
       <c r="AC47">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.78564322566400013</v>
       </c>
       <c r="AD47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>7.383990585664006E-3</v>
       </c>
-      <c r="AJ47">
+      <c r="AM47">
         <v>20</v>
       </c>
-      <c r="AK47">
+      <c r="AN47">
         <v>0.78</v>
       </c>
     </row>
-    <row r="48" spans="1:42" ht="17">
+    <row r="48" spans="1:45" ht="17">
       <c r="A48" s="3" t="s">
         <v>25</v>
       </c>
@@ -4895,88 +5068,88 @@
         <v>66</v>
       </c>
       <c r="J48">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.34</v>
       </c>
       <c r="K48">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L48" t="s">
         <v>58</v>
       </c>
       <c r="M48">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="24"/>
+        <v>0.95</v>
+      </c>
+      <c r="O48">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P48">
+        <f t="shared" si="25"/>
+        <v>7</v>
+      </c>
+      <c r="Q48">
+        <f t="shared" si="26"/>
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="R48">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U48">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V48">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X48">
         <f t="shared" si="21"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N48">
-        <f t="shared" si="22"/>
-        <v>0.95</v>
-      </c>
-      <c r="O48">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P48">
-        <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="Q48">
-        <f t="shared" si="24"/>
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="R48">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U48">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V48">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X48">
-        <f t="shared" si="19"/>
         <v>0.76</v>
       </c>
       <c r="Y48">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.6653363200000019E-3</v>
       </c>
       <c r="Z48">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA48">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB48">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7.2941730816000083</v>
       </c>
       <c r="AC48">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.85706533708800003</v>
       </c>
       <c r="AD48">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>8.1512384186880078E-3</v>
       </c>
-      <c r="AJ48">
+      <c r="AM48">
         <v>21</v>
       </c>
-      <c r="AK48">
+      <c r="AN48">
         <v>0.78</v>
       </c>
     </row>
-    <row r="49" spans="1:37" ht="17">
+    <row r="49" spans="1:40" ht="17">
       <c r="A49" s="3" t="s">
         <v>25</v>
       </c>
@@ -4999,88 +5172,88 @@
         <v>67</v>
       </c>
       <c r="J49">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.34</v>
       </c>
       <c r="K49">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L49" t="s">
         <v>58</v>
       </c>
       <c r="M49">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="24"/>
+        <v>0.95</v>
+      </c>
+      <c r="O49">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P49">
+        <f t="shared" si="25"/>
+        <v>7</v>
+      </c>
+      <c r="Q49">
+        <f t="shared" si="26"/>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="R49">
+        <f t="shared" si="27"/>
+        <v>1</v>
+      </c>
+      <c r="T49">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U49">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V49">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X49">
         <f t="shared" si="21"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N49">
-        <f t="shared" si="22"/>
-        <v>0.95</v>
-      </c>
-      <c r="O49">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P49">
-        <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="Q49">
-        <f t="shared" si="24"/>
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="R49">
-        <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="T49">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U49">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V49">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X49">
-        <f t="shared" si="19"/>
         <v>0.77</v>
       </c>
       <c r="Y49">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.6872486400000017E-3</v>
       </c>
       <c r="Z49">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA49">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB49">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>8.0059947968000085</v>
       </c>
       <c r="AC49">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.92848744851200005</v>
       </c>
       <c r="AD49">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>8.9344822453120091E-3</v>
       </c>
-      <c r="AJ49">
+      <c r="AM49">
         <v>22</v>
       </c>
-      <c r="AK49">
+      <c r="AN49">
         <v>0.78</v>
       </c>
     </row>
-    <row r="50" spans="1:37" ht="17">
+    <row r="50" spans="1:40" ht="17">
       <c r="A50" s="3" t="s">
         <v>25</v>
       </c>
@@ -5103,88 +5276,88 @@
         <v>68</v>
       </c>
       <c r="J50">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.34</v>
       </c>
       <c r="K50">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L50" t="s">
         <v>58</v>
       </c>
       <c r="M50">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="N50">
+        <f t="shared" si="24"/>
+        <v>0.95</v>
+      </c>
+      <c r="O50">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P50">
+        <f t="shared" si="25"/>
+        <v>7</v>
+      </c>
+      <c r="Q50">
+        <f t="shared" si="26"/>
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="R50">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U50">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V50">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X50">
         <f t="shared" si="21"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="N50">
-        <f t="shared" si="22"/>
-        <v>0.95</v>
-      </c>
-      <c r="O50">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P50">
-        <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="Q50">
-        <f t="shared" si="24"/>
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="R50">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="T50">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U50">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V50">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X50">
-        <f t="shared" si="19"/>
         <v>0.77</v>
       </c>
       <c r="Y50">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.6872486400000017E-3</v>
       </c>
       <c r="Z50">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.9567701760000002E-4</v>
       </c>
       <c r="AB50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>8.6218405504000089</v>
       </c>
       <c r="AC50">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.99990955993600006</v>
       </c>
       <c r="AD50">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>9.6217501103360095E-3</v>
       </c>
-      <c r="AJ50">
+      <c r="AM50">
         <v>23</v>
       </c>
-      <c r="AK50">
+      <c r="AN50">
         <v>0.79</v>
       </c>
     </row>
-    <row r="51" spans="1:37" ht="17">
+    <row r="51" spans="1:40" ht="17">
       <c r="A51" s="3" t="s">
         <v>25</v>
       </c>
@@ -5207,88 +5380,88 @@
         <v>69</v>
       </c>
       <c r="J51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.34</v>
       </c>
       <c r="K51">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L51" t="s">
         <v>57</v>
       </c>
       <c r="M51">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="O51">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P51">
+        <f t="shared" si="25"/>
+        <v>7</v>
+      </c>
+      <c r="Q51">
+        <f t="shared" si="26"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="R51">
+        <f t="shared" si="27"/>
+        <v>1</v>
+      </c>
+      <c r="T51">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U51">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V51">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X51">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="O51">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P51">
-        <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="Q51">
-        <f t="shared" si="24"/>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="R51">
-        <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="T51">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U51">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V51">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X51">
-        <f t="shared" si="19"/>
         <v>0.78</v>
       </c>
       <c r="Y51">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Z51">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA51">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB51">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AC51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1.1277175488000002</v>
       </c>
       <c r="AD51">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1.1277175488000003E-3</v>
       </c>
-      <c r="AJ51">
+      <c r="AM51">
         <v>24</v>
       </c>
-      <c r="AK51">
+      <c r="AN51">
         <v>0.79</v>
       </c>
     </row>
-    <row r="52" spans="1:37" ht="17">
+    <row r="52" spans="1:40" ht="17">
       <c r="A52" s="3" t="s">
         <v>24</v>
       </c>
@@ -5311,88 +5484,88 @@
         <v>70</v>
       </c>
       <c r="J52">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.91</v>
       </c>
       <c r="K52">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L52" t="s">
         <v>57</v>
       </c>
       <c r="M52">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="O52">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P52">
+        <f t="shared" si="25"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" si="26"/>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="R52">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U52">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V52">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X52">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="O52">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P52">
-        <f t="shared" si="23"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q52">
-        <f t="shared" si="24"/>
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="R52">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="T52">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U52">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V52">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X52">
-        <f t="shared" si="19"/>
         <v>0.78</v>
       </c>
       <c r="Y52">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Z52">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA52">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB52">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AC52">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>3.21952304128</v>
       </c>
       <c r="AD52">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>3.21952304128E-3</v>
       </c>
-      <c r="AJ52">
+      <c r="AM52">
         <v>25</v>
       </c>
-      <c r="AK52">
+      <c r="AN52">
         <v>0.79</v>
       </c>
     </row>
-    <row r="53" spans="1:37" ht="17">
+    <row r="53" spans="1:40" ht="17">
       <c r="A53" s="3" t="s">
         <v>24</v>
       </c>
@@ -5415,88 +5588,88 @@
         <v>71</v>
       </c>
       <c r="J53">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.91</v>
       </c>
       <c r="K53">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L53" t="s">
         <v>57</v>
       </c>
       <c r="M53">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="O53">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P53">
+        <f t="shared" si="25"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="26"/>
+        <v>1.8E-3</v>
+      </c>
+      <c r="R53">
+        <f t="shared" si="27"/>
+        <v>1</v>
+      </c>
+      <c r="T53">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U53">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V53">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X53">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="N53">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="O53">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P53">
-        <f t="shared" si="23"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q53">
-        <f t="shared" si="24"/>
-        <v>1.8E-3</v>
-      </c>
-      <c r="R53">
-        <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="T53">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U53">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V53">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X53">
-        <f t="shared" si="19"/>
         <v>0.78</v>
       </c>
       <c r="Y53">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Z53">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA53">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB53">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AC53">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>3.4207432313599999</v>
       </c>
       <c r="AD53">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>3.4207432313600001E-3</v>
       </c>
-      <c r="AJ53">
+      <c r="AM53">
         <v>26</v>
       </c>
-      <c r="AK53">
+      <c r="AN53">
         <v>0.79</v>
       </c>
     </row>
-    <row r="54" spans="1:37" ht="17">
+    <row r="54" spans="1:40" ht="17">
       <c r="A54" s="3" t="s">
         <v>24</v>
       </c>
@@ -5519,88 +5692,88 @@
         <v>28</v>
       </c>
       <c r="J54">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.91</v>
       </c>
       <c r="K54">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L54" t="s">
         <v>57</v>
       </c>
       <c r="M54">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="O54">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P54">
+        <f t="shared" si="25"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q54">
+        <f t="shared" si="26"/>
+        <v>1.8E-3</v>
+      </c>
+      <c r="R54">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U54">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V54">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X54">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="N54">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="O54">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P54">
-        <f t="shared" si="23"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q54">
-        <f t="shared" si="24"/>
-        <v>1.8E-3</v>
-      </c>
-      <c r="R54">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="T54">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U54">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V54">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X54">
-        <f t="shared" si="19"/>
         <v>0.79</v>
       </c>
       <c r="Y54">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Z54">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA54">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB54">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AC54">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>3.6219634214399998</v>
       </c>
       <c r="AD54">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>3.6219634214399998E-3</v>
       </c>
-      <c r="AJ54">
+      <c r="AM54">
         <v>27</v>
       </c>
-      <c r="AK54">
+      <c r="AN54">
         <v>0.8</v>
       </c>
     </row>
-    <row r="55" spans="1:37" ht="17">
+    <row r="55" spans="1:40" ht="17">
       <c r="A55" s="3" t="s">
         <v>24</v>
       </c>
@@ -5623,88 +5796,88 @@
         <v>65</v>
       </c>
       <c r="J55">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.91</v>
       </c>
       <c r="K55">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L55" t="s">
         <v>57</v>
       </c>
       <c r="M55">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="O55">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P55">
+        <f t="shared" si="25"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="26"/>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="R55">
+        <f t="shared" si="27"/>
+        <v>1</v>
+      </c>
+      <c r="T55">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U55">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V55">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X55">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="N55">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="O55">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P55">
-        <f t="shared" si="23"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q55">
-        <f t="shared" si="24"/>
-        <v>2.8999999999999998E-3</v>
-      </c>
-      <c r="R55">
-        <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="T55">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U55">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V55">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X55">
-        <f t="shared" si="19"/>
         <v>0.79</v>
       </c>
       <c r="Y55">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Z55">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA55">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB55">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AC55">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>3.8231836115200006</v>
       </c>
       <c r="AD55">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>3.8231836115200008E-3</v>
       </c>
-      <c r="AJ55" t="s">
+      <c r="AM55" t="s">
         <v>93</v>
       </c>
-      <c r="AK55">
+      <c r="AN55">
         <v>0.8</v>
       </c>
     </row>
-    <row r="56" spans="1:37">
+    <row r="56" spans="1:40">
       <c r="A56" s="2" t="s">
         <v>19</v>
       </c>
@@ -5727,82 +5900,82 @@
         <v>66</v>
       </c>
       <c r="J56">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2.73</v>
       </c>
       <c r="K56">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L56" t="s">
         <v>57</v>
       </c>
       <c r="M56">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="O56">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P56">
+        <f t="shared" si="25"/>
+        <v>39.5</v>
+      </c>
+      <c r="Q56">
+        <f t="shared" si="26"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R56">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U56">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V56">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X56">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="O56">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P56">
-        <f t="shared" si="23"/>
-        <v>39.5</v>
-      </c>
-      <c r="Q56">
-        <f t="shared" si="24"/>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="R56">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="T56">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U56">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V56">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X56">
-        <f t="shared" si="19"/>
         <v>0.79</v>
       </c>
       <c r="Y56">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Z56">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA56">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.6538645760000002E-3</v>
       </c>
       <c r="AB56">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AC56">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>12.0732114048</v>
       </c>
       <c r="AD56">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1.2073211404800001E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:37">
+    <row r="57" spans="1:40">
       <c r="A57" s="2" t="s">
         <v>20</v>
       </c>
@@ -5825,82 +5998,82 @@
         <v>67</v>
       </c>
       <c r="J57">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.34</v>
       </c>
       <c r="K57">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L57" t="s">
         <v>57</v>
       </c>
       <c r="M57">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="O57">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P57">
+        <f t="shared" si="25"/>
+        <v>7</v>
+      </c>
+      <c r="Q57">
+        <f t="shared" si="26"/>
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="R57">
+        <f t="shared" si="27"/>
+        <v>1</v>
+      </c>
+      <c r="T57">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U57">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V57">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X57">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="N57">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="O57">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P57">
-        <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="Q57">
-        <f t="shared" si="24"/>
-        <v>1.9900000000000001E-2</v>
-      </c>
-      <c r="R57">
-        <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="T57">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U57">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V57">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X57">
-        <f t="shared" si="19"/>
         <v>0.79</v>
       </c>
       <c r="Y57">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Z57">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA57">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB57">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AC57">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1.57880456832</v>
       </c>
       <c r="AD57">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1.5788045683200001E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:37">
+    <row r="58" spans="1:40">
       <c r="A58" s="2" t="s">
         <v>21</v>
       </c>
@@ -5923,82 +6096,82 @@
         <v>68</v>
       </c>
       <c r="J58">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2.73</v>
       </c>
       <c r="K58">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L58" t="s">
         <v>57</v>
       </c>
       <c r="M58">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="O58">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P58">
+        <f t="shared" si="25"/>
+        <v>39.5</v>
+      </c>
+      <c r="Q58">
+        <f t="shared" si="26"/>
+        <v>5.3E-3</v>
+      </c>
+      <c r="R58">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U58">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V58">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X58">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="N58">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="O58">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P58">
-        <f t="shared" si="23"/>
-        <v>39.5</v>
-      </c>
-      <c r="Q58">
-        <f t="shared" si="24"/>
-        <v>5.3E-3</v>
-      </c>
-      <c r="R58">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="T58">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U58">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V58">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X58">
-        <f t="shared" si="19"/>
         <v>0.8</v>
       </c>
       <c r="Y58">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Z58">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA58">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.6538645760000002E-3</v>
       </c>
       <c r="AB58">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AC58">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>13.28053254528</v>
       </c>
       <c r="AD58">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1.3280532545279999E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:37">
+    <row r="59" spans="1:40">
       <c r="A59" s="2" t="s">
         <v>22</v>
       </c>
@@ -6021,82 +6194,82 @@
         <v>69</v>
       </c>
       <c r="J59">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.91</v>
       </c>
       <c r="K59">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L59" t="s">
         <v>57</v>
       </c>
       <c r="M59">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="O59">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P59">
+        <f t="shared" si="25"/>
+        <v>13.2</v>
+      </c>
+      <c r="Q59">
+        <f t="shared" si="26"/>
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="R59">
+        <f t="shared" si="27"/>
+        <v>1</v>
+      </c>
+      <c r="T59">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U59">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V59">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X59">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="N59">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="O59">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P59">
-        <f t="shared" si="23"/>
-        <v>13.2</v>
-      </c>
-      <c r="Q59">
-        <f t="shared" si="24"/>
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="R59">
-        <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="T59">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U59">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V59">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X59">
-        <f t="shared" si="19"/>
         <v>0.8</v>
       </c>
       <c r="Y59">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Z59">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA59">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB59">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AC59">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>4.6280643718399999</v>
       </c>
       <c r="AD59">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>4.6280643718400001E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:37">
+    <row r="60" spans="1:40">
       <c r="A60" s="2" t="s">
         <v>64</v>
       </c>
@@ -6119,96 +6292,96 @@
         <v>70</v>
       </c>
       <c r="J60">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.34</v>
       </c>
       <c r="K60">
-        <f>$AN$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L60" t="s">
         <v>57</v>
       </c>
       <c r="M60">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="O60">
+        <f>$AN$4</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="P60">
+        <f t="shared" si="25"/>
+        <v>7</v>
+      </c>
+      <c r="Q60">
+        <f t="shared" si="26"/>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="R60">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <f>$AQ$3</f>
+        <v>0.24</v>
+      </c>
+      <c r="U60">
+        <f>$AQ$4</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V60">
+        <f>$AN$5</f>
+        <v>0.6784</v>
+      </c>
+      <c r="X60">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="N60">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="O60">
-        <f>$AK$4</f>
-        <v>1.5714285714285714</v>
-      </c>
-      <c r="P60">
-        <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="Q60">
-        <f t="shared" si="24"/>
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="R60">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="T60">
-        <f>$AN$3</f>
-        <v>0.24</v>
-      </c>
-      <c r="U60">
-        <f>$AN$4</f>
-        <v>0.11</v>
-      </c>
-      <c r="V60">
-        <f>$AK$5</f>
-        <v>0.6784</v>
-      </c>
-      <c r="X60">
-        <f t="shared" si="19"/>
         <v>0.78</v>
       </c>
       <c r="Y60">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Z60">
-        <f>$AJ$33</f>
+        <f>$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA60">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB60">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AC60">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1.8043480780800005</v>
       </c>
       <c r="AD60">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1.8043480780800005E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:37">
+    <row r="61" spans="1:40">
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:37">
+    <row r="62" spans="1:40">
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:37">
+    <row r="63" spans="1:40">
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:37">
+    <row r="64" spans="1:40">
       <c r="E64" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="AN18:AN19"/>
+    <mergeCell ref="AQ18:AQ19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
